--- a/research/traditional_assets/database/data/norway/norway_oil_gas_integrated.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_oil_gas_integrated.xlsx
@@ -650,10 +650,10 @@
         <v>0.1932140071431504</v>
       </c>
       <c r="X2">
-        <v>0.1009501378941284</v>
+        <v>0.1009146812588905</v>
       </c>
       <c r="Y2">
-        <v>0.092263869249022</v>
+        <v>0.09229932588425988</v>
       </c>
       <c r="Z2">
         <v>1.64938232748446</v>
@@ -662,10 +662,10 @@
         <v>0.236635455189236</v>
       </c>
       <c r="AB2">
-        <v>0.0820244265678957</v>
+        <v>0.08200019772931252</v>
       </c>
       <c r="AC2">
-        <v>0.1546110286213403</v>
+        <v>0.1546352574599235</v>
       </c>
       <c r="AD2">
         <v>29596</v>
@@ -787,10 +787,10 @@
         <v>0.1932140071431504</v>
       </c>
       <c r="X3">
-        <v>0.1009501378941284</v>
+        <v>0.1009146812588905</v>
       </c>
       <c r="Y3">
-        <v>0.092263869249022</v>
+        <v>0.09229932588425988</v>
       </c>
       <c r="Z3">
         <v>1.64938232748446</v>
@@ -799,10 +799,10 @@
         <v>0.236635455189236</v>
       </c>
       <c r="AB3">
-        <v>0.0820244265678957</v>
+        <v>0.08200019772931252</v>
       </c>
       <c r="AC3">
-        <v>0.1546110286213403</v>
+        <v>0.1546352574599235</v>
       </c>
       <c r="AD3">
         <v>29596</v>
@@ -1139,7 +1139,7 @@
         <v>35.5330882352941</v>
       </c>
       <c r="F2">
-        <v>5.69756422438528</v>
+        <v>5.85730901572318</v>
       </c>
       <c r="G2">
         <v>0.7631572161625541</v>
@@ -1157,13 +1157,13 @@
         <v>63866.2</v>
       </c>
       <c r="L2">
-        <v>4092.05792663909</v>
+        <v>4605.18916243296</v>
       </c>
       <c r="M2">
         <v>85460.2</v>
       </c>
       <c r="N2">
-        <v>88617.63592663909</v>
+        <v>89130.767162433</v>
       </c>
       <c r="O2">
         <v>29596</v>
@@ -1172,16 +1172,16 @@
         <v>92527.57799999999</v>
       </c>
       <c r="Q2">
-        <v>0.0820244265678957</v>
+        <v>0.0820001977293125</v>
       </c>
       <c r="R2">
-        <v>0.07461449602954449</v>
+        <v>0.0734358250727718</v>
       </c>
       <c r="S2">
         <v>0.041184</v>
       </c>
       <c r="T2">
-        <v>0.0429</v>
+        <v>0.04173</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.100950137894128</v>
+        <v>0.10091468125889</v>
       </c>
       <c r="X2">
-        <v>3.21434960295445</v>
+        <v>3.21231250727718</v>
       </c>
       <c r="Y2">
         <v>1.27285638011294</v>
@@ -1236,7 +1236,7 @@
         <v>63866.2</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.0433</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08630817697461586</v>
+        <v>0.08628213381842471</v>
       </c>
       <c r="C2">
-        <v>91737.42037598875</v>
+        <v>91738.09831568993</v>
       </c>
       <c r="D2">
-        <v>83735.42037598875</v>
+        <v>83736.09831568993</v>
       </c>
       <c r="E2">
         <v>-29596</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08630817697461586</v>
+        <v>0.08628213381842471</v>
       </c>
       <c r="T2">
         <v>0.9349222590860211</v>
       </c>
       <c r="U2">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.22</v>
       </c>
       <c r="W2">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08616431898527172</v>
+        <v>0.08612741312402418</v>
       </c>
       <c r="C3">
-        <v>90859.58985642997</v>
+        <v>90864.56160269018</v>
       </c>
       <c r="D3">
-        <v>83792.21185642997</v>
+        <v>83797.18360269019</v>
       </c>
       <c r="E3">
         <v>-28661.378</v>
@@ -1539,37 +1539,37 @@
         <v>28995</v>
       </c>
       <c r="M3">
-        <v>48.3199574</v>
+        <v>47.0114866</v>
       </c>
       <c r="N3">
-        <v>28946.6800426</v>
+        <v>28947.9885134</v>
       </c>
       <c r="O3">
-        <v>6368.269609372001</v>
+        <v>6368.557472948</v>
       </c>
       <c r="P3">
-        <v>22578.410433228</v>
+        <v>22579.431040452</v>
       </c>
       <c r="Q3">
-        <v>32364.410433228</v>
+        <v>32365.431040452</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08662733230835526</v>
+        <v>0.08660108396366079</v>
       </c>
       <c r="T3">
         <v>0.942288313248517</v>
       </c>
       <c r="U3">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.22</v>
       </c>
       <c r="W3">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>600.0626151214281</v>
+        <v>616.7641590810703</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08602046099592757</v>
+        <v>0.08597269242962365</v>
       </c>
       <c r="C4">
-        <v>89981.83642399113</v>
+        <v>89991.11407789977</v>
       </c>
       <c r="D4">
-        <v>83849.08042399114</v>
+        <v>83858.35807789977</v>
       </c>
       <c r="E4">
         <v>-27726.756</v>
@@ -1621,37 +1621,37 @@
         <v>28995</v>
       </c>
       <c r="M4">
-        <v>96.6399148</v>
+        <v>94.0229732</v>
       </c>
       <c r="N4">
-        <v>28898.3600852</v>
+        <v>28900.9770268</v>
       </c>
       <c r="O4">
-        <v>6357.639218744001</v>
+        <v>6358.214945896</v>
       </c>
       <c r="P4">
-        <v>22540.720866456</v>
+        <v>22542.762080904</v>
       </c>
       <c r="Q4">
-        <v>32326.720866456</v>
+        <v>32328.762080904</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.08695300101625261</v>
+        <v>0.08692654329553434</v>
       </c>
       <c r="T4">
         <v>0.9498046950469823</v>
       </c>
       <c r="U4">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.22</v>
       </c>
       <c r="W4">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>300.031307560714</v>
+        <v>308.3820795405351</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.0858766030065834</v>
+        <v>0.08581797173522311</v>
       </c>
       <c r="C5">
-        <v>89104.16023573259</v>
+        <v>89117.75593679161</v>
       </c>
       <c r="D5">
-        <v>83906.02623573258</v>
+        <v>83919.62193679161</v>
       </c>
       <c r="E5">
         <v>-26792.134</v>
@@ -1703,37 +1703,37 @@
         <v>28995</v>
       </c>
       <c r="M5">
-        <v>144.9598722</v>
+        <v>141.0344598</v>
       </c>
       <c r="N5">
-        <v>28850.0401278</v>
+        <v>28853.9655402</v>
       </c>
       <c r="O5">
-        <v>6347.008828116</v>
+        <v>6347.872418844</v>
       </c>
       <c r="P5">
-        <v>22503.031299684</v>
+        <v>22506.093121356</v>
       </c>
       <c r="Q5">
-        <v>32289.031299684</v>
+        <v>32292.093121356</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.08728538454286949</v>
+        <v>0.087258713129096</v>
       </c>
       <c r="T5">
         <v>0.9574760537897458</v>
       </c>
       <c r="U5">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.22</v>
       </c>
       <c r="W5">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>200.0208717071427</v>
+        <v>205.5880530270234</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08573274501723924</v>
+        <v>0.08566325104082259</v>
       </c>
       <c r="C6">
-        <v>88226.56144914162</v>
+        <v>88244.4873754103</v>
       </c>
       <c r="D6">
-        <v>83963.04944914162</v>
+        <v>83980.9753754103</v>
       </c>
       <c r="E6">
         <v>-25857.512</v>
@@ -1785,37 +1785,37 @@
         <v>28995</v>
       </c>
       <c r="M6">
-        <v>193.2798296</v>
+        <v>188.0459464</v>
       </c>
       <c r="N6">
-        <v>28801.7201704</v>
+        <v>28806.9540536</v>
       </c>
       <c r="O6">
-        <v>6336.378437488</v>
+        <v>6337.529891792</v>
       </c>
       <c r="P6">
-        <v>22465.341732912</v>
+        <v>22469.424161808</v>
       </c>
       <c r="Q6">
-        <v>32251.341732912</v>
+        <v>32255.424161808</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.08762469272629088</v>
+        <v>0.08759780316752352</v>
       </c>
       <c r="T6">
         <v>0.9653072325063168</v>
       </c>
       <c r="U6">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.22</v>
       </c>
       <c r="W6">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>150.015653780357</v>
+        <v>154.1910397702675</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08558888702789508</v>
+        <v>0.08550853034642203</v>
       </c>
       <c r="C7">
-        <v>87349.04022213396</v>
+        <v>87371.30859037423</v>
       </c>
       <c r="D7">
-        <v>84020.15022213396</v>
+        <v>84042.41859037423</v>
       </c>
       <c r="E7">
         <v>-24922.89</v>
@@ -1867,37 +1867,37 @@
         <v>28995</v>
       </c>
       <c r="M7">
-        <v>241.599787</v>
+        <v>235.057433</v>
       </c>
       <c r="N7">
-        <v>28753.400213</v>
+        <v>28759.942567</v>
       </c>
       <c r="O7">
-        <v>6325.748046860001</v>
+        <v>6327.18736474</v>
       </c>
       <c r="P7">
-        <v>22427.65216614</v>
+        <v>22432.75520226</v>
       </c>
       <c r="Q7">
-        <v>32213.65216614</v>
+        <v>32218.75520226</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.08797114423988957</v>
+        <v>0.08794403194360215</v>
       </c>
       <c r="T7">
         <v>0.9733032781432368</v>
       </c>
       <c r="U7">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.22</v>
       </c>
       <c r="W7">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>120.0125230242856</v>
+        <v>123.352831816214</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08544502903855093</v>
+        <v>0.08535380965202151</v>
       </c>
       <c r="C8">
-        <v>86471.59671305519</v>
+        <v>86498.21977887749</v>
       </c>
       <c r="D8">
-        <v>84077.32871305519</v>
+        <v>84103.9517788775</v>
       </c>
       <c r="E8">
         <v>-23988.268</v>
@@ -1949,37 +1949,37 @@
         <v>28995</v>
       </c>
       <c r="M8">
-        <v>289.9197444</v>
+        <v>282.0689196</v>
       </c>
       <c r="N8">
-        <v>28705.0802556</v>
+        <v>28712.9310804</v>
       </c>
       <c r="O8">
-        <v>6315.117656232001</v>
+        <v>6316.844837688001</v>
       </c>
       <c r="P8">
-        <v>22389.962599368</v>
+        <v>22396.086242712</v>
       </c>
       <c r="Q8">
-        <v>32175.962599368</v>
+        <v>32182.086242712</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.08832496706228823</v>
+        <v>0.08829762728938459</v>
       </c>
       <c r="T8">
         <v>0.9814694524107294</v>
       </c>
       <c r="U8">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.22</v>
       </c>
       <c r="W8">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>100.0104358535714</v>
+        <v>102.7940265135117</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08530117104920679</v>
+        <v>0.08519908895762097</v>
       </c>
       <c r="C9">
-        <v>85594.23108068221</v>
+        <v>85625.22113869224</v>
       </c>
       <c r="D9">
-        <v>84134.58508068221</v>
+        <v>84165.57513869225</v>
       </c>
       <c r="E9">
         <v>-23053.646</v>
@@ -2031,37 +2031,37 @@
         <v>28995</v>
       </c>
       <c r="M9">
-        <v>338.2397018</v>
+        <v>329.0804062</v>
       </c>
       <c r="N9">
-        <v>28656.7602982</v>
+        <v>28665.9195938</v>
       </c>
       <c r="O9">
-        <v>6304.487265604</v>
+        <v>6306.502310636</v>
       </c>
       <c r="P9">
-        <v>22352.273032596</v>
+        <v>22359.417283164</v>
       </c>
       <c r="Q9">
-        <v>32138.273032596</v>
+        <v>32145.417283164</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.0886863989776417</v>
+        <v>0.08865882683615159</v>
       </c>
       <c r="T9">
         <v>0.9898112433291361</v>
       </c>
       <c r="U9">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.22</v>
       </c>
       <c r="W9">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>85.72323073163257</v>
+        <v>88.10916558301004</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08515731305986264</v>
+        <v>0.08504436826322044</v>
       </c>
       <c r="C10">
-        <v>84716.94348422477</v>
+        <v>84752.31286817061</v>
       </c>
       <c r="D10">
-        <v>84191.91948422477</v>
+        <v>84227.28886817061</v>
       </c>
       <c r="E10">
         <v>-22119.024</v>
@@ -2113,37 +2113,37 @@
         <v>28995</v>
       </c>
       <c r="M10">
-        <v>386.5596592</v>
+        <v>376.0918928</v>
       </c>
       <c r="N10">
-        <v>28608.4403408</v>
+        <v>28618.9081072</v>
       </c>
       <c r="O10">
-        <v>6293.856874976</v>
+        <v>6296.159783584</v>
       </c>
       <c r="P10">
-        <v>22314.583465824</v>
+        <v>22322.748323616</v>
       </c>
       <c r="Q10">
-        <v>32100.583465824</v>
+        <v>32108.748323616</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.08905568810854633</v>
+        <v>0.08902787854697874</v>
       </c>
       <c r="T10">
         <v>0.9983343775283773</v>
       </c>
       <c r="U10">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V10">
         <v>0.22</v>
       </c>
       <c r="W10">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>75.00782689017851</v>
+        <v>77.09551988513378</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08501345507051847</v>
+        <v>0.08488964756881991</v>
       </c>
       <c r="C11">
-        <v>83839.73408332685</v>
+        <v>83879.49516624695</v>
       </c>
       <c r="D11">
-        <v>84249.33208332685</v>
+        <v>84289.09316624695</v>
       </c>
       <c r="E11">
         <v>-21184.402</v>
@@ -2195,37 +2195,37 @@
         <v>28995</v>
       </c>
       <c r="M11">
-        <v>434.8796166</v>
+        <v>423.1033794</v>
       </c>
       <c r="N11">
-        <v>28560.1203834</v>
+        <v>28571.8966206</v>
       </c>
       <c r="O11">
-        <v>6283.226484348</v>
+        <v>6285.817256532</v>
       </c>
       <c r="P11">
-        <v>22276.893899052</v>
+        <v>22286.079364068</v>
       </c>
       <c r="Q11">
-        <v>32062.893899052</v>
+        <v>32072.079364068</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.08943309348408623</v>
+        <v>0.08940504128441748</v>
       </c>
       <c r="T11">
         <v>1.007044833358371</v>
       </c>
       <c r="U11">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V11">
         <v>0.22</v>
       </c>
       <c r="W11">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>66.6736239023809</v>
+        <v>68.5293510090078</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.08486959708117432</v>
+        <v>0.08473492687441937</v>
       </c>
       <c r="C12">
-        <v>82962.60303806818</v>
+        <v>83006.76823243995</v>
       </c>
       <c r="D12">
-        <v>84306.82303806818</v>
+        <v>84350.98823243995</v>
       </c>
       <c r="E12">
         <v>-20249.78</v>
@@ -2277,37 +2277,37 @@
         <v>28995</v>
       </c>
       <c r="M12">
-        <v>483.199574</v>
+        <v>470.1148659999999</v>
       </c>
       <c r="N12">
-        <v>28511.800426</v>
+        <v>28524.885134</v>
       </c>
       <c r="O12">
-        <v>6272.596093720001</v>
+        <v>6275.47472948</v>
       </c>
       <c r="P12">
-        <v>22239.20433228</v>
+        <v>22249.41040452</v>
       </c>
       <c r="Q12">
-        <v>32025.20433228</v>
+        <v>32035.41040452</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.08981888564574925</v>
+        <v>0.08979058541602153</v>
       </c>
       <c r="T12">
         <v>1.015948854873476</v>
       </c>
       <c r="U12">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V12">
         <v>0.22</v>
       </c>
       <c r="W12">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>60.00626151214281</v>
+        <v>61.67641590810702</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.08472573909183016</v>
+        <v>0.08458020618001884</v>
       </c>
       <c r="C13">
-        <v>82085.55050896578</v>
+        <v>82134.13226685474</v>
       </c>
       <c r="D13">
-        <v>84364.39250896579</v>
+        <v>84412.97426685474</v>
       </c>
       <c r="E13">
         <v>-19315.158</v>
@@ -2359,37 +2359,37 @@
         <v>28995</v>
       </c>
       <c r="M13">
-        <v>531.5195314</v>
+        <v>517.1263526</v>
       </c>
       <c r="N13">
-        <v>28463.4804686</v>
+        <v>28477.8736474</v>
       </c>
       <c r="O13">
-        <v>6261.965703092</v>
+        <v>6265.132202428</v>
       </c>
       <c r="P13">
-        <v>22201.514765508</v>
+        <v>22212.741444972</v>
       </c>
       <c r="Q13">
-        <v>31987.514765508</v>
+        <v>31998.741444972</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.0902133472941912</v>
+        <v>0.09018479346069533</v>
       </c>
       <c r="T13">
         <v>1.025052966759707</v>
       </c>
       <c r="U13">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V13">
         <v>0.22</v>
       </c>
       <c r="W13">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>54.55114682922073</v>
+        <v>56.06946900737002</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.08458188110248602</v>
+        <v>0.08442548548561832</v>
       </c>
       <c r="C14">
-        <v>81208.57665697538</v>
+        <v>81261.5874701851</v>
       </c>
       <c r="D14">
-        <v>84422.04065697538</v>
+        <v>84475.05147018509</v>
       </c>
       <c r="E14">
         <v>-18380.536</v>
@@ -2441,37 +2441,37 @@
         <v>28995</v>
       </c>
       <c r="M14">
-        <v>579.8394888</v>
+        <v>564.1378391999999</v>
       </c>
       <c r="N14">
-        <v>28415.1605112</v>
+        <v>28430.8621608</v>
       </c>
       <c r="O14">
-        <v>6251.335312464</v>
+        <v>6254.789675376</v>
       </c>
       <c r="P14">
-        <v>22163.825198736</v>
+        <v>22176.072485424</v>
       </c>
       <c r="Q14">
-        <v>31949.825198736</v>
+        <v>31962.072485424</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.09061677398009774</v>
+        <v>0.09058796077911171</v>
       </c>
       <c r="T14">
         <v>1.034363990279716</v>
       </c>
       <c r="U14">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V14">
         <v>0.22</v>
       </c>
       <c r="W14">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>50.00521792678567</v>
+        <v>51.39701325675586</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.08443802311314184</v>
+        <v>0.08427076479121776</v>
       </c>
       <c r="C15">
-        <v>80331.68164349296</v>
+        <v>80389.13404371562</v>
       </c>
       <c r="D15">
-        <v>84479.76764349296</v>
+        <v>84537.22004371561</v>
       </c>
       <c r="E15">
         <v>-17445.914</v>
@@ -2523,37 +2523,37 @@
         <v>28995</v>
       </c>
       <c r="M15">
-        <v>628.1594462</v>
+        <v>611.1493257999999</v>
       </c>
       <c r="N15">
-        <v>28366.8405538</v>
+        <v>28383.8506742</v>
       </c>
       <c r="O15">
-        <v>6240.704921836</v>
+        <v>6244.447148323999</v>
       </c>
       <c r="P15">
-        <v>22126.135631964</v>
+        <v>22139.403525876</v>
       </c>
       <c r="Q15">
-        <v>31912.135631964</v>
+        <v>31925.403525876</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.09102947484269178</v>
+        <v>0.09100039631174456</v>
       </c>
       <c r="T15">
         <v>1.043889060317426</v>
       </c>
       <c r="U15">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V15">
         <v>0.22</v>
       </c>
       <c r="W15">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>46.15866270164831</v>
+        <v>47.44339685239002</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.0842941651237977</v>
+        <v>0.08411604409681722</v>
       </c>
       <c r="C16">
-        <v>79454.86563035623</v>
+        <v>79516.77218932379</v>
       </c>
       <c r="D16">
-        <v>84537.57363035623</v>
+        <v>84599.48018932379</v>
       </c>
       <c r="E16">
         <v>-16511.292</v>
@@ -2605,37 +2605,37 @@
         <v>28995</v>
       </c>
       <c r="M16">
-        <v>676.4794036000001</v>
+        <v>658.1608123999999</v>
       </c>
       <c r="N16">
-        <v>28318.5205964</v>
+        <v>28336.8391876</v>
       </c>
       <c r="O16">
-        <v>6230.074531208001</v>
+        <v>6234.104621271999</v>
       </c>
       <c r="P16">
-        <v>22088.446065192</v>
+        <v>22102.734566328</v>
       </c>
       <c r="Q16">
-        <v>31874.446065192</v>
+        <v>31888.734566328</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.09145177339976476</v>
+        <v>0.09142242336839213</v>
       </c>
       <c r="T16">
         <v>1.053635643611827</v>
       </c>
       <c r="U16">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V16">
         <v>0.22</v>
       </c>
       <c r="W16">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>42.86161536581629</v>
+        <v>44.05458279150502</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.08415030713445354</v>
+        <v>0.0839613234024167</v>
       </c>
       <c r="C17">
-        <v>78578.1287798462</v>
+        <v>78644.50210948233</v>
       </c>
       <c r="D17">
-        <v>84595.4587798462</v>
+        <v>84661.83210948233</v>
       </c>
       <c r="E17">
         <v>-15576.67</v>
@@ -2687,37 +2687,37 @@
         <v>28995</v>
       </c>
       <c r="M17">
-        <v>724.7993610000001</v>
+        <v>705.172299</v>
       </c>
       <c r="N17">
-        <v>28270.200639</v>
+        <v>28289.827701</v>
       </c>
       <c r="O17">
-        <v>6219.44414058</v>
+        <v>6223.76209422</v>
       </c>
       <c r="P17">
-        <v>22050.75649842</v>
+        <v>22066.06560678</v>
       </c>
       <c r="Q17">
-        <v>31836.75649842</v>
+        <v>31852.06560678</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.09188400839347476</v>
+        <v>0.09185438047343142</v>
       </c>
       <c r="T17">
         <v>1.063611558277862</v>
       </c>
       <c r="U17">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V17">
         <v>0.22</v>
       </c>
       <c r="W17">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>40.00417434142853</v>
+        <v>41.11761060540468</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.08400644914510938</v>
+        <v>0.08380660270801615</v>
       </c>
       <c r="C18">
-        <v>77701.4712546886</v>
+        <v>77772.32400726131</v>
       </c>
       <c r="D18">
-        <v>84653.42325468861</v>
+        <v>84724.27600726132</v>
       </c>
       <c r="E18">
         <v>-14642.048</v>
@@ -2769,37 +2769,37 @@
         <v>28995</v>
       </c>
       <c r="M18">
-        <v>773.1193184</v>
+        <v>752.1837856</v>
       </c>
       <c r="N18">
-        <v>28221.8806816</v>
+        <v>28242.8162144</v>
       </c>
       <c r="O18">
-        <v>6208.813749952</v>
+        <v>6213.419567168</v>
       </c>
       <c r="P18">
-        <v>22013.066931648</v>
+        <v>22029.396647232</v>
       </c>
       <c r="Q18">
-        <v>31799.066931648</v>
+        <v>31815.396647232</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.0923265346965588</v>
+        <v>0.0922966222714478</v>
       </c>
       <c r="T18">
         <v>1.073824994721658</v>
       </c>
       <c r="U18">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V18">
         <v>0.22</v>
       </c>
       <c r="W18">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>37.50391344508925</v>
+        <v>38.54775994256689</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.08386259115576523</v>
+        <v>0.08365188201361563</v>
       </c>
       <c r="C19">
-        <v>76824.89321805551</v>
+        <v>76900.2380863303</v>
       </c>
       <c r="D19">
-        <v>84711.46721805551</v>
+        <v>84786.81208633029</v>
       </c>
       <c r="E19">
         <v>-13707.426</v>
@@ -2851,37 +2851,37 @@
         <v>28995</v>
       </c>
       <c r="M19">
-        <v>821.4392758</v>
+        <v>799.1952722</v>
       </c>
       <c r="N19">
-        <v>28173.5607242</v>
+        <v>28195.8047278</v>
       </c>
       <c r="O19">
-        <v>6198.183359324</v>
+        <v>6203.077040116001</v>
       </c>
       <c r="P19">
-        <v>21975.377364876</v>
+        <v>21992.727687684</v>
       </c>
       <c r="Q19">
-        <v>31761.377364876</v>
+        <v>31778.727687684</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.09277972428405451</v>
+        <v>0.0927495204983321</v>
       </c>
       <c r="T19">
         <v>1.084284538067716</v>
       </c>
       <c r="U19">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V19">
         <v>0.22</v>
       </c>
       <c r="W19">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>35.29780088949577</v>
+        <v>36.28024465182766</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.08371873316642109</v>
+        <v>0.0834971613192151</v>
       </c>
       <c r="C20">
-        <v>75948.39483356682</v>
+        <v>76028.24455096065</v>
       </c>
       <c r="D20">
-        <v>84769.59083356682</v>
+        <v>84849.44055096064</v>
       </c>
       <c r="E20">
         <v>-12772.804</v>
@@ -2933,37 +2933,37 @@
         <v>28995</v>
       </c>
       <c r="M20">
-        <v>869.7592332</v>
+        <v>846.2067588</v>
       </c>
       <c r="N20">
-        <v>28125.2407668</v>
+        <v>28148.7932412</v>
       </c>
       <c r="O20">
-        <v>6187.552968696001</v>
+        <v>6192.734513064001</v>
       </c>
       <c r="P20">
-        <v>21937.687798104</v>
+        <v>21956.058728136</v>
       </c>
       <c r="Q20">
-        <v>31723.687798104</v>
+        <v>31742.058728136</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.09324396727612326</v>
+        <v>0.09321346502343303</v>
       </c>
       <c r="T20">
         <v>1.094999192227091</v>
       </c>
       <c r="U20">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V20">
         <v>0.22</v>
       </c>
       <c r="W20">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>33.33681195119045</v>
+        <v>34.2646755045039</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.08357487517707693</v>
+        <v>0.08334244062481456</v>
       </c>
       <c r="C21">
-        <v>75071.97626529179</v>
+        <v>75156.34360602775</v>
       </c>
       <c r="D21">
-        <v>84827.79426529178</v>
+        <v>84912.16160602774</v>
       </c>
       <c r="E21">
         <v>-11838.182</v>
@@ -3015,37 +3015,37 @@
         <v>28995</v>
       </c>
       <c r="M21">
-        <v>918.0791906000001</v>
+        <v>893.2182453999999</v>
       </c>
       <c r="N21">
-        <v>28076.9208094</v>
+        <v>28101.7817546</v>
       </c>
       <c r="O21">
-        <v>6176.922578068</v>
+        <v>6182.391986012</v>
       </c>
       <c r="P21">
-        <v>21899.998231332</v>
+        <v>21919.389768588</v>
       </c>
       <c r="Q21">
-        <v>31685.998231332</v>
+        <v>31705.389768588</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.09371967305811965</v>
+        <v>0.09368886496890687</v>
       </c>
       <c r="T21">
         <v>1.105978405748427</v>
       </c>
       <c r="U21">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V21">
         <v>0.22</v>
       </c>
       <c r="W21">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>31.58224290112779</v>
+        <v>32.46127153058265</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.08343101718773277</v>
+        <v>0.08318771993041403</v>
       </c>
       <c r="C22">
-        <v>74195.63767775059</v>
+        <v>74284.53545701316</v>
       </c>
       <c r="D22">
-        <v>84886.0776777506</v>
+        <v>84974.97545701316</v>
       </c>
       <c r="E22">
         <v>-10903.56</v>
@@ -3097,37 +3097,37 @@
         <v>28995</v>
       </c>
       <c r="M22">
-        <v>966.399148</v>
+        <v>940.2297319999999</v>
       </c>
       <c r="N22">
-        <v>28028.600852</v>
+        <v>28054.770268</v>
       </c>
       <c r="O22">
-        <v>6166.29218744</v>
+        <v>6172.04945896</v>
       </c>
       <c r="P22">
-        <v>21862.30866456</v>
+        <v>21882.72080904</v>
       </c>
       <c r="Q22">
-        <v>31648.30866456</v>
+        <v>31668.72080904</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.09420727148466596</v>
+        <v>0.09417614991301754</v>
       </c>
       <c r="T22">
         <v>1.117232099607795</v>
       </c>
       <c r="U22">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V22">
         <v>0.22</v>
       </c>
       <c r="W22">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>30.0031307560714</v>
+        <v>30.83820795405351</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08328715919838861</v>
+        <v>0.08303299923601348</v>
       </c>
       <c r="C23">
-        <v>73319.3792359159</v>
+        <v>73412.82031000697</v>
       </c>
       <c r="D23">
-        <v>84944.44123591589</v>
+        <v>85037.88231000697</v>
       </c>
       <c r="E23">
         <v>-9968.938000000002</v>
@@ -3179,37 +3179,37 @@
         <v>28995</v>
       </c>
       <c r="M23">
-        <v>1014.7191054</v>
+        <v>987.2412185999998</v>
       </c>
       <c r="N23">
-        <v>27980.2808946</v>
+        <v>28007.7587814</v>
       </c>
       <c r="O23">
-        <v>6155.661796812</v>
+        <v>6161.706931908</v>
       </c>
       <c r="P23">
-        <v>21824.619097788</v>
+        <v>21846.051849492</v>
       </c>
       <c r="Q23">
-        <v>31610.619097788</v>
+        <v>31632.051849492</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.09470721417517546</v>
+        <v>0.0946757711848272</v>
       </c>
       <c r="T23">
         <v>1.128770697109173</v>
       </c>
       <c r="U23">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V23">
         <v>0.22</v>
       </c>
       <c r="W23">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>28.57441024387753</v>
+        <v>29.36972186100335</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.08314330120904445</v>
+        <v>0.08287827854161296</v>
       </c>
       <c r="C24">
-        <v>72443.20110521434</v>
+        <v>72541.19837170994</v>
       </c>
       <c r="D24">
-        <v>85002.88510521433</v>
+        <v>85100.88237170994</v>
       </c>
       <c r="E24">
         <v>-9034.315999999999</v>
@@ -3261,37 +3261,37 @@
         <v>28995</v>
       </c>
       <c r="M24">
-        <v>1063.0390628</v>
+        <v>1034.2527052</v>
       </c>
       <c r="N24">
-        <v>27931.9609372</v>
+        <v>27960.7472948</v>
       </c>
       <c r="O24">
-        <v>6145.031406184</v>
+        <v>6151.364404856</v>
       </c>
       <c r="P24">
-        <v>21786.929531016</v>
+        <v>21809.382889944</v>
       </c>
       <c r="Q24">
-        <v>31572.929531016</v>
+        <v>31595.382889944</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.09521997590903135</v>
+        <v>0.09518820325847815</v>
       </c>
       <c r="T24">
         <v>1.140605156084946</v>
       </c>
       <c r="U24">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V24">
         <v>0.22</v>
       </c>
       <c r="W24">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>27.27557341461037</v>
+        <v>28.03473450368501</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.08299944321970032</v>
+        <v>0.08272355784721243</v>
       </c>
       <c r="C25">
-        <v>71567.10345152816</v>
+        <v>71669.66984943586</v>
       </c>
       <c r="D25">
-        <v>85061.40945152816</v>
+        <v>85163.97584943585</v>
       </c>
       <c r="E25">
         <v>-8099.694</v>
@@ -3343,37 +3343,37 @@
         <v>28995</v>
       </c>
       <c r="M25">
-        <v>1111.3590202</v>
+        <v>1081.2641918</v>
       </c>
       <c r="N25">
-        <v>27883.6409798</v>
+        <v>27913.7358082</v>
       </c>
       <c r="O25">
-        <v>6134.401015556</v>
+        <v>6141.021877804</v>
       </c>
       <c r="P25">
-        <v>21749.239964244</v>
+        <v>21772.713930396</v>
       </c>
       <c r="Q25">
-        <v>31535.239964244</v>
+        <v>31558.713930396</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.09574605612948092</v>
+        <v>0.09571394525612004</v>
       </c>
       <c r="T25">
         <v>1.152747003605544</v>
       </c>
       <c r="U25">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V25">
         <v>0.22</v>
       </c>
       <c r="W25">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>26.08967891832296</v>
+        <v>26.81583300352479</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.08285558523035616</v>
+        <v>0.08256883715281188</v>
       </c>
       <c r="C26">
-        <v>70691.08644119681</v>
+        <v>70798.23495111374</v>
       </c>
       <c r="D26">
-        <v>85120.01444119681</v>
+        <v>85227.16295111374</v>
       </c>
       <c r="E26">
         <v>-7165.072</v>
@@ -3425,37 +3425,37 @@
         <v>28995</v>
       </c>
       <c r="M26">
-        <v>1159.6789776</v>
+        <v>1128.2756784</v>
       </c>
       <c r="N26">
-        <v>27835.3210224</v>
+        <v>27866.7243216</v>
       </c>
       <c r="O26">
-        <v>6123.770624928</v>
+        <v>6130.679350752</v>
       </c>
       <c r="P26">
-        <v>21711.550397472</v>
+        <v>21736.044970848</v>
       </c>
       <c r="Q26">
-        <v>31497.550397472</v>
+        <v>31522.044970848</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.09628598056625809</v>
+        <v>0.09625352256948932</v>
       </c>
       <c r="T26">
         <v>1.165208373429315</v>
       </c>
       <c r="U26">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V26">
         <v>0.22</v>
       </c>
       <c r="W26">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>25.00260896339283</v>
+        <v>25.69850662837793</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.082711727241012</v>
+        <v>0.08241411645841136</v>
       </c>
       <c r="C27">
-        <v>69815.15024101837</v>
+        <v>69926.89388529018</v>
       </c>
       <c r="D27">
-        <v>85178.70024101838</v>
+        <v>85290.44388529018</v>
       </c>
       <c r="E27">
         <v>-6230.450000000001</v>
@@ -3507,37 +3507,37 @@
         <v>28995</v>
       </c>
       <c r="M27">
-        <v>1207.998935</v>
+        <v>1175.287165</v>
       </c>
       <c r="N27">
-        <v>27787.001065</v>
+        <v>27819.712835</v>
       </c>
       <c r="O27">
-        <v>6113.1402343</v>
+        <v>6120.3368237</v>
       </c>
       <c r="P27">
-        <v>21673.8608307</v>
+        <v>21699.3760113</v>
       </c>
       <c r="Q27">
-        <v>31459.8608307</v>
+        <v>31485.3760113</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.09684030298801599</v>
+        <v>0.09680748861121515</v>
       </c>
       <c r="T27">
         <v>1.178002046448387</v>
       </c>
       <c r="U27">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V27">
         <v>0.22</v>
       </c>
       <c r="W27">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>24.00250460485712</v>
+        <v>24.67056636324281</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08256786925166783</v>
+        <v>0.08225939576401083</v>
       </c>
       <c r="C28">
-        <v>68939.29501825135</v>
+        <v>69055.64686113159</v>
       </c>
       <c r="D28">
-        <v>85237.46701825134</v>
+        <v>85353.81886113159</v>
       </c>
       <c r="E28">
         <v>-5295.828000000001</v>
@@ -3589,37 +3589,37 @@
         <v>28995</v>
       </c>
       <c r="M28">
-        <v>1256.3188924</v>
+        <v>1222.2986516</v>
       </c>
       <c r="N28">
-        <v>27738.6811076</v>
+        <v>27772.7013484</v>
       </c>
       <c r="O28">
-        <v>6102.509843672</v>
+        <v>6109.994296648</v>
       </c>
       <c r="P28">
-        <v>21636.171263928</v>
+        <v>21662.707051752</v>
       </c>
       <c r="Q28">
-        <v>31422.171263928</v>
+        <v>31448.707051752</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.09740960709684843</v>
+        <v>0.09737642670812274</v>
       </c>
       <c r="T28">
         <v>1.19114149441392</v>
       </c>
       <c r="U28">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V28">
         <v>0.22</v>
       </c>
       <c r="W28">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>23.07933135082416</v>
+        <v>23.72169842619501</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.08242401126232368</v>
+        <v>0.08210467506961028</v>
       </c>
       <c r="C29">
-        <v>68063.520940616</v>
+        <v>68184.49408842652</v>
       </c>
       <c r="D29">
-        <v>85296.31494061599</v>
+        <v>85417.28808842653</v>
       </c>
       <c r="E29">
         <v>-4361.205999999998</v>
@@ -3671,37 +3671,37 @@
         <v>28995</v>
       </c>
       <c r="M29">
-        <v>1304.6388498</v>
+        <v>1269.3101382</v>
       </c>
       <c r="N29">
-        <v>27690.3611502</v>
+        <v>27725.6898618</v>
       </c>
       <c r="O29">
-        <v>6091.879453044</v>
+        <v>6099.651769596</v>
       </c>
       <c r="P29">
-        <v>21598.481697156</v>
+        <v>21626.038092204</v>
       </c>
       <c r="Q29">
-        <v>31384.481697156</v>
+        <v>31412.038092204</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.0979945085785256</v>
+        <v>0.09796095215015108</v>
       </c>
       <c r="T29">
         <v>1.204640927255221</v>
       </c>
       <c r="U29">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V29">
         <v>0.22</v>
       </c>
       <c r="W29">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>22.22454130079363</v>
+        <v>22.8431170030026</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.08228015327297954</v>
+        <v>0.08194995437520974</v>
       </c>
       <c r="C30">
-        <v>67187.82817629621</v>
+        <v>67313.43577758805</v>
       </c>
       <c r="D30">
-        <v>85355.24417629621</v>
+        <v>85480.85177758805</v>
       </c>
       <c r="E30">
         <v>-3426.583999999999</v>
@@ -3753,37 +3753,37 @@
         <v>28995</v>
       </c>
       <c r="M30">
-        <v>1352.9588072</v>
+        <v>1316.3216248</v>
       </c>
       <c r="N30">
-        <v>27642.0411928</v>
+        <v>27678.6783752</v>
       </c>
       <c r="O30">
-        <v>6081.249062416</v>
+        <v>6089.309242544</v>
       </c>
       <c r="P30">
-        <v>21560.792130384</v>
+        <v>21589.369132656</v>
       </c>
       <c r="Q30">
-        <v>31346.792130384</v>
+        <v>31375.369132656</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.09859565732358269</v>
+        <v>0.09856171441001355</v>
       </c>
       <c r="T30">
         <v>1.218515344342114</v>
       </c>
       <c r="U30">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V30">
         <v>0.22</v>
       </c>
       <c r="W30">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>21.43080768290814</v>
+        <v>22.02729139575251</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.08213629528363536</v>
+        <v>0.08179523368080922</v>
       </c>
       <c r="C31">
-        <v>66312.21689394093</v>
+        <v>66442.47213965593</v>
       </c>
       <c r="D31">
-        <v>85414.25489394093</v>
+        <v>85544.51013965593</v>
       </c>
       <c r="E31">
         <v>-2491.962000000003</v>
@@ -3835,37 +3835,37 @@
         <v>28995</v>
       </c>
       <c r="M31">
-        <v>1401.2787646</v>
+        <v>1363.3331114</v>
       </c>
       <c r="N31">
-        <v>27593.7212354</v>
+        <v>27631.6668886</v>
       </c>
       <c r="O31">
-        <v>6070.618671788</v>
+        <v>6078.966715492</v>
       </c>
       <c r="P31">
-        <v>21523.102563612</v>
+        <v>21552.700173108</v>
       </c>
       <c r="Q31">
-        <v>31309.102563612</v>
+        <v>31338.700173108</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.09921373983610615</v>
+        <v>0.09917939955043552</v>
       </c>
       <c r="T31">
         <v>1.232780590079342</v>
       </c>
       <c r="U31">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V31">
         <v>0.22</v>
       </c>
       <c r="W31">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>20.691814314532</v>
+        <v>21.26772962348518</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.08199243729429122</v>
+        <v>0.08164051298640866</v>
       </c>
       <c r="C32">
-        <v>65436.68726266579</v>
+        <v>65571.60338629918</v>
       </c>
       <c r="D32">
-        <v>85473.34726266579</v>
+        <v>85608.26338629918</v>
       </c>
       <c r="E32">
         <v>-1557.34</v>
@@ -3917,37 +3917,37 @@
         <v>28995</v>
       </c>
       <c r="M32">
-        <v>1449.598722</v>
+        <v>1410.344598</v>
       </c>
       <c r="N32">
-        <v>27545.401278</v>
+        <v>27584.655402</v>
       </c>
       <c r="O32">
-        <v>6059.98828116</v>
+        <v>6068.62418844</v>
       </c>
       <c r="P32">
-        <v>21485.41299684</v>
+        <v>21516.03121356</v>
       </c>
       <c r="Q32">
-        <v>31271.41299684</v>
+        <v>31302.03121356</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.09984948184898745</v>
+        <v>0.09981473283772668</v>
       </c>
       <c r="T32">
         <v>1.247453414266205</v>
       </c>
       <c r="U32">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V32">
         <v>0.22</v>
       </c>
       <c r="W32">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>20.00208717071427</v>
+        <v>20.55880530270234</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.08184857930494706</v>
+        <v>0.08148579229200814</v>
       </c>
       <c r="C33">
-        <v>64561.23945205476</v>
+        <v>64700.82972981812</v>
       </c>
       <c r="D33">
-        <v>85532.52145205476</v>
+        <v>85672.11172981812</v>
       </c>
       <c r="E33">
         <v>-622.7180000000008</v>
@@ -3999,37 +3999,37 @@
         <v>28995</v>
       </c>
       <c r="M33">
-        <v>1497.9186794</v>
+        <v>1457.3560846</v>
       </c>
       <c r="N33">
-        <v>27497.0813206</v>
+        <v>27537.6439154</v>
       </c>
       <c r="O33">
-        <v>6049.357890532</v>
+        <v>6058.281661388</v>
       </c>
       <c r="P33">
-        <v>21447.723430068</v>
+        <v>21479.362254012</v>
       </c>
       <c r="Q33">
-        <v>31233.723430068</v>
+        <v>31265.362254012</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1005036511665899</v>
+        <v>0.1004684815826205</v>
       </c>
       <c r="T33">
         <v>1.262551537704862</v>
       </c>
       <c r="U33">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V33">
         <v>0.22</v>
       </c>
       <c r="W33">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>19.35685855230413</v>
+        <v>19.89561803487323</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.0817047213156029</v>
+        <v>0.08133107159760762</v>
       </c>
       <c r="C34">
-        <v>63685.87363216175</v>
+        <v>63830.15138314702</v>
       </c>
       <c r="D34">
-        <v>85591.77763216174</v>
+        <v>85736.05538314702</v>
       </c>
       <c r="E34">
         <v>311.9039999999986</v>
@@ -4081,37 +4081,37 @@
         <v>28995</v>
       </c>
       <c r="M34">
-        <v>1546.2386368</v>
+        <v>1504.3675712</v>
       </c>
       <c r="N34">
-        <v>27448.7613632</v>
+        <v>27490.6324288</v>
       </c>
       <c r="O34">
-        <v>6038.727499904</v>
+        <v>6047.939134336</v>
       </c>
       <c r="P34">
-        <v>21410.033863296</v>
+        <v>21442.693294464</v>
       </c>
       <c r="Q34">
-        <v>31196.033863296</v>
+        <v>31228.693294464</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1011770607582396</v>
+        <v>0.1011414582317759</v>
       </c>
       <c r="T34">
         <v>1.278093723597596</v>
       </c>
       <c r="U34">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V34">
         <v>0.22</v>
       </c>
       <c r="W34">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>18.75195672254463</v>
+        <v>19.27387997128345</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.08156086332625874</v>
+        <v>0.08117635090320707</v>
       </c>
       <c r="C35">
-        <v>62810.58997351225</v>
+        <v>62959.5685598563</v>
       </c>
       <c r="D35">
-        <v>85651.11597351225</v>
+        <v>85800.0945598563</v>
       </c>
       <c r="E35">
         <v>1246.526000000002</v>
@@ -4163,37 +4163,37 @@
         <v>28995</v>
       </c>
       <c r="M35">
-        <v>1594.5585942</v>
+        <v>1551.3790578</v>
       </c>
       <c r="N35">
-        <v>27400.4414058</v>
+        <v>27443.6209422</v>
       </c>
       <c r="O35">
-        <v>6028.097109276</v>
+        <v>6037.596607284</v>
       </c>
       <c r="P35">
-        <v>21372.344296524</v>
+        <v>21406.024334916</v>
       </c>
       <c r="Q35">
-        <v>31158.344296524</v>
+        <v>31192.024334916</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1018705721287444</v>
+        <v>0.10183452373613</v>
       </c>
       <c r="T35">
         <v>1.294099855337875</v>
       </c>
       <c r="U35">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V35">
         <v>0.22</v>
       </c>
       <c r="W35">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>18.18371560974024</v>
+        <v>18.68982300245667</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.08141700533691458</v>
+        <v>0.08102163020880654</v>
       </c>
       <c r="C36">
-        <v>61935.38864710496</v>
+        <v>62089.08147415493</v>
       </c>
       <c r="D36">
-        <v>85710.53664710496</v>
+        <v>85864.22947415493</v>
       </c>
       <c r="E36">
         <v>2181.148000000001</v>
@@ -4245,37 +4245,37 @@
         <v>28995</v>
       </c>
       <c r="M36">
-        <v>1642.8785516</v>
+        <v>1598.3905444</v>
       </c>
       <c r="N36">
-        <v>27352.1214484</v>
+        <v>27396.6094556</v>
       </c>
       <c r="O36">
-        <v>6017.466718648</v>
+        <v>6027.254080232</v>
       </c>
       <c r="P36">
-        <v>21334.654729752</v>
+        <v>21369.355375368</v>
       </c>
       <c r="Q36">
-        <v>31120.654729752</v>
+        <v>31155.355375368</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1025850989953251</v>
+        <v>0.1025485912254645</v>
       </c>
       <c r="T36">
         <v>1.310591021373313</v>
       </c>
       <c r="U36">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V36">
         <v>0.22</v>
       </c>
       <c r="W36">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>17.64890044474788</v>
+        <v>18.14012232591383</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.08127314734757045</v>
+        <v>0.080866909514406</v>
       </c>
       <c r="C37">
-        <v>61060.26982441342</v>
+        <v>61218.69034089286</v>
       </c>
       <c r="D37">
-        <v>85770.03982441343</v>
+        <v>85928.46034089287</v>
       </c>
       <c r="E37">
         <v>3115.77</v>
@@ -4327,37 +4327,37 @@
         <v>28995</v>
       </c>
       <c r="M37">
-        <v>1691.198509</v>
+        <v>1645.402031</v>
       </c>
       <c r="N37">
-        <v>27303.801491</v>
+        <v>27349.597969</v>
       </c>
       <c r="O37">
-        <v>6006.83632802</v>
+        <v>6016.91155318</v>
       </c>
       <c r="P37">
-        <v>21296.96516298</v>
+        <v>21332.68641582</v>
       </c>
       <c r="Q37">
-        <v>31082.96516298</v>
+        <v>31118.68641582</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1033216113039545</v>
+        <v>0.1032846300221631</v>
       </c>
       <c r="T37">
         <v>1.32758960790215</v>
       </c>
       <c r="U37">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V37">
         <v>0.22</v>
       </c>
       <c r="W37">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>17.14464614632652</v>
+        <v>17.62183311660201</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.08112928935822628</v>
+        <v>0.08071218882000547</v>
       </c>
       <c r="C38">
-        <v>60185.23367738773</v>
+        <v>60348.39537556341</v>
       </c>
       <c r="D38">
-        <v>85829.62567738772</v>
+        <v>85992.78737556341</v>
       </c>
       <c r="E38">
         <v>4050.392</v>
@@ -4409,37 +4409,37 @@
         <v>28995</v>
       </c>
       <c r="M38">
-        <v>1739.5184664</v>
+        <v>1692.4135176</v>
       </c>
       <c r="N38">
-        <v>27255.4815336</v>
+        <v>27302.5864824</v>
       </c>
       <c r="O38">
-        <v>5996.205937392</v>
+        <v>6006.569026128001</v>
       </c>
       <c r="P38">
-        <v>21259.275596208</v>
+        <v>21296.017456272</v>
       </c>
       <c r="Q38">
-        <v>31045.275596208</v>
+        <v>31082.017456272</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1040811396222286</v>
+        <v>0.1040436700312586</v>
       </c>
       <c r="T38">
         <v>1.345119400260013</v>
       </c>
       <c r="U38">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V38">
         <v>0.22</v>
       </c>
       <c r="W38">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>16.66840597559522</v>
+        <v>17.13233775225195</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.08098543136888213</v>
+        <v>0.08055746812560495</v>
       </c>
       <c r="C39">
-        <v>59310.28037845602</v>
+        <v>59478.19679430562</v>
       </c>
       <c r="D39">
-        <v>85889.29437845602</v>
+        <v>86057.21079430562</v>
       </c>
       <c r="E39">
         <v>4985.013999999996</v>
@@ -4491,37 +4491,37 @@
         <v>28995</v>
       </c>
       <c r="M39">
-        <v>1787.8384238</v>
+        <v>1739.4250042</v>
       </c>
       <c r="N39">
-        <v>27207.1615762</v>
+        <v>27255.5749958</v>
       </c>
       <c r="O39">
-        <v>5985.575546764</v>
+        <v>5996.226499076</v>
       </c>
       <c r="P39">
-        <v>21221.586029436</v>
+        <v>21259.348496724</v>
       </c>
       <c r="Q39">
-        <v>31007.586029436</v>
+        <v>31045.348496724</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1048647799506066</v>
+        <v>0.1048268065485793</v>
       </c>
       <c r="T39">
         <v>1.36320569396257</v>
       </c>
       <c r="U39">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V39">
         <v>0.22</v>
       </c>
       <c r="W39">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>16.21790851679535</v>
+        <v>16.66930159678569</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.08084157337953797</v>
+        <v>0.0804027474312044</v>
       </c>
       <c r="C40">
-        <v>58435.41010052639</v>
+        <v>58608.09481390679</v>
       </c>
       <c r="D40">
-        <v>85949.04610052639</v>
+        <v>86121.73081390679</v>
       </c>
       <c r="E40">
         <v>5919.635999999999</v>
@@ -4573,37 +4573,37 @@
         <v>28995</v>
       </c>
       <c r="M40">
-        <v>1836.1583812</v>
+        <v>1786.4364908</v>
       </c>
       <c r="N40">
-        <v>27158.8416188</v>
+        <v>27208.5635092</v>
       </c>
       <c r="O40">
-        <v>5974.945156136</v>
+        <v>5985.883972024</v>
       </c>
       <c r="P40">
-        <v>21183.896462664</v>
+        <v>21222.679537176</v>
       </c>
       <c r="Q40">
-        <v>30969.896462664</v>
+        <v>31008.679537176</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1056736989992548</v>
+        <v>0.1056352055342007</v>
       </c>
       <c r="T40">
         <v>1.381875416494242</v>
       </c>
       <c r="U40">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V40">
         <v>0.22</v>
       </c>
       <c r="W40">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>15.7911214505639</v>
+        <v>16.23063576529132</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.08069771539019382</v>
+        <v>0.08024802673680387</v>
       </c>
       <c r="C41">
-        <v>57560.62301698832</v>
+        <v>57738.08965180475</v>
       </c>
       <c r="D41">
-        <v>86008.88101698832</v>
+        <v>86186.34765180475</v>
       </c>
       <c r="E41">
         <v>6854.258000000002</v>
@@ -4655,37 +4655,37 @@
         <v>28995</v>
       </c>
       <c r="M41">
-        <v>1884.4783386</v>
+        <v>1833.4479774</v>
       </c>
       <c r="N41">
-        <v>27110.5216614</v>
+        <v>27161.5520226</v>
       </c>
       <c r="O41">
-        <v>5964.314765507999</v>
+        <v>5975.541444972</v>
       </c>
       <c r="P41">
-        <v>21146.206895892</v>
+        <v>21186.010577628</v>
       </c>
       <c r="Q41">
-        <v>30932.206895892</v>
+        <v>30972.010577628</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1065091399839243</v>
+        <v>0.1064701094045965</v>
       </c>
       <c r="T41">
         <v>1.401157261076132</v>
       </c>
       <c r="U41">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V41">
         <v>0.22</v>
       </c>
       <c r="W41">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>15.38622090054944</v>
+        <v>15.81446561746334</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.08055385740084967</v>
+        <v>0.08009330604240333</v>
       </c>
       <c r="C42">
-        <v>56685.91930171454</v>
+        <v>56868.18152609045</v>
       </c>
       <c r="D42">
-        <v>86068.79930171453</v>
+        <v>86251.06152609045</v>
       </c>
       <c r="E42">
         <v>7788.879999999997</v>
@@ -4737,37 +4737,37 @@
         <v>28995</v>
       </c>
       <c r="M42">
-        <v>1932.798296</v>
+        <v>1880.459464</v>
       </c>
       <c r="N42">
-        <v>27062.201704</v>
+        <v>27114.540536</v>
       </c>
       <c r="O42">
-        <v>5953.68437488</v>
+        <v>5965.19891792</v>
       </c>
       <c r="P42">
-        <v>21108.51732912</v>
+        <v>21149.34161808</v>
       </c>
       <c r="Q42">
-        <v>30894.51732912</v>
+        <v>30935.34161808</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1073724290014161</v>
+        <v>0.1073328434040056</v>
       </c>
       <c r="T42">
         <v>1.421081833810752</v>
       </c>
       <c r="U42">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V42">
         <v>0.22</v>
       </c>
       <c r="W42">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>15.0015653780357</v>
+        <v>15.41910397702676</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.08040999941150551</v>
+        <v>0.0799385853480028</v>
       </c>
       <c r="C43">
-        <v>55811.29912906256</v>
+        <v>55998.37065551035</v>
       </c>
       <c r="D43">
-        <v>86128.80112906256</v>
+        <v>86315.87265551035</v>
       </c>
       <c r="E43">
         <v>8723.502</v>
@@ -4819,37 +4819,37 @@
         <v>28995</v>
       </c>
       <c r="M43">
-        <v>1981.1182534</v>
+        <v>1927.4709506</v>
       </c>
       <c r="N43">
-        <v>27013.8817466</v>
+        <v>27067.5290494</v>
       </c>
       <c r="O43">
-        <v>5943.053984252</v>
+        <v>5954.856390868</v>
       </c>
       <c r="P43">
-        <v>21070.827762348</v>
+        <v>21112.672658532</v>
       </c>
       <c r="Q43">
-        <v>30856.827762348</v>
+        <v>30898.672658532</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1082649820533992</v>
+        <v>0.1082248226237336</v>
       </c>
       <c r="T43">
         <v>1.441681815790613</v>
       </c>
       <c r="U43">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V43">
         <v>0.22</v>
       </c>
       <c r="W43">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>14.63567353954702</v>
+        <v>15.04302827027001</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.08026614142216137</v>
+        <v>0.07978386465360227</v>
       </c>
       <c r="C44">
-        <v>54936.76267387648</v>
+        <v>55128.65725946888</v>
       </c>
       <c r="D44">
-        <v>86188.88667387648</v>
+        <v>86380.78125946887</v>
       </c>
       <c r="E44">
         <v>9658.123999999996</v>
@@ -4901,37 +4901,37 @@
         <v>28995</v>
       </c>
       <c r="M44">
-        <v>2029.4382108</v>
+        <v>1974.4824372</v>
       </c>
       <c r="N44">
-        <v>26965.5617892</v>
+        <v>27020.5175628</v>
       </c>
       <c r="O44">
-        <v>5932.423593624</v>
+        <v>5944.513863816</v>
       </c>
       <c r="P44">
-        <v>21033.138195576</v>
+        <v>21076.003698984</v>
       </c>
       <c r="Q44">
-        <v>30819.138195576</v>
+        <v>30862.003698984</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1091883127968299</v>
+        <v>0.1091475597475901</v>
       </c>
       <c r="T44">
         <v>1.462992141976677</v>
       </c>
       <c r="U44">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V44">
         <v>0.22</v>
       </c>
       <c r="W44">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>14.28720512193876</v>
+        <v>14.68486093050167</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.0801222834328172</v>
+        <v>0.07962914395920175</v>
       </c>
       <c r="C45">
-        <v>54062.31011148867</v>
+        <v>54259.04155803091</v>
       </c>
       <c r="D45">
-        <v>86249.05611148867</v>
+        <v>86445.7875580309</v>
       </c>
       <c r="E45">
         <v>10592.746</v>
@@ -4983,37 +4983,37 @@
         <v>28995</v>
       </c>
       <c r="M45">
-        <v>2077.7581682</v>
+        <v>2021.4939238</v>
       </c>
       <c r="N45">
-        <v>26917.2418318</v>
+        <v>26973.5060762</v>
       </c>
       <c r="O45">
-        <v>5921.793202995999</v>
+        <v>5934.171336764</v>
       </c>
       <c r="P45">
-        <v>20995.448628804</v>
+        <v>21039.334739436</v>
       </c>
       <c r="Q45">
-        <v>30781.448628804</v>
+        <v>30825.334739436</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1101440411102056</v>
+        <v>0.1101026736126346</v>
       </c>
       <c r="T45">
         <v>1.485050198906111</v>
       </c>
       <c r="U45">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V45">
         <v>0.22</v>
       </c>
       <c r="W45">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>13.95494453770763</v>
+        <v>14.34335253676907</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.07997842544347306</v>
+        <v>0.07947442326480121</v>
       </c>
       <c r="C46">
-        <v>53187.94161772134</v>
+        <v>53389.52377192429</v>
       </c>
       <c r="D46">
-        <v>86309.30961772134</v>
+        <v>86510.89177192429</v>
       </c>
       <c r="E46">
         <v>11527.368</v>
@@ -5065,37 +5065,37 @@
         <v>28995</v>
       </c>
       <c r="M46">
-        <v>2126.0781256</v>
+        <v>2068.5054104</v>
       </c>
       <c r="N46">
-        <v>26868.9218744</v>
+        <v>26926.4945896</v>
       </c>
       <c r="O46">
-        <v>5911.162812368</v>
+        <v>5923.828809711999</v>
       </c>
       <c r="P46">
-        <v>20957.759062032</v>
+        <v>21002.665779888</v>
       </c>
       <c r="Q46">
-        <v>30743.759062032</v>
+        <v>30788.665779888</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1111339025776305</v>
+        <v>0.111091898687145</v>
       </c>
       <c r="T46">
         <v>1.507896043583026</v>
       </c>
       <c r="U46">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V46">
         <v>0.22</v>
       </c>
       <c r="W46">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>13.63778670730518</v>
+        <v>14.0173672518425</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.0798345674541289</v>
+        <v>0.07931970257040066</v>
       </c>
       <c r="C47">
-        <v>52313.6573688885</v>
+        <v>52520.10412254229</v>
       </c>
       <c r="D47">
-        <v>86369.6473688885</v>
+        <v>86576.09412254229</v>
       </c>
       <c r="E47">
         <v>12461.99</v>
@@ -5147,37 +5147,37 @@
         <v>28995</v>
       </c>
       <c r="M47">
-        <v>2174.398083</v>
+        <v>2115.516897</v>
       </c>
       <c r="N47">
-        <v>26820.601917</v>
+        <v>26879.483103</v>
       </c>
       <c r="O47">
-        <v>5900.53242174</v>
+        <v>5913.48628266</v>
       </c>
       <c r="P47">
-        <v>20920.06949526</v>
+        <v>20965.99682034</v>
       </c>
       <c r="Q47">
-        <v>30706.06949526</v>
+        <v>30751.99682034</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1121597590075071</v>
+        <v>0.1121170955825466</v>
       </c>
       <c r="T47">
         <v>1.531572646248191</v>
       </c>
       <c r="U47">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V47">
         <v>0.22</v>
       </c>
       <c r="W47">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>13.33472478047618</v>
+        <v>13.70587020180156</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.07969070946478474</v>
+        <v>0.07916498187600013</v>
       </c>
       <c r="C48">
-        <v>51439.45754179745</v>
+        <v>51650.78283194612</v>
       </c>
       <c r="D48">
-        <v>86430.06954179745</v>
+        <v>86641.39483194612</v>
       </c>
       <c r="E48">
         <v>13396.612</v>
@@ -5229,37 +5229,37 @@
         <v>28995</v>
       </c>
       <c r="M48">
-        <v>2222.7180404</v>
+        <v>2162.5283836</v>
       </c>
       <c r="N48">
-        <v>26772.2819596</v>
+        <v>26832.4716164</v>
       </c>
       <c r="O48">
-        <v>5889.902031112</v>
+        <v>5903.143755608</v>
       </c>
       <c r="P48">
-        <v>20882.379928488</v>
+        <v>20929.327860792</v>
       </c>
       <c r="Q48">
-        <v>30668.379928488</v>
+        <v>30715.327860792</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1132236101199717</v>
+        <v>0.1131802627333336</v>
       </c>
       <c r="T48">
         <v>1.556126160123177</v>
       </c>
       <c r="U48">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V48">
         <v>0.22</v>
       </c>
       <c r="W48">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>13.04483945916148</v>
+        <v>13.4079165017624</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.07954685147544059</v>
+        <v>0.07901026118159961</v>
       </c>
       <c r="C49">
-        <v>50565.34231375058</v>
+        <v>50781.56012286747</v>
       </c>
       <c r="D49">
-        <v>86490.57631375059</v>
+        <v>86706.79412286748</v>
       </c>
       <c r="E49">
         <v>14331.234</v>
@@ -5311,37 +5311,37 @@
         <v>28995</v>
       </c>
       <c r="M49">
-        <v>2271.037997800001</v>
+        <v>2209.5398702</v>
       </c>
       <c r="N49">
-        <v>26723.9620022</v>
+        <v>26785.4601298</v>
       </c>
       <c r="O49">
-        <v>5879.271640483999</v>
+        <v>5892.801228556</v>
       </c>
       <c r="P49">
-        <v>20844.690361716</v>
+        <v>20892.658901244</v>
       </c>
       <c r="Q49">
-        <v>30630.690361716</v>
+        <v>30678.658901244</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1143276065574351</v>
+        <v>0.1142835493992445</v>
       </c>
       <c r="T49">
         <v>1.58160622169156</v>
       </c>
       <c r="U49">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V49">
         <v>0.22</v>
       </c>
       <c r="W49">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>12.76728968343464</v>
+        <v>13.12264168257596</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.07940299348609643</v>
+        <v>0.07885554048719906</v>
       </c>
       <c r="C50">
-        <v>49691.3118625472</v>
+        <v>49912.43621871108</v>
       </c>
       <c r="D50">
-        <v>86551.1678625472</v>
+        <v>86772.29221871108</v>
       </c>
       <c r="E50">
         <v>15265.856</v>
@@ -5393,37 +5393,37 @@
         <v>28995</v>
       </c>
       <c r="M50">
-        <v>2319.3579552</v>
+        <v>2256.5513568</v>
       </c>
       <c r="N50">
-        <v>26675.6420448</v>
+        <v>26738.4486432</v>
       </c>
       <c r="O50">
-        <v>5868.641249855999</v>
+        <v>5882.458701504001</v>
       </c>
       <c r="P50">
-        <v>20807.000794944</v>
+        <v>20855.989941696</v>
       </c>
       <c r="Q50">
-        <v>30593.000794944</v>
+        <v>30641.989941696</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1154740643963393</v>
+        <v>0.1154292701676905</v>
       </c>
       <c r="T50">
         <v>1.608066285627956</v>
       </c>
       <c r="U50">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V50">
         <v>0.22</v>
       </c>
       <c r="W50">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>12.50130448169642</v>
+        <v>12.84925331418897</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.07925913549675227</v>
+        <v>0.07870081979279853</v>
       </c>
       <c r="C51">
-        <v>48817.36636648516</v>
+        <v>49043.41134355713</v>
       </c>
       <c r="D51">
-        <v>86611.84436648515</v>
+        <v>86837.88934355712</v>
       </c>
       <c r="E51">
         <v>16200.478</v>
@@ -5475,37 +5475,37 @@
         <v>28995</v>
       </c>
       <c r="M51">
-        <v>2367.6779126</v>
+        <v>2303.5628434</v>
       </c>
       <c r="N51">
-        <v>26627.3220874</v>
+        <v>26691.4371566</v>
       </c>
       <c r="O51">
-        <v>5858.010859228</v>
+        <v>5872.116174452</v>
       </c>
       <c r="P51">
-        <v>20769.311228172</v>
+        <v>20819.320982148</v>
       </c>
       <c r="Q51">
-        <v>30555.311228172</v>
+        <v>30605.320982148</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1166654813661809</v>
+        <v>0.1166199211623501</v>
       </c>
       <c r="T51">
         <v>1.635563999130486</v>
       </c>
       <c r="U51">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V51">
         <v>0.22</v>
       </c>
       <c r="W51">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>12.24617581880465</v>
+        <v>12.58702365471572</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.07911527750740811</v>
+        <v>0.07854609909839799</v>
       </c>
       <c r="C52">
-        <v>47943.50600436265</v>
+        <v>48174.48572216402</v>
       </c>
       <c r="D52">
-        <v>86672.60600436265</v>
+        <v>86903.58572216402</v>
       </c>
       <c r="E52">
         <v>17135.1</v>
@@ -5557,37 +5557,37 @@
         <v>28995</v>
       </c>
       <c r="M52">
-        <v>2415.99787</v>
+        <v>2350.57433</v>
       </c>
       <c r="N52">
-        <v>26579.00213</v>
+        <v>26644.42567</v>
       </c>
       <c r="O52">
-        <v>5847.3804686</v>
+        <v>5861.7736474</v>
       </c>
       <c r="P52">
-        <v>20731.6216614</v>
+        <v>20782.6520226</v>
       </c>
       <c r="Q52">
-        <v>30517.6216614</v>
+        <v>30568.6520226</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1179045550148162</v>
+        <v>0.117858198196796</v>
       </c>
       <c r="T52">
         <v>1.664161621173118</v>
       </c>
       <c r="U52">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V52">
         <v>0.22</v>
       </c>
       <c r="W52">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>12.00125230242856</v>
+        <v>12.3352831816214</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.07897141951806397</v>
+        <v>0.07839137840399746</v>
       </c>
       <c r="C53">
-        <v>47069.73095547991</v>
+        <v>47305.65957997072</v>
       </c>
       <c r="D53">
-        <v>86733.45295547991</v>
+        <v>86969.38157997072</v>
       </c>
       <c r="E53">
         <v>18069.722</v>
@@ -5639,37 +5639,37 @@
         <v>28995</v>
       </c>
       <c r="M53">
-        <v>2464.3178274</v>
+        <v>2397.5858166</v>
       </c>
       <c r="N53">
-        <v>26530.6821726</v>
+        <v>26597.4141834</v>
       </c>
       <c r="O53">
-        <v>5836.750077971999</v>
+        <v>5851.431120348</v>
       </c>
       <c r="P53">
-        <v>20693.932094628</v>
+        <v>20745.983063052</v>
       </c>
       <c r="Q53">
-        <v>30479.932094628</v>
+        <v>30531.983063052</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1191942030980897</v>
+        <v>0.1191470171510152</v>
       </c>
       <c r="T53">
         <v>1.69392649309504</v>
       </c>
       <c r="U53">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V53">
         <v>0.22</v>
       </c>
       <c r="W53">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>11.76593362983192</v>
+        <v>12.09341488394255</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.07882756152871982</v>
+        <v>0.07823665770959692</v>
       </c>
       <c r="C54">
-        <v>46196.04139964108</v>
+        <v>46436.93314309954</v>
       </c>
       <c r="D54">
-        <v>86794.38539964108</v>
+        <v>87035.27714309953</v>
       </c>
       <c r="E54">
         <v>19004.344</v>
@@ -5721,37 +5721,37 @@
         <v>28995</v>
       </c>
       <c r="M54">
-        <v>2512.6377848</v>
+        <v>2444.5973032</v>
       </c>
       <c r="N54">
-        <v>26482.3622152</v>
+        <v>26550.4026968</v>
       </c>
       <c r="O54">
-        <v>5826.119687343999</v>
+        <v>5841.088593296</v>
       </c>
       <c r="P54">
-        <v>20656.242527856</v>
+        <v>20709.314103504</v>
       </c>
       <c r="Q54">
-        <v>30442.242527856</v>
+        <v>30495.314103504</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1205375865181663</v>
+        <v>0.1204895368949936</v>
       </c>
       <c r="T54">
         <v>1.724931568013709</v>
       </c>
       <c r="U54">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V54">
         <v>0.22</v>
       </c>
       <c r="W54">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>11.53966567541208</v>
+        <v>11.86084921309751</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.07868370353937565</v>
+        <v>0.07808193701519639</v>
       </c>
       <c r="C55">
-        <v>45322.43751715594</v>
+        <v>45568.30663835855</v>
       </c>
       <c r="D55">
-        <v>86855.40351715594</v>
+        <v>87101.27263835855</v>
       </c>
       <c r="E55">
         <v>19938.966</v>
@@ -5803,37 +5803,37 @@
         <v>28995</v>
       </c>
       <c r="M55">
-        <v>2560.9577422</v>
+        <v>2491.6087898</v>
       </c>
       <c r="N55">
-        <v>26434.0422578</v>
+        <v>26503.3912102</v>
       </c>
       <c r="O55">
-        <v>5815.489296716</v>
+        <v>5830.746066244</v>
       </c>
       <c r="P55">
-        <v>20618.552961084</v>
+        <v>20672.645143956</v>
       </c>
       <c r="Q55">
-        <v>30404.552961084</v>
+        <v>30458.645143956</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.121938135190161</v>
+        <v>0.1218891851387157</v>
       </c>
       <c r="T55">
         <v>1.757256007822534</v>
       </c>
       <c r="U55">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V55">
         <v>0.22</v>
       </c>
       <c r="W55">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>11.32193613436657</v>
+        <v>11.63705960530321</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.07853984555003149</v>
+        <v>0.07792721632079586</v>
       </c>
       <c r="C56">
-        <v>44448.9194888416</v>
+        <v>44699.78029324432</v>
       </c>
       <c r="D56">
-        <v>86916.5074888416</v>
+        <v>87167.36829324432</v>
       </c>
       <c r="E56">
         <v>20873.588</v>
@@ -5885,37 +5885,37 @@
         <v>28995</v>
       </c>
       <c r="M56">
-        <v>2609.2776996</v>
+        <v>2538.6202764</v>
       </c>
       <c r="N56">
-        <v>26385.7223004</v>
+        <v>26456.3797236</v>
       </c>
       <c r="O56">
-        <v>5804.858906088</v>
+        <v>5820.403539192</v>
       </c>
       <c r="P56">
-        <v>20580.863394312</v>
+        <v>20635.976184408</v>
       </c>
       <c r="Q56">
-        <v>30366.863394312</v>
+        <v>30421.976184408</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1233995772826772</v>
+        <v>0.1233496876539041</v>
       </c>
       <c r="T56">
         <v>1.79098585805783</v>
       </c>
       <c r="U56">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V56">
         <v>0.22</v>
       </c>
       <c r="W56">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>11.11227065039682</v>
+        <v>11.4215585015013</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.07839598756068734</v>
+        <v>0.07777249562639532</v>
       </c>
       <c r="C57">
-        <v>43575.48749602441</v>
+        <v>43831.35433594447</v>
       </c>
       <c r="D57">
-        <v>86977.69749602441</v>
+        <v>87233.56433594447</v>
       </c>
       <c r="E57">
         <v>21808.21</v>
@@ -5967,37 +5967,37 @@
         <v>28995</v>
       </c>
       <c r="M57">
-        <v>2657.597657</v>
+        <v>2585.631763</v>
       </c>
       <c r="N57">
-        <v>26337.402343</v>
+        <v>26409.368237</v>
       </c>
       <c r="O57">
-        <v>5794.22851546</v>
+        <v>5810.06101214</v>
       </c>
       <c r="P57">
-        <v>20543.17382754</v>
+        <v>20599.30722486</v>
       </c>
       <c r="Q57">
-        <v>30329.17382754</v>
+        <v>30385.30722486</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.124925972357083</v>
+        <v>0.1248751013919896</v>
       </c>
       <c r="T57">
         <v>1.826214812748028</v>
       </c>
       <c r="U57">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V57">
         <v>0.22</v>
       </c>
       <c r="W57">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>10.91022936584415</v>
+        <v>11.213893801474</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07825212957134318</v>
+        <v>0.07761777493199477</v>
       </c>
       <c r="C58">
-        <v>42702.14172054172</v>
+        <v>42963.02899534023</v>
       </c>
       <c r="D58">
-        <v>87038.97372054172</v>
+        <v>87299.86099534023</v>
       </c>
       <c r="E58">
         <v>22742.832</v>
@@ -6049,37 +6049,37 @@
         <v>28995</v>
       </c>
       <c r="M58">
-        <v>2705.9176144</v>
+        <v>2632.6432496</v>
       </c>
       <c r="N58">
-        <v>26289.0823856</v>
+        <v>26362.3567504</v>
       </c>
       <c r="O58">
-        <v>5783.598124831999</v>
+        <v>5799.718485088</v>
       </c>
       <c r="P58">
-        <v>20505.484260768</v>
+        <v>20562.638265312</v>
       </c>
       <c r="Q58">
-        <v>30291.484260768</v>
+        <v>30348.638265312</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.12652174902578</v>
+        <v>0.12646985211817</v>
       </c>
       <c r="T58">
         <v>1.863045083560508</v>
       </c>
       <c r="U58">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V58">
         <v>0.22</v>
       </c>
       <c r="W58">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>10.71540384145407</v>
+        <v>11.01364569787625</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07810827158199904</v>
+        <v>0.07746305423759425</v>
       </c>
       <c r="C59">
-        <v>41828.88234474358</v>
+        <v>42094.80450100924</v>
       </c>
       <c r="D59">
-        <v>87100.33634474358</v>
+        <v>87366.25850100924</v>
       </c>
       <c r="E59">
         <v>23677.45400000001</v>
@@ -6131,37 +6131,37 @@
         <v>28995</v>
       </c>
       <c r="M59">
-        <v>2754.2375718</v>
+        <v>2679.6547362</v>
       </c>
       <c r="N59">
-        <v>26240.7624282</v>
+        <v>26315.3452638</v>
       </c>
       <c r="O59">
-        <v>5772.967734204</v>
+        <v>5789.375958036</v>
       </c>
       <c r="P59">
-        <v>20467.794693996</v>
+        <v>20525.969305764</v>
       </c>
       <c r="Q59">
-        <v>30253.794693996</v>
+        <v>30311.969305764</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.128191747865114</v>
+        <v>0.1281387772967308</v>
       </c>
       <c r="T59">
         <v>1.901588390224731</v>
       </c>
       <c r="U59">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V59">
         <v>0.22</v>
       </c>
       <c r="W59">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>10.52741430037593</v>
+        <v>10.82042384352755</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.07796441359265488</v>
+        <v>0.07730833354319372</v>
       </c>
       <c r="C60">
-        <v>40955.70955149472</v>
+        <v>41226.6810832281</v>
       </c>
       <c r="D60">
-        <v>87161.78555149472</v>
+        <v>87432.75708322809</v>
       </c>
       <c r="E60">
         <v>24612.07599999999</v>
@@ -6213,37 +6213,37 @@
         <v>28995</v>
       </c>
       <c r="M60">
-        <v>2802.5575292</v>
+        <v>2726.6662228</v>
       </c>
       <c r="N60">
-        <v>26192.4424708</v>
+        <v>26268.3337772</v>
       </c>
       <c r="O60">
-        <v>5762.337343576</v>
+        <v>5779.033430984</v>
       </c>
       <c r="P60">
-        <v>20430.105127224</v>
+        <v>20489.300346216</v>
       </c>
       <c r="Q60">
-        <v>30216.105127224</v>
+        <v>30275.300346216</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1299412704587021</v>
+        <v>0.1298871751028422</v>
       </c>
       <c r="T60">
         <v>1.941967092444392</v>
       </c>
       <c r="U60">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V60">
         <v>0.22</v>
       </c>
       <c r="W60">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>10.345907157266</v>
+        <v>10.63386481174259</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.07782055560331072</v>
+        <v>0.07715361284879318</v>
       </c>
       <c r="C61">
-        <v>40082.62352417624</v>
+        <v>40358.65897297495</v>
       </c>
       <c r="D61">
-        <v>87223.32152417624</v>
+        <v>87499.35697297494</v>
       </c>
       <c r="E61">
         <v>25546.698</v>
@@ -6295,37 +6295,37 @@
         <v>28995</v>
       </c>
       <c r="M61">
-        <v>2850.8774866</v>
+        <v>2773.6777094</v>
       </c>
       <c r="N61">
-        <v>26144.1225134</v>
+        <v>26221.3222906</v>
       </c>
       <c r="O61">
-        <v>5751.706952948</v>
+        <v>5768.690903932</v>
       </c>
       <c r="P61">
-        <v>20392.415560452</v>
+        <v>20452.631386668</v>
       </c>
       <c r="Q61">
-        <v>30178.415560452</v>
+        <v>30238.631386668</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.131776135617831</v>
+        <v>0.1317208606068126</v>
       </c>
       <c r="T61">
         <v>1.984315487455257</v>
       </c>
       <c r="U61">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V61">
         <v>0.22</v>
       </c>
       <c r="W61">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>10.17055279866827</v>
+        <v>10.45362981493339</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.07767669761396657</v>
+        <v>0.07699889215439266</v>
       </c>
       <c r="C62">
-        <v>39209.62444668743</v>
+        <v>39490.73840193233</v>
       </c>
       <c r="D62">
-        <v>87284.94444668743</v>
+        <v>87566.05840193233</v>
       </c>
       <c r="E62">
         <v>26481.32</v>
@@ -6377,37 +6377,37 @@
         <v>28995</v>
       </c>
       <c r="M62">
-        <v>2899.197444</v>
+        <v>2820.689196</v>
       </c>
       <c r="N62">
-        <v>26095.802556</v>
+        <v>26174.310804</v>
       </c>
       <c r="O62">
-        <v>5741.07656232</v>
+        <v>5758.348376880001</v>
       </c>
       <c r="P62">
-        <v>20354.72599368</v>
+        <v>20415.96242712</v>
       </c>
       <c r="Q62">
-        <v>30140.72599368</v>
+        <v>30201.96242712</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1337027440349164</v>
+        <v>0.1336462303859816</v>
       </c>
       <c r="T62">
         <v>2.028781302216666</v>
       </c>
       <c r="U62">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V62">
         <v>0.22</v>
       </c>
       <c r="W62">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>10.00104358535713</v>
+        <v>10.27940265135117</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.0775328396246224</v>
+        <v>0.07684417145999212</v>
       </c>
       <c r="C63">
-        <v>38336.71250344774</v>
+        <v>38622.91960248977</v>
       </c>
       <c r="D63">
-        <v>87346.65450344773</v>
+        <v>87632.86160248976</v>
       </c>
       <c r="E63">
         <v>27415.942</v>
@@ -6459,37 +6459,37 @@
         <v>28995</v>
       </c>
       <c r="M63">
-        <v>2947.5174014</v>
+        <v>2867.7006826</v>
       </c>
       <c r="N63">
-        <v>26047.4825986</v>
+        <v>26127.2993174</v>
       </c>
       <c r="O63">
-        <v>5730.446171692</v>
+        <v>5748.005849828</v>
       </c>
       <c r="P63">
-        <v>20317.036426908</v>
+        <v>20379.293467572</v>
       </c>
       <c r="Q63">
-        <v>30103.036426908</v>
+        <v>30165.293467572</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1357281528836472</v>
+        <v>0.1356703370769028</v>
       </c>
       <c r="T63">
         <v>2.075527415170967</v>
       </c>
       <c r="U63">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V63">
         <v>0.22</v>
       </c>
       <c r="W63">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>9.837092051170952</v>
+        <v>10.11088785378804</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.07738898163527826</v>
+        <v>0.07668945076559158</v>
       </c>
       <c r="C64">
-        <v>37463.88787939843</v>
+        <v>37755.20280774641</v>
       </c>
       <c r="D64">
-        <v>87408.45187939843</v>
+        <v>87699.7668077464</v>
       </c>
       <c r="E64">
         <v>28350.564</v>
@@ -6541,37 +6541,37 @@
         <v>28995</v>
       </c>
       <c r="M64">
-        <v>2995.8373588</v>
+        <v>2914.7121692</v>
       </c>
       <c r="N64">
-        <v>25999.1626412</v>
+        <v>26080.2878308</v>
       </c>
       <c r="O64">
-        <v>5719.815781064</v>
+        <v>5737.663322776</v>
       </c>
       <c r="P64">
-        <v>20279.346860136</v>
+        <v>20342.624508024</v>
       </c>
       <c r="Q64">
-        <v>30065.346860136</v>
+        <v>30128.624508024</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1378601621981007</v>
+        <v>0.1378009756989252</v>
       </c>
       <c r="T64">
         <v>2.124733849859705</v>
       </c>
       <c r="U64">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V64">
         <v>0.22</v>
       </c>
       <c r="W64">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>9.678429276152066</v>
+        <v>9.947809017436617</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.07724512364593411</v>
+        <v>0.07653473007119105</v>
       </c>
       <c r="C65">
-        <v>36591.15076000456</v>
+        <v>36887.58825151388</v>
       </c>
       <c r="D65">
-        <v>87470.33676000456</v>
+        <v>87766.77425151388</v>
       </c>
       <c r="E65">
         <v>29285.186</v>
@@ -6623,37 +6623,37 @@
         <v>28995</v>
       </c>
       <c r="M65">
-        <v>3044.1573162</v>
+        <v>2961.7236558</v>
       </c>
       <c r="N65">
-        <v>25950.8426838</v>
+        <v>26033.2763442</v>
       </c>
       <c r="O65">
-        <v>5709.185390436</v>
+        <v>5727.320795724</v>
       </c>
       <c r="P65">
-        <v>20241.657293364</v>
+        <v>20305.955548476</v>
       </c>
       <c r="Q65">
-        <v>30027.657293364</v>
+        <v>30091.955548476</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1401074152592814</v>
+        <v>0.140046783976192</v>
       </c>
       <c r="T65">
         <v>2.176600091828915</v>
       </c>
       <c r="U65">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V65">
         <v>0.22</v>
       </c>
       <c r="W65">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>9.524803414625842</v>
+        <v>9.789907287001114</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.07710126565658995</v>
+        <v>0.07638000937679051</v>
       </c>
       <c r="C66">
-        <v>35718.50133125683</v>
+        <v>36020.0761683189</v>
       </c>
       <c r="D66">
-        <v>87532.30933125682</v>
+        <v>87833.88416831889</v>
       </c>
       <c r="E66">
         <v>30219.808</v>
@@ -6705,37 +6705,37 @@
         <v>28995</v>
       </c>
       <c r="M66">
-        <v>3092.4772736</v>
+        <v>3008.7351424</v>
       </c>
       <c r="N66">
-        <v>25902.5227264</v>
+        <v>25986.2648576</v>
       </c>
       <c r="O66">
-        <v>5698.554999808</v>
+        <v>5716.978268672</v>
       </c>
       <c r="P66">
-        <v>20203.967726592</v>
+        <v>20269.286588928</v>
       </c>
       <c r="Q66">
-        <v>29989.967726592</v>
+        <v>30055.286588928</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1424795157127499</v>
+        <v>0.1424173593799737</v>
       </c>
       <c r="T66">
         <v>2.231347791685304</v>
       </c>
       <c r="U66">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V66">
         <v>0.22</v>
       </c>
       <c r="W66">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>9.375978361272313</v>
+        <v>9.636939985641723</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.07695740766724579</v>
+        <v>0.07622528868238998</v>
       </c>
       <c r="C67">
-        <v>34845.9397796733</v>
+        <v>35152.66679340605</v>
       </c>
       <c r="D67">
-        <v>87594.3697796733</v>
+        <v>87901.09679340605</v>
       </c>
       <c r="E67">
         <v>31154.43</v>
@@ -6787,37 +6787,37 @@
         <v>28995</v>
       </c>
       <c r="M67">
-        <v>3140.797231</v>
+        <v>3055.746629</v>
       </c>
       <c r="N67">
-        <v>25854.202769</v>
+        <v>25939.253371</v>
       </c>
       <c r="O67">
-        <v>5687.92460918</v>
+        <v>5706.63574162</v>
       </c>
       <c r="P67">
-        <v>20166.27815982</v>
+        <v>20232.61762938</v>
       </c>
       <c r="Q67">
-        <v>29952.27815982</v>
+        <v>30018.61762938</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1449871647635594</v>
+        <v>0.1449233962354</v>
       </c>
       <c r="T67">
         <v>2.289223931533486</v>
       </c>
       <c r="U67">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V67">
         <v>0.22</v>
       </c>
       <c r="W67">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>9.231732540329663</v>
+        <v>9.488679370478003</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.07681354967790165</v>
+        <v>0.07607056798798945</v>
       </c>
       <c r="C68">
-        <v>33973.46629230149</v>
+        <v>34285.3603627405</v>
       </c>
       <c r="D68">
-        <v>87656.51829230149</v>
+        <v>87968.41236274051</v>
       </c>
       <c r="E68">
         <v>32089.052</v>
@@ -6869,37 +6869,37 @@
         <v>28995</v>
       </c>
       <c r="M68">
-        <v>3189.1171884</v>
+        <v>3102.7581156</v>
       </c>
       <c r="N68">
-        <v>25805.8828116</v>
+        <v>25892.2418844</v>
       </c>
       <c r="O68">
-        <v>5677.294218552001</v>
+        <v>5696.293214568</v>
       </c>
       <c r="P68">
-        <v>20128.588593048</v>
+        <v>20195.948669832</v>
       </c>
       <c r="Q68">
-        <v>29914.588593048</v>
+        <v>29981.948669832</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1476423225820637</v>
+        <v>0.1475768470234984</v>
       </c>
       <c r="T68">
         <v>2.350504550196268</v>
       </c>
       <c r="U68">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V68">
         <v>0.22</v>
       </c>
       <c r="W68">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>9.091857804870122</v>
+        <v>9.344911501228335</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.07666969168855749</v>
+        <v>0.0759158472935889</v>
       </c>
       <c r="C69">
-        <v>33101.08105672008</v>
+        <v>33418.15711301089</v>
       </c>
       <c r="D69">
-        <v>87718.75505672008</v>
+        <v>88035.83111301089</v>
       </c>
       <c r="E69">
         <v>33023.674</v>
@@ -6951,37 +6951,37 @@
         <v>28995</v>
       </c>
       <c r="M69">
-        <v>3237.4371458</v>
+        <v>3149.7696022</v>
       </c>
       <c r="N69">
-        <v>25757.5628542</v>
+        <v>25845.2303978</v>
       </c>
       <c r="O69">
-        <v>5666.663827924001</v>
+        <v>5685.950687516</v>
       </c>
       <c r="P69">
-        <v>20090.899026276</v>
+        <v>20159.279710284</v>
       </c>
       <c r="Q69">
-        <v>29876.899026276</v>
+        <v>29945.279710284</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1504583990562348</v>
+        <v>0.1503911130108755</v>
       </c>
       <c r="T69">
         <v>2.415499145747702</v>
       </c>
       <c r="U69">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V69">
         <v>0.22</v>
       </c>
       <c r="W69">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>8.956158434648181</v>
+        <v>9.205435210165227</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.07652583369921334</v>
+        <v>0.07576112659918838</v>
       </c>
       <c r="C70">
-        <v>32228.78426104083</v>
+        <v>32551.05728163185</v>
       </c>
       <c r="D70">
-        <v>87781.08026104083</v>
+        <v>88103.35328163185</v>
       </c>
       <c r="E70">
         <v>33958.296</v>
@@ -7033,37 +7033,37 @@
         <v>28995</v>
       </c>
       <c r="M70">
-        <v>3285.7571032</v>
+        <v>3196.7810888</v>
       </c>
       <c r="N70">
-        <v>25709.2428968</v>
+        <v>25798.2189112</v>
       </c>
       <c r="O70">
-        <v>5656.033437296</v>
+        <v>5675.608160464</v>
       </c>
       <c r="P70">
-        <v>20053.209459504</v>
+        <v>20122.610750736</v>
       </c>
       <c r="Q70">
-        <v>29839.209459504</v>
+        <v>29908.610750736</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1534504803100417</v>
+        <v>0.1533812706224637</v>
       </c>
       <c r="T70">
         <v>2.484555903521102</v>
       </c>
       <c r="U70">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V70">
         <v>0.22</v>
       </c>
       <c r="W70">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>8.82445022237394</v>
+        <v>9.070061162956915</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07638197570986917</v>
+        <v>0.07560640590478784</v>
       </c>
       <c r="C71">
-        <v>31356.5760939106</v>
+        <v>31684.06110674706</v>
       </c>
       <c r="D71">
-        <v>87843.4940939106</v>
+        <v>88170.97910674707</v>
       </c>
       <c r="E71">
         <v>34892.91800000001</v>
@@ -7115,37 +7115,37 @@
         <v>28995</v>
       </c>
       <c r="M71">
-        <v>3334.077060600001</v>
+        <v>3243.7925754</v>
       </c>
       <c r="N71">
-        <v>25660.9229394</v>
+        <v>25751.2074246</v>
       </c>
       <c r="O71">
-        <v>5645.403046668</v>
+        <v>5665.265633412</v>
       </c>
       <c r="P71">
-        <v>20015.519892732</v>
+        <v>20085.941791188</v>
       </c>
       <c r="Q71">
-        <v>29801.519892732</v>
+        <v>29871.941791188</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1566355990640941</v>
+        <v>0.1565643416283479</v>
       </c>
       <c r="T71">
         <v>2.558067935989559</v>
       </c>
       <c r="U71">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V71">
         <v>0.22</v>
       </c>
       <c r="W71">
-        <v>0.040326</v>
+        <v>0.039234</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>8.696559639440984</v>
+        <v>8.93861100117493</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07683871772052502</v>
+        <v>0.0754516852103873</v>
       </c>
       <c r="C72">
-        <v>30224.09900831422</v>
+        <v>30817.16882723194</v>
       </c>
       <c r="D72">
-        <v>87645.63900831422</v>
+        <v>88238.70882723194</v>
       </c>
       <c r="E72">
         <v>35827.54</v>
@@ -7197,45 +7197,45 @@
         <v>28995</v>
       </c>
       <c r="M72">
-        <v>3454.362912</v>
+        <v>3290.804062</v>
       </c>
       <c r="N72">
-        <v>25540.637088</v>
+        <v>25704.195938</v>
       </c>
       <c r="O72">
-        <v>5618.94015936</v>
+        <v>5654.92310636</v>
       </c>
       <c r="P72">
-        <v>19921.69692864</v>
+        <v>20049.27283164</v>
       </c>
       <c r="Q72">
-        <v>29707.69692864</v>
+        <v>29835.27283164</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1600330590684167</v>
+        <v>0.1599596173679577</v>
       </c>
       <c r="T72">
         <v>2.63648077062258</v>
       </c>
       <c r="U72">
-        <v>0.0528</v>
+        <v>0.0503</v>
       </c>
       <c r="V72">
         <v>0.22</v>
       </c>
       <c r="W72">
-        <v>0.041184</v>
+        <v>0.039234</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>Aaa/AAA</t>
         </is>
       </c>
       <c r="Y72">
-        <v>8.393733009139023</v>
+        <v>8.810916558301003</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.07670343973118086</v>
+        <v>0.07612766451598678</v>
       </c>
       <c r="C73">
-        <v>29347.98482931319</v>
+        <v>29587.39691979749</v>
       </c>
       <c r="D73">
-        <v>87704.14682931319</v>
+        <v>87943.55891979749</v>
       </c>
       <c r="E73">
         <v>36762.162</v>
@@ -7279,37 +7279,37 @@
         <v>28995</v>
       </c>
       <c r="M73">
-        <v>3503.7109536</v>
+        <v>3437.3527916</v>
       </c>
       <c r="N73">
-        <v>25491.2890464</v>
+        <v>25557.6472084</v>
       </c>
       <c r="O73">
-        <v>5608.083590208001</v>
+        <v>5622.682385848</v>
       </c>
       <c r="P73">
-        <v>19883.205456192</v>
+        <v>19934.964822552</v>
       </c>
       <c r="Q73">
-        <v>29669.205456192</v>
+        <v>29720.964822552</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1636648266592443</v>
+        <v>0.1635890500551268</v>
       </c>
       <c r="T73">
         <v>2.720301386954429</v>
       </c>
       <c r="U73">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V73">
         <v>0.22</v>
       </c>
       <c r="W73">
-        <v>0.041184</v>
+        <v>0.040404</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>8.27551141746101</v>
+        <v>8.435270325134002</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.07656816174183671</v>
+        <v>0.07598464382158623</v>
       </c>
       <c r="C74">
-        <v>28471.94881624982</v>
+        <v>28715.05662349581</v>
       </c>
       <c r="D74">
-        <v>87762.73281624982</v>
+        <v>88005.84062349581</v>
       </c>
       <c r="E74">
         <v>37696.784</v>
@@ -7361,37 +7361,37 @@
         <v>28995</v>
       </c>
       <c r="M74">
-        <v>3553.0589952</v>
+        <v>3485.7662112</v>
       </c>
       <c r="N74">
-        <v>25441.9410048</v>
+        <v>25509.2337888</v>
       </c>
       <c r="O74">
-        <v>5597.227021056</v>
+        <v>5612.031433536</v>
       </c>
       <c r="P74">
-        <v>19844.713983744</v>
+        <v>19897.202355264</v>
       </c>
       <c r="Q74">
-        <v>29630.713983744</v>
+        <v>29683.202355264</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1675560062208454</v>
+        <v>0.1674777279342366</v>
       </c>
       <c r="T74">
         <v>2.810109190167126</v>
       </c>
       <c r="U74">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V74">
         <v>0.22</v>
       </c>
       <c r="W74">
-        <v>0.041184</v>
+        <v>0.040404</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>8.16057375888516</v>
+        <v>8.318113792840474</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.07643288375249255</v>
+        <v>0.0758416231271857</v>
       </c>
       <c r="C75">
-        <v>27595.9911258723</v>
+        <v>27842.80460562473</v>
       </c>
       <c r="D75">
-        <v>87821.3971258723</v>
+        <v>88068.21060562473</v>
       </c>
       <c r="E75">
         <v>38631.406</v>
@@ -7443,37 +7443,37 @@
         <v>28995</v>
       </c>
       <c r="M75">
-        <v>3602.4070368</v>
+        <v>3534.1796308</v>
       </c>
       <c r="N75">
-        <v>25392.5929632</v>
+        <v>25460.8203692</v>
       </c>
       <c r="O75">
-        <v>5586.370451904</v>
+        <v>5601.380481224</v>
       </c>
       <c r="P75">
-        <v>19806.222511296</v>
+        <v>19859.439887976</v>
       </c>
       <c r="Q75">
-        <v>29592.222511296</v>
+        <v>29645.439887976</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.171735421305528</v>
+        <v>0.1716544560266137</v>
       </c>
       <c r="T75">
         <v>2.90656942324743</v>
       </c>
       <c r="U75">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V75">
         <v>0.22</v>
       </c>
       <c r="W75">
-        <v>0.041184</v>
+        <v>0.040404</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>8.048785077256596</v>
+        <v>8.204167028554988</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.07629760576314841</v>
+        <v>0.07569860243278517</v>
       </c>
       <c r="C76">
-        <v>26720.11191534832</v>
+        <v>26970.64105400686</v>
       </c>
       <c r="D76">
-        <v>87880.13991534831</v>
+        <v>88130.66905400685</v>
       </c>
       <c r="E76">
         <v>39566.02799999999</v>
@@ -7525,37 +7525,37 @@
         <v>28995</v>
       </c>
       <c r="M76">
-        <v>3651.7550784</v>
+        <v>3582.593050399999</v>
       </c>
       <c r="N76">
-        <v>25343.2449216</v>
+        <v>25412.4069496</v>
       </c>
       <c r="O76">
-        <v>5575.513882752</v>
+        <v>5590.729528912</v>
       </c>
       <c r="P76">
-        <v>19767.731038848</v>
+        <v>19821.677420688</v>
       </c>
       <c r="Q76">
-        <v>29553.731038848</v>
+        <v>29607.677420688</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1762363298582631</v>
+        <v>0.1761524708953276</v>
       </c>
       <c r="T76">
         <v>3.010449674256988</v>
       </c>
       <c r="U76">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V76">
         <v>0.22</v>
       </c>
       <c r="W76">
-        <v>0.041184</v>
+        <v>0.040404</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>7.940017711347727</v>
+        <v>8.09329990654749</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.07616232777380424</v>
+        <v>0.07555558173838464</v>
       </c>
       <c r="C77">
-        <v>25844.31134226618</v>
+        <v>26098.56615699799</v>
       </c>
       <c r="D77">
-        <v>87938.96134226618</v>
+        <v>88193.21615699798</v>
       </c>
       <c r="E77">
         <v>40500.64999999999</v>
@@ -7607,37 +7607,37 @@
         <v>28995</v>
       </c>
       <c r="M77">
-        <v>3701.10312</v>
+        <v>3631.00647</v>
       </c>
       <c r="N77">
-        <v>25293.89688</v>
+        <v>25363.99353</v>
       </c>
       <c r="O77">
-        <v>5564.6573136</v>
+        <v>5580.0785766</v>
       </c>
       <c r="P77">
-        <v>19729.2395664</v>
+        <v>19783.9149534</v>
       </c>
       <c r="Q77">
-        <v>29515.2395664</v>
+        <v>29569.9149534</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.181097311095217</v>
+        <v>0.1810103269535386</v>
       </c>
       <c r="T77">
         <v>3.12264034534731</v>
       </c>
       <c r="U77">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V77">
         <v>0.22</v>
       </c>
       <c r="W77">
-        <v>0.041184</v>
+        <v>0.040404</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>7.834150808529756</v>
+        <v>7.985389241126855</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.07602704978446009</v>
+        <v>0.07541256104398411</v>
       </c>
       <c r="C78">
-        <v>24968.58956463658</v>
+        <v>25226.58010348903</v>
       </c>
       <c r="D78">
-        <v>87997.86156463658</v>
+        <v>88255.85210348903</v>
       </c>
       <c r="E78">
         <v>41435.272</v>
@@ -7689,37 +7689,37 @@
         <v>28995</v>
       </c>
       <c r="M78">
-        <v>3750.4511616</v>
+        <v>3679.4198896</v>
       </c>
       <c r="N78">
-        <v>25244.5488384</v>
+        <v>25315.5801104</v>
       </c>
       <c r="O78">
-        <v>5553.800744448</v>
+        <v>5569.427624288</v>
       </c>
       <c r="P78">
-        <v>19690.748093952</v>
+        <v>19746.152486112</v>
       </c>
       <c r="Q78">
-        <v>29476.748093952</v>
+        <v>29532.152486112</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1863633741019171</v>
+        <v>0.1862730043499338</v>
       </c>
       <c r="T78">
         <v>3.244180239028494</v>
       </c>
       <c r="U78">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V78">
         <v>0.22</v>
       </c>
       <c r="W78">
-        <v>0.041184</v>
+        <v>0.040404</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>7.731069876838574</v>
+        <v>7.880318330059396</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.07589177179511594</v>
+        <v>0.07526954034958357</v>
       </c>
       <c r="C79">
-        <v>24092.94674089368</v>
+        <v>24354.68308290788</v>
       </c>
       <c r="D79">
-        <v>88056.84074089368</v>
+        <v>88318.57708290788</v>
       </c>
       <c r="E79">
         <v>42369.894</v>
@@ -7771,37 +7771,37 @@
         <v>28995</v>
       </c>
       <c r="M79">
-        <v>3799.7992032</v>
+        <v>3727.8333092</v>
       </c>
       <c r="N79">
-        <v>25195.2007968</v>
+        <v>25267.1666908</v>
       </c>
       <c r="O79">
-        <v>5542.944175296</v>
+        <v>5558.776671976</v>
       </c>
       <c r="P79">
-        <v>19652.256621504</v>
+        <v>19708.390018824</v>
       </c>
       <c r="Q79">
-        <v>29438.256621504</v>
+        <v>29494.390018824</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1920873556309389</v>
+        <v>0.1919933058677546</v>
       </c>
       <c r="T79">
         <v>3.376288819116736</v>
       </c>
       <c r="U79">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V79">
         <v>0.22</v>
       </c>
       <c r="W79">
-        <v>0.041184</v>
+        <v>0.040404</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>7.630666371944566</v>
+        <v>7.777976533565119</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.07575649380577179</v>
+        <v>0.07512651965518302</v>
       </c>
       <c r="C80">
-        <v>23217.38302989677</v>
+        <v>23482.87528522134</v>
       </c>
       <c r="D80">
-        <v>88115.89902989677</v>
+        <v>88381.39128522134</v>
       </c>
       <c r="E80">
         <v>43304.516</v>
@@ -7853,37 +7853,37 @@
         <v>28995</v>
       </c>
       <c r="M80">
-        <v>3849.1472448</v>
+        <v>3776.2467288</v>
       </c>
       <c r="N80">
-        <v>25145.8527552</v>
+        <v>25218.7532712</v>
       </c>
       <c r="O80">
-        <v>5532.087606144</v>
+        <v>5548.125719664</v>
       </c>
       <c r="P80">
-        <v>19613.765149056</v>
+        <v>19670.627551536</v>
       </c>
       <c r="Q80">
-        <v>29399.765149056</v>
+        <v>29456.627551536</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1983316991171445</v>
+        <v>0.1982336347962865</v>
       </c>
       <c r="T80">
         <v>3.520407270122091</v>
       </c>
       <c r="U80">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V80">
         <v>0.22</v>
       </c>
       <c r="W80">
-        <v>0.041184</v>
+        <v>0.040404</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>7.532837315893996</v>
+        <v>7.678258885698898</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.07562121581642763</v>
+        <v>0.07498349896078249</v>
       </c>
       <c r="C81">
-        <v>22341.89859093154</v>
+        <v>22611.15690093703</v>
       </c>
       <c r="D81">
-        <v>88175.03659093154</v>
+        <v>88444.29490093703</v>
       </c>
       <c r="E81">
         <v>44239.13800000001</v>
@@ -7935,37 +7935,37 @@
         <v>28995</v>
       </c>
       <c r="M81">
-        <v>3898.4952864</v>
+        <v>3824.6601484</v>
       </c>
       <c r="N81">
-        <v>25096.5047136</v>
+        <v>25170.3398516</v>
       </c>
       <c r="O81">
-        <v>5521.231036992</v>
+        <v>5537.474767352001</v>
       </c>
       <c r="P81">
-        <v>19575.273676608</v>
+        <v>19632.865084248</v>
       </c>
       <c r="Q81">
-        <v>29361.273676608</v>
+        <v>29418.865084248</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2051707419829887</v>
+        <v>0.205068280765631</v>
       </c>
       <c r="T81">
         <v>3.678251287889861</v>
       </c>
       <c r="U81">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V81">
         <v>0.22</v>
       </c>
       <c r="W81">
-        <v>0.041184</v>
+        <v>0.040404</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>7.437484944806729</v>
+        <v>7.581065735247014</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.07548593782708347</v>
+        <v>0.07484047826638196</v>
       </c>
       <c r="C82">
-        <v>21466.49358371165</v>
+        <v>21739.52812110529</v>
       </c>
       <c r="D82">
-        <v>88234.25358371164</v>
+        <v>88507.28812110529</v>
       </c>
       <c r="E82">
         <v>45173.75999999999</v>
@@ -8017,37 +8017,37 @@
         <v>28995</v>
       </c>
       <c r="M82">
-        <v>3947.843328</v>
+        <v>3873.073568</v>
       </c>
       <c r="N82">
-        <v>25047.156672</v>
+        <v>25121.926432</v>
       </c>
       <c r="O82">
-        <v>5510.37446784</v>
+        <v>5526.82381504</v>
       </c>
       <c r="P82">
-        <v>19536.78220416</v>
+        <v>19595.10261696</v>
       </c>
       <c r="Q82">
-        <v>29322.78220416</v>
+        <v>29381.10261696</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2126936891354174</v>
+        <v>0.2125863913319098</v>
       </c>
       <c r="T82">
         <v>3.851879707434408</v>
       </c>
       <c r="U82">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V82">
         <v>0.22</v>
       </c>
       <c r="W82">
-        <v>0.041184</v>
+        <v>0.040404</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>7.344516382996646</v>
+        <v>7.486302413556427</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07535065983773931</v>
+        <v>0.07469745757198143</v>
       </c>
       <c r="C83">
-        <v>20591.16816838</v>
+        <v>20867.98913732117</v>
       </c>
       <c r="D83">
-        <v>88293.55016838</v>
+        <v>88570.37113732117</v>
       </c>
       <c r="E83">
         <v>46108.382</v>
@@ -8099,37 +8099,37 @@
         <v>28995</v>
       </c>
       <c r="M83">
-        <v>3997.1913696</v>
+        <v>3921.4869876</v>
       </c>
       <c r="N83">
-        <v>24997.8086304</v>
+        <v>25073.5130124</v>
       </c>
       <c r="O83">
-        <v>5499.517898688</v>
+        <v>5516.172862728</v>
       </c>
       <c r="P83">
-        <v>19498.290731712</v>
+        <v>19557.340149672</v>
       </c>
       <c r="Q83">
-        <v>29284.290731712</v>
+        <v>29343.340149672</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2210085254617859</v>
+        <v>0.2208958819577971</v>
       </c>
       <c r="T83">
         <v>4.043784802720486</v>
       </c>
       <c r="U83">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V83">
         <v>0.22</v>
       </c>
       <c r="W83">
-        <v>0.041184</v>
+        <v>0.040404</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>7.253843341231256</v>
+        <v>7.39387892696931</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.07521538184839516</v>
+        <v>0.0745544368775809</v>
       </c>
       <c r="C84">
-        <v>19715.92250551037</v>
+        <v>19996.54014172632</v>
       </c>
       <c r="D84">
-        <v>88352.92650551038</v>
+        <v>88633.54414172632</v>
       </c>
       <c r="E84">
         <v>47043.004</v>
@@ -8181,37 +8181,37 @@
         <v>28995</v>
       </c>
       <c r="M84">
-        <v>4046.5394112</v>
+        <v>3969.9004072</v>
       </c>
       <c r="N84">
-        <v>24948.4605888</v>
+        <v>25025.0995928</v>
       </c>
       <c r="O84">
-        <v>5488.661329536</v>
+        <v>5505.521910416001</v>
       </c>
       <c r="P84">
-        <v>19459.799259264</v>
+        <v>19519.577682384</v>
       </c>
       <c r="Q84">
-        <v>29245.799259264</v>
+        <v>29305.577682384</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2302472324910843</v>
+        <v>0.2301286493198939</v>
       </c>
       <c r="T84">
         <v>4.257012686371684</v>
       </c>
       <c r="U84">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V84">
         <v>0.22</v>
       </c>
       <c r="W84">
-        <v>0.041184</v>
+        <v>0.040404</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>7.165381837069899</v>
+        <v>7.303709671762368</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.07508010385905101</v>
+        <v>0.07441141618318037</v>
       </c>
       <c r="C85">
-        <v>18840.75675610865</v>
+        <v>19125.18132701099</v>
       </c>
       <c r="D85">
-        <v>88412.38275610865</v>
+        <v>88696.80732701099</v>
       </c>
       <c r="E85">
         <v>47977.626</v>
@@ -8263,37 +8263,37 @@
         <v>28995</v>
       </c>
       <c r="M85">
-        <v>4095.8874528</v>
+        <v>4018.3138268</v>
       </c>
       <c r="N85">
-        <v>24899.1125472</v>
+        <v>24976.6861732</v>
       </c>
       <c r="O85">
-        <v>5477.804760384</v>
+        <v>5494.870958104</v>
       </c>
       <c r="P85">
-        <v>19421.307786816</v>
+        <v>19481.815215096</v>
       </c>
       <c r="Q85">
-        <v>29207.307786816</v>
+        <v>29267.815215096</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2405728462297119</v>
+        <v>0.2404476246069434</v>
       </c>
       <c r="T85">
         <v>4.495326203393612</v>
       </c>
       <c r="U85">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V85">
         <v>0.22</v>
       </c>
       <c r="W85">
-        <v>0.041184</v>
+        <v>0.040404</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>7.079051935418453</v>
+        <v>7.215713169692941</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.07494482586970685</v>
+        <v>0.07426839548877984</v>
       </c>
       <c r="C86">
-        <v>17965.67108161455</v>
+        <v>18253.91288641596</v>
       </c>
       <c r="D86">
-        <v>88471.91908161454</v>
+        <v>88760.16088641595</v>
       </c>
       <c r="E86">
         <v>48912.24799999999</v>
@@ -8345,37 +8345,37 @@
         <v>28995</v>
       </c>
       <c r="M86">
-        <v>4145.2354944</v>
+        <v>4066.727246399999</v>
       </c>
       <c r="N86">
-        <v>24849.7645056</v>
+        <v>24928.2727536</v>
       </c>
       <c r="O86">
-        <v>5466.948191232</v>
+        <v>5484.220005792001</v>
       </c>
       <c r="P86">
-        <v>19382.816314368</v>
+        <v>19444.052747808</v>
       </c>
       <c r="Q86">
-        <v>29168.816314368</v>
+        <v>29230.052747808</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2521891616856678</v>
+        <v>0.2520564718048739</v>
       </c>
       <c r="T86">
         <v>4.763428910043277</v>
       </c>
       <c r="U86">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V86">
         <v>0.22</v>
       </c>
       <c r="W86">
-        <v>0.041184</v>
+        <v>0.040404</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>6.994777507615853</v>
+        <v>7.129811822434693</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.0748095478803627</v>
+        <v>0.07412537479437931</v>
       </c>
       <c r="C87">
-        <v>17090.66564390277</v>
+        <v>17382.73501373448</v>
       </c>
       <c r="D87">
-        <v>88531.53564390277</v>
+        <v>88823.60501373447</v>
       </c>
       <c r="E87">
         <v>49846.87</v>
@@ -8427,37 +8427,37 @@
         <v>28995</v>
       </c>
       <c r="M87">
-        <v>4194.583536</v>
+        <v>4115.140665999999</v>
       </c>
       <c r="N87">
-        <v>24800.416464</v>
+        <v>24879.859334</v>
       </c>
       <c r="O87">
-        <v>5456.09162208</v>
+        <v>5473.569053480001</v>
       </c>
       <c r="P87">
-        <v>19344.32484192</v>
+        <v>19406.29028052</v>
       </c>
       <c r="Q87">
-        <v>29130.32484192</v>
+        <v>29192.29028052</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.265354319202418</v>
+        <v>0.2652131652958619</v>
       </c>
       <c r="T87">
         <v>5.067278644246234</v>
       </c>
       <c r="U87">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V87">
         <v>0.22</v>
       </c>
       <c r="W87">
-        <v>0.041184</v>
+        <v>0.040404</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>6.912486007526255</v>
+        <v>7.045931683347226</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.07467426989101852</v>
+        <v>0.07398235409997876</v>
       </c>
       <c r="C88">
-        <v>16215.74060528475</v>
+        <v>16511.64790331427</v>
       </c>
       <c r="D88">
-        <v>88591.23260528475</v>
+        <v>88887.13990331427</v>
       </c>
       <c r="E88">
         <v>50781.492</v>
@@ -8509,37 +8509,37 @@
         <v>28995</v>
       </c>
       <c r="M88">
-        <v>4243.9315776</v>
+        <v>4163.5540856</v>
       </c>
       <c r="N88">
-        <v>24751.0684224</v>
+        <v>24831.4459144</v>
       </c>
       <c r="O88">
-        <v>5445.235052928</v>
+        <v>5462.918101168</v>
       </c>
       <c r="P88">
-        <v>19305.833369472</v>
+        <v>19368.527813232</v>
       </c>
       <c r="Q88">
-        <v>29091.833369472</v>
+        <v>29154.527813232</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2804002135072752</v>
+        <v>0.2802493864284197</v>
       </c>
       <c r="T88">
         <v>5.414535483335327</v>
       </c>
       <c r="U88">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V88">
         <v>0.22</v>
       </c>
       <c r="W88">
-        <v>0.041184</v>
+        <v>0.040404</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>6.832108263252693</v>
+        <v>6.964002245168769</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.07603191190167438</v>
+        <v>0.07383933340557822</v>
       </c>
       <c r="C89">
-        <v>14685.62922520132</v>
+        <v>15640.65175005957</v>
       </c>
       <c r="D89">
-        <v>87995.74322520132</v>
+        <v>88950.76575005957</v>
       </c>
       <c r="E89">
         <v>51716.114</v>
@@ -8591,45 +8591,45 @@
         <v>28995</v>
       </c>
       <c r="M89">
-        <v>4472.16627</v>
+        <v>4211.9675052</v>
       </c>
       <c r="N89">
-        <v>24522.83373</v>
+        <v>24783.0324948</v>
       </c>
       <c r="O89">
-        <v>5395.0234206</v>
+        <v>5452.267148856</v>
       </c>
       <c r="P89">
-        <v>19127.8103094</v>
+        <v>19330.765345944</v>
       </c>
       <c r="Q89">
-        <v>28913.8103094</v>
+        <v>29116.765345944</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2977608607821107</v>
+        <v>0.2975988723506017</v>
       </c>
       <c r="T89">
         <v>5.815216451515052</v>
       </c>
       <c r="U89">
-        <v>0.055</v>
+        <v>0.0518</v>
       </c>
       <c r="V89">
         <v>0.22</v>
       </c>
       <c r="W89">
-        <v>0.0429</v>
+        <v>0.040404</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y89">
-        <v>6.483435151886694</v>
+        <v>6.883956242350736</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.07591379391233025</v>
+        <v>0.07369631271117769</v>
       </c>
       <c r="C90">
-        <v>13802.4980408266</v>
+        <v>14769.74674943302</v>
       </c>
       <c r="D90">
-        <v>88047.2340408266</v>
+        <v>89014.48274943302</v>
       </c>
       <c r="E90">
         <v>52650.736</v>
@@ -8673,45 +8673,45 @@
         <v>28995</v>
       </c>
       <c r="M90">
-        <v>4523.57048</v>
+        <v>4260.3809248</v>
       </c>
       <c r="N90">
-        <v>24471.42952</v>
+        <v>24734.6190752</v>
       </c>
       <c r="O90">
-        <v>5383.714494399999</v>
+        <v>5441.616196544</v>
       </c>
       <c r="P90">
-        <v>19087.7150256</v>
+        <v>19293.002878656</v>
       </c>
       <c r="Q90">
-        <v>28873.7150256</v>
+        <v>29079.002878656</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3180149492694186</v>
+        <v>0.3178399392598141</v>
       </c>
       <c r="T90">
         <v>6.282677581058063</v>
       </c>
       <c r="U90">
-        <v>0.055</v>
+        <v>0.0518</v>
       </c>
       <c r="V90">
         <v>0.22</v>
       </c>
       <c r="W90">
-        <v>0.0429</v>
+        <v>0.040404</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y90">
-        <v>6.409759752433435</v>
+        <v>6.805729466869479</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.07579567592298608</v>
+        <v>0.07355329201677716</v>
       </c>
       <c r="C91">
-        <v>12919.42715155981</v>
+        <v>13898.93309745775</v>
       </c>
       <c r="D91">
-        <v>88098.7851515598</v>
+        <v>89078.29109745774</v>
       </c>
       <c r="E91">
         <v>53585.35799999999</v>
@@ -8755,45 +8755,45 @@
         <v>28995</v>
       </c>
       <c r="M91">
-        <v>4574.97469</v>
+        <v>4308.794344399999</v>
       </c>
       <c r="N91">
-        <v>24420.02531</v>
+        <v>24686.2056556</v>
       </c>
       <c r="O91">
-        <v>5372.4055682</v>
+        <v>5430.965244232</v>
       </c>
       <c r="P91">
-        <v>19047.6197418</v>
+        <v>19255.240411368</v>
       </c>
       <c r="Q91">
-        <v>28833.6197418</v>
+        <v>29041.240411368</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3419515992998735</v>
+        <v>0.3417612001525196</v>
       </c>
       <c r="T91">
         <v>6.835131643245257</v>
       </c>
       <c r="U91">
-        <v>0.055</v>
+        <v>0.0518</v>
       </c>
       <c r="V91">
         <v>0.22</v>
       </c>
       <c r="W91">
-        <v>0.0429</v>
+        <v>0.040404</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y91">
-        <v>6.337739979934184</v>
+        <v>6.729260596455216</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.07567755793364192</v>
+        <v>0.07460367132237662</v>
       </c>
       <c r="C92">
-        <v>12036.41666337017</v>
+        <v>12497.80685555839</v>
       </c>
       <c r="D92">
-        <v>88150.39666337016</v>
+        <v>88611.78685555838</v>
       </c>
       <c r="E92">
         <v>54519.98</v>
@@ -8837,37 +8837,37 @@
         <v>28995</v>
       </c>
       <c r="M92">
-        <v>4626.3789</v>
+        <v>4500.20493</v>
       </c>
       <c r="N92">
-        <v>24368.6211</v>
+        <v>24494.79507</v>
       </c>
       <c r="O92">
-        <v>5361.096642</v>
+        <v>5388.8549154</v>
       </c>
       <c r="P92">
-        <v>19007.524458</v>
+        <v>19105.9401546</v>
       </c>
       <c r="Q92">
-        <v>28793.524458</v>
+        <v>28891.9401546</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.3706755793364193</v>
+        <v>0.3704667132237662</v>
       </c>
       <c r="T92">
         <v>7.49807651786989</v>
       </c>
       <c r="U92">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V92">
         <v>0.22</v>
       </c>
       <c r="W92">
-        <v>0.0429</v>
+        <v>0.04173</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>6.267320646823805</v>
+        <v>6.4430399172955</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.07555943994429778</v>
+        <v>0.07447391062797609</v>
       </c>
       <c r="C93">
-        <v>11153.46668247542</v>
+        <v>11620.55068573273</v>
       </c>
       <c r="D93">
-        <v>88202.06868247542</v>
+        <v>88669.15268573273</v>
       </c>
       <c r="E93">
         <v>55454.602</v>
@@ -8919,37 +8919,37 @@
         <v>28995</v>
       </c>
       <c r="M93">
-        <v>4677.78311</v>
+        <v>4550.207206999999</v>
       </c>
       <c r="N93">
-        <v>24317.21689</v>
+        <v>24444.792793</v>
       </c>
       <c r="O93">
-        <v>5349.7877158</v>
+        <v>5377.85441446</v>
       </c>
       <c r="P93">
-        <v>18967.4291742</v>
+        <v>19066.93837854</v>
       </c>
       <c r="Q93">
-        <v>28753.4291742</v>
+        <v>28852.93837854</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4057826660477531</v>
+        <v>0.4055512291997344</v>
       </c>
       <c r="T93">
         <v>8.308342475744444</v>
       </c>
       <c r="U93">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V93">
         <v>0.22</v>
       </c>
       <c r="W93">
-        <v>0.0429</v>
+        <v>0.04173</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>6.198448991364201</v>
+        <v>6.372237280841704</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.07544132195495362</v>
+        <v>0.07434414993357555</v>
       </c>
       <c r="C94">
-        <v>10270.57731534258</v>
+        <v>10743.36883943455</v>
       </c>
       <c r="D94">
-        <v>88253.80131534259</v>
+        <v>88726.59283943455</v>
       </c>
       <c r="E94">
         <v>56389.224</v>
@@ -9001,37 +9001,37 @@
         <v>28995</v>
       </c>
       <c r="M94">
-        <v>4729.18732</v>
+        <v>4600.209484</v>
       </c>
       <c r="N94">
-        <v>24265.81268</v>
+        <v>24394.790516</v>
       </c>
       <c r="O94">
-        <v>5338.4787896</v>
+        <v>5366.85391352</v>
       </c>
       <c r="P94">
-        <v>18927.3338904</v>
+        <v>19027.93660248</v>
       </c>
       <c r="Q94">
-        <v>28713.3338904</v>
+        <v>28813.93660248</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.4496665244369204</v>
+        <v>0.4494068741696946</v>
       </c>
       <c r="T94">
         <v>9.321174923087636</v>
       </c>
       <c r="U94">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V94">
         <v>0.22</v>
       </c>
       <c r="W94">
-        <v>0.0429</v>
+        <v>0.04173</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>6.131074545805896</v>
+        <v>6.302973832136902</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.07532320396560946</v>
+        <v>0.07421438923917503</v>
       </c>
       <c r="C95">
-        <v>9387.74866868848</v>
+        <v>9866.261461198505</v>
       </c>
       <c r="D95">
-        <v>88305.59466868849</v>
+        <v>88784.10746119851</v>
       </c>
       <c r="E95">
         <v>57323.84600000001</v>
@@ -9083,37 +9083,37 @@
         <v>28995</v>
       </c>
       <c r="M95">
-        <v>4780.591530000001</v>
+        <v>4650.211761</v>
       </c>
       <c r="N95">
-        <v>24214.40847</v>
+        <v>24344.788239</v>
       </c>
       <c r="O95">
-        <v>5327.169863399999</v>
+        <v>5355.853412580001</v>
       </c>
       <c r="P95">
-        <v>18887.2386066</v>
+        <v>18988.93482642</v>
       </c>
       <c r="Q95">
-        <v>28673.2386066</v>
+        <v>28774.93482642</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.5060886280801354</v>
+        <v>0.5057927034167863</v>
       </c>
       <c r="T95">
         <v>10.62338806967174</v>
       </c>
       <c r="U95">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V95">
         <v>0.22</v>
       </c>
       <c r="W95">
-        <v>0.0429</v>
+        <v>0.04173</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>6.065149013055294</v>
+        <v>6.235199919963387</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.0752050859762653</v>
+        <v>0.07408462854477449</v>
       </c>
       <c r="C96">
-        <v>8504.980849480678</v>
+        <v>8989.22869593426</v>
       </c>
       <c r="D96">
-        <v>88357.44884948069</v>
+        <v>88841.69669593427</v>
       </c>
       <c r="E96">
         <v>58258.46800000001</v>
@@ -9165,37 +9165,37 @@
         <v>28995</v>
       </c>
       <c r="M96">
-        <v>4831.99574</v>
+        <v>4700.214038</v>
       </c>
       <c r="N96">
-        <v>24163.00426</v>
+        <v>24294.785962</v>
       </c>
       <c r="O96">
-        <v>5315.8609372</v>
+        <v>5344.85291164</v>
       </c>
       <c r="P96">
-        <v>18847.1433228</v>
+        <v>18949.93305036</v>
       </c>
       <c r="Q96">
-        <v>28633.1433228</v>
+        <v>28735.93305036</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.5813180996044222</v>
+        <v>0.5809738090795752</v>
       </c>
       <c r="T96">
         <v>12.35967226511721</v>
       </c>
       <c r="U96">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V96">
         <v>0.22</v>
       </c>
       <c r="W96">
-        <v>0.0429</v>
+        <v>0.04173</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>6.000626151214281</v>
+        <v>6.168868005921223</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.07508696798692116</v>
+        <v>0.07395486785037395</v>
       </c>
       <c r="C97">
-        <v>7622.273964938082</v>
+        <v>8112.270688927732</v>
       </c>
       <c r="D97">
-        <v>88409.36396493808</v>
+        <v>88899.36068892773</v>
       </c>
       <c r="E97">
         <v>59193.09</v>
@@ -9247,37 +9247,37 @@
         <v>28995</v>
       </c>
       <c r="M97">
-        <v>4883.39995</v>
+        <v>4750.216315</v>
       </c>
       <c r="N97">
-        <v>24111.60005</v>
+        <v>24244.783685</v>
       </c>
       <c r="O97">
-        <v>5304.552011000001</v>
+        <v>5333.8524107</v>
       </c>
       <c r="P97">
-        <v>18807.048039</v>
+        <v>18910.9312743</v>
       </c>
       <c r="Q97">
-        <v>28593.048039</v>
+        <v>28696.9312743</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.6866393597384238</v>
+        <v>0.6862273570074798</v>
       </c>
       <c r="T97">
         <v>14.79047013874088</v>
       </c>
       <c r="U97">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V97">
         <v>0.22</v>
       </c>
       <c r="W97">
-        <v>0.0429</v>
+        <v>0.04173</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>5.937461665412025</v>
+        <v>6.103932553227316</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.074968849997577</v>
+        <v>0.07382510715597342</v>
       </c>
       <c r="C98">
-        <v>6739.628122531794</v>
+        <v>7235.387585842254</v>
       </c>
       <c r="D98">
-        <v>88461.34012253179</v>
+        <v>88957.09958584225</v>
       </c>
       <c r="E98">
         <v>60127.712</v>
@@ -9329,37 +9329,37 @@
         <v>28995</v>
       </c>
       <c r="M98">
-        <v>4934.80416</v>
+        <v>4800.218592</v>
       </c>
       <c r="N98">
-        <v>24060.19584</v>
+        <v>24194.781408</v>
       </c>
       <c r="O98">
-        <v>5293.2430848</v>
+        <v>5322.85190976</v>
       </c>
       <c r="P98">
-        <v>18766.9527552</v>
+        <v>18871.92949824</v>
       </c>
       <c r="Q98">
-        <v>28552.9527552</v>
+        <v>28657.92949824</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.8446212499394241</v>
+        <v>0.8441076788993346</v>
       </c>
       <c r="T98">
         <v>18.43666694917632</v>
       </c>
       <c r="U98">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V98">
         <v>0.22</v>
       </c>
       <c r="W98">
-        <v>0.0429</v>
+        <v>0.04173</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>5.875613106397317</v>
+        <v>6.040349922464531</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.07485073200823283</v>
+        <v>0.07369534646157289</v>
       </c>
       <c r="C99">
-        <v>5857.043429985759</v>
+        <v>6358.579532719828</v>
       </c>
       <c r="D99">
-        <v>88513.37742998575</v>
+        <v>89014.91353271982</v>
       </c>
       <c r="E99">
         <v>61062.33399999999</v>
@@ -9411,37 +9411,37 @@
         <v>28995</v>
       </c>
       <c r="M99">
-        <v>4986.208369999999</v>
+        <v>4850.220868999999</v>
       </c>
       <c r="N99">
-        <v>24008.79163</v>
+        <v>24144.779131</v>
       </c>
       <c r="O99">
-        <v>5281.9341586</v>
+        <v>5311.851408820001</v>
       </c>
       <c r="P99">
-        <v>18726.8574714</v>
+        <v>18832.92772218</v>
       </c>
       <c r="Q99">
-        <v>28512.8574714</v>
+        <v>28618.92772218</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.107924400274427</v>
+        <v>1.107241548719095</v>
       </c>
       <c r="T99">
         <v>24.51366163323545</v>
       </c>
       <c r="U99">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V99">
         <v>0.22</v>
       </c>
       <c r="W99">
-        <v>0.0429</v>
+        <v>0.04173</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>5.81503977540353</v>
+        <v>5.978078273779332</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.0747326140188887</v>
+        <v>0.07356558576717236</v>
       </c>
       <c r="C100">
-        <v>4974.519995277529</v>
+        <v>5481.846675982364</v>
       </c>
       <c r="D100">
-        <v>88565.47599527752</v>
+        <v>89072.80267598236</v>
       </c>
       <c r="E100">
         <v>61996.95599999999</v>
@@ -9493,37 +9493,37 @@
         <v>28995</v>
       </c>
       <c r="M100">
-        <v>5037.61258</v>
+        <v>4900.223145999999</v>
       </c>
       <c r="N100">
-        <v>23957.38742</v>
+        <v>24094.776854</v>
       </c>
       <c r="O100">
-        <v>5270.6252324</v>
+        <v>5300.85090788</v>
       </c>
       <c r="P100">
-        <v>18686.7621876</v>
+        <v>18793.92594612</v>
       </c>
       <c r="Q100">
-        <v>28472.7621876</v>
+        <v>28579.92594612</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.634530700944433</v>
+        <v>1.633509288358616</v>
       </c>
       <c r="T100">
         <v>36.66765100135372</v>
       </c>
       <c r="U100">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V100">
         <v>0.22</v>
       </c>
       <c r="W100">
-        <v>0.0429</v>
+        <v>0.04173</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>5.755702634838188</v>
+        <v>5.917077475067297</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.07461449602954454</v>
+        <v>0.07343582507277181</v>
       </c>
       <c r="C101">
-        <v>4092.057926639085</v>
+        <v>4605.189162432958</v>
       </c>
       <c r="D101">
-        <v>88617.63592663908</v>
+        <v>89130.76716243295</v>
       </c>
       <c r="E101">
         <v>62931.57799999999</v>
@@ -9575,37 +9575,37 @@
         <v>28995</v>
       </c>
       <c r="M101">
-        <v>5089.01679</v>
+        <v>4950.225423</v>
       </c>
       <c r="N101">
-        <v>23905.98321</v>
+        <v>24044.774577</v>
       </c>
       <c r="O101">
-        <v>5259.316306199999</v>
+        <v>5289.85040694</v>
       </c>
       <c r="P101">
-        <v>18646.6669038</v>
+        <v>18754.92417006</v>
       </c>
       <c r="Q101">
-        <v>28432.6669038</v>
+        <v>28540.92417006</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.21434960295445</v>
+        <v>3.212312507277178</v>
       </c>
       <c r="T101">
         <v>73.12961910570851</v>
       </c>
       <c r="U101">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V101">
         <v>0.22</v>
       </c>
       <c r="W101">
-        <v>0.0429</v>
+        <v>0.04173</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>5.697564224385276</v>
+        <v>5.857309015723182</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/norway/norway_oil_gas_integrated.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_oil_gas_integrated.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08628213381842471</v>
+        <v>0.08612741312402418</v>
       </c>
       <c r="C2">
-        <v>91738.09831568993</v>
+        <v>90864.56160269018</v>
       </c>
       <c r="D2">
-        <v>83736.09831568993</v>
+        <v>83797.18360269019</v>
       </c>
       <c r="E2">
-        <v>-29596</v>
+        <v>-28661.378</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>934.622</v>
       </c>
       <c r="G2">
         <v>8002</v>
@@ -1457,28 +1457,28 @@
         <v>28995</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>47.0114866</v>
       </c>
       <c r="N2">
-        <v>28995</v>
+        <v>28947.9885134</v>
       </c>
       <c r="O2">
-        <v>6378.9</v>
+        <v>6368.557472948</v>
       </c>
       <c r="P2">
-        <v>22616.1</v>
+        <v>22579.431040452</v>
       </c>
       <c r="Q2">
-        <v>32402.1</v>
+        <v>32365.431040452</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08628213381842471</v>
+        <v>0.08660108396366079</v>
       </c>
       <c r="T2">
-        <v>0.9349222590860211</v>
+        <v>0.942288313248517</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>616.7641590810703</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08612741312402418</v>
+        <v>0.08597269242962365</v>
       </c>
       <c r="C3">
-        <v>90864.56160269018</v>
+        <v>89991.11407789977</v>
       </c>
       <c r="D3">
-        <v>83797.18360269019</v>
+        <v>83858.35807789977</v>
       </c>
       <c r="E3">
-        <v>-28661.378</v>
+        <v>-27726.756</v>
       </c>
       <c r="F3">
-        <v>934.622</v>
+        <v>1869.244</v>
       </c>
       <c r="G3">
         <v>8002</v>
@@ -1539,28 +1539,28 @@
         <v>28995</v>
       </c>
       <c r="M3">
-        <v>47.0114866</v>
+        <v>94.0229732</v>
       </c>
       <c r="N3">
-        <v>28947.9885134</v>
+        <v>28900.9770268</v>
       </c>
       <c r="O3">
-        <v>6368.557472948</v>
+        <v>6358.214945896</v>
       </c>
       <c r="P3">
-        <v>22579.431040452</v>
+        <v>22542.762080904</v>
       </c>
       <c r="Q3">
-        <v>32365.431040452</v>
+        <v>32328.762080904</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08660108396366079</v>
+        <v>0.08692654329553434</v>
       </c>
       <c r="T3">
-        <v>0.942288313248517</v>
+        <v>0.9498046950469823</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>616.7641590810703</v>
+        <v>308.3820795405351</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08597269242962365</v>
+        <v>0.08581797173522311</v>
       </c>
       <c r="C4">
-        <v>89991.11407789977</v>
+        <v>89117.75593679161</v>
       </c>
       <c r="D4">
-        <v>83858.35807789977</v>
+        <v>83919.62193679161</v>
       </c>
       <c r="E4">
-        <v>-27726.756</v>
+        <v>-26792.134</v>
       </c>
       <c r="F4">
-        <v>1869.244</v>
+        <v>2803.866</v>
       </c>
       <c r="G4">
         <v>8002</v>
@@ -1621,28 +1621,28 @@
         <v>28995</v>
       </c>
       <c r="M4">
-        <v>94.0229732</v>
+        <v>141.0344598</v>
       </c>
       <c r="N4">
-        <v>28900.9770268</v>
+        <v>28853.9655402</v>
       </c>
       <c r="O4">
-        <v>6358.214945896</v>
+        <v>6347.872418844</v>
       </c>
       <c r="P4">
-        <v>22542.762080904</v>
+        <v>22506.093121356</v>
       </c>
       <c r="Q4">
-        <v>32328.762080904</v>
+        <v>32292.093121356</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08692654329553434</v>
+        <v>0.087258713129096</v>
       </c>
       <c r="T4">
-        <v>0.9498046950469823</v>
+        <v>0.9574760537897458</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>308.3820795405351</v>
+        <v>205.5880530270234</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08581797173522311</v>
+        <v>0.08566325104082259</v>
       </c>
       <c r="C5">
-        <v>89117.75593679161</v>
+        <v>88244.4873754103</v>
       </c>
       <c r="D5">
-        <v>83919.62193679161</v>
+        <v>83980.9753754103</v>
       </c>
       <c r="E5">
-        <v>-26792.134</v>
+        <v>-25857.512</v>
       </c>
       <c r="F5">
-        <v>2803.866</v>
+        <v>3738.488</v>
       </c>
       <c r="G5">
         <v>8002</v>
@@ -1703,28 +1703,28 @@
         <v>28995</v>
       </c>
       <c r="M5">
-        <v>141.0344598</v>
+        <v>188.0459464</v>
       </c>
       <c r="N5">
-        <v>28853.9655402</v>
+        <v>28806.9540536</v>
       </c>
       <c r="O5">
-        <v>6347.872418844</v>
+        <v>6337.529891792</v>
       </c>
       <c r="P5">
-        <v>22506.093121356</v>
+        <v>22469.424161808</v>
       </c>
       <c r="Q5">
-        <v>32292.093121356</v>
+        <v>32255.424161808</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.087258713129096</v>
+        <v>0.08759780316752352</v>
       </c>
       <c r="T5">
-        <v>0.9574760537897458</v>
+        <v>0.9653072325063168</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>205.5880530270234</v>
+        <v>154.1910397702675</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08566325104082259</v>
+        <v>0.08550853034642203</v>
       </c>
       <c r="C6">
-        <v>88244.4873754103</v>
+        <v>87371.30859037423</v>
       </c>
       <c r="D6">
-        <v>83980.9753754103</v>
+        <v>84042.41859037423</v>
       </c>
       <c r="E6">
-        <v>-25857.512</v>
+        <v>-24922.89</v>
       </c>
       <c r="F6">
-        <v>3738.488</v>
+        <v>4673.11</v>
       </c>
       <c r="G6">
         <v>8002</v>
@@ -1785,28 +1785,28 @@
         <v>28995</v>
       </c>
       <c r="M6">
-        <v>188.0459464</v>
+        <v>235.057433</v>
       </c>
       <c r="N6">
-        <v>28806.9540536</v>
+        <v>28759.942567</v>
       </c>
       <c r="O6">
-        <v>6337.529891792</v>
+        <v>6327.18736474</v>
       </c>
       <c r="P6">
-        <v>22469.424161808</v>
+        <v>22432.75520226</v>
       </c>
       <c r="Q6">
-        <v>32255.424161808</v>
+        <v>32218.75520226</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08759780316752352</v>
+        <v>0.08794403194360215</v>
       </c>
       <c r="T6">
-        <v>0.9653072325063168</v>
+        <v>0.9733032781432368</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>154.1910397702675</v>
+        <v>123.352831816214</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08550853034642203</v>
+        <v>0.08535380965202151</v>
       </c>
       <c r="C7">
-        <v>87371.30859037423</v>
+        <v>86498.21977887749</v>
       </c>
       <c r="D7">
-        <v>84042.41859037423</v>
+        <v>84103.9517788775</v>
       </c>
       <c r="E7">
-        <v>-24922.89</v>
+        <v>-23988.268</v>
       </c>
       <c r="F7">
-        <v>4673.11</v>
+        <v>5607.732</v>
       </c>
       <c r="G7">
         <v>8002</v>
@@ -1867,28 +1867,28 @@
         <v>28995</v>
       </c>
       <c r="M7">
-        <v>235.057433</v>
+        <v>282.0689196</v>
       </c>
       <c r="N7">
-        <v>28759.942567</v>
+        <v>28712.9310804</v>
       </c>
       <c r="O7">
-        <v>6327.18736474</v>
+        <v>6316.844837688001</v>
       </c>
       <c r="P7">
-        <v>22432.75520226</v>
+        <v>22396.086242712</v>
       </c>
       <c r="Q7">
-        <v>32218.75520226</v>
+        <v>32182.086242712</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08794403194360215</v>
+        <v>0.08829762728938459</v>
       </c>
       <c r="T7">
-        <v>0.9733032781432368</v>
+        <v>0.9814694524107294</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>123.352831816214</v>
+        <v>102.7940265135117</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08535380965202151</v>
+        <v>0.08519908895762099</v>
       </c>
       <c r="C8">
-        <v>86498.21977887749</v>
+        <v>85625.22113869223</v>
       </c>
       <c r="D8">
-        <v>84103.9517788775</v>
+        <v>84165.57513869223</v>
       </c>
       <c r="E8">
-        <v>-23988.268</v>
+        <v>-23053.646</v>
       </c>
       <c r="F8">
-        <v>5607.732</v>
+        <v>6542.353999999999</v>
       </c>
       <c r="G8">
         <v>8002</v>
@@ -1949,28 +1949,28 @@
         <v>28995</v>
       </c>
       <c r="M8">
-        <v>282.0689196</v>
+        <v>329.0804062</v>
       </c>
       <c r="N8">
-        <v>28712.9310804</v>
+        <v>28665.9195938</v>
       </c>
       <c r="O8">
-        <v>6316.844837688001</v>
+        <v>6306.502310636</v>
       </c>
       <c r="P8">
-        <v>22396.086242712</v>
+        <v>22359.417283164</v>
       </c>
       <c r="Q8">
-        <v>32182.086242712</v>
+        <v>32145.417283164</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08829762728938459</v>
+        <v>0.08865882683615159</v>
       </c>
       <c r="T8">
-        <v>0.9814694524107294</v>
+        <v>0.9898112433291358</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>102.7940265135117</v>
+        <v>88.10916558301004</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08519908895762097</v>
+        <v>0.08504436826322044</v>
       </c>
       <c r="C9">
-        <v>85625.22113869224</v>
+        <v>84752.31286817061</v>
       </c>
       <c r="D9">
-        <v>84165.57513869225</v>
+        <v>84227.28886817061</v>
       </c>
       <c r="E9">
-        <v>-23053.646</v>
+        <v>-22119.024</v>
       </c>
       <c r="F9">
-        <v>6542.354</v>
+        <v>7476.976</v>
       </c>
       <c r="G9">
         <v>8002</v>
@@ -2031,28 +2031,28 @@
         <v>28995</v>
       </c>
       <c r="M9">
-        <v>329.0804062</v>
+        <v>376.0918928</v>
       </c>
       <c r="N9">
-        <v>28665.9195938</v>
+        <v>28618.9081072</v>
       </c>
       <c r="O9">
-        <v>6306.502310636</v>
+        <v>6296.159783584</v>
       </c>
       <c r="P9">
-        <v>22359.417283164</v>
+        <v>22322.748323616</v>
       </c>
       <c r="Q9">
-        <v>32145.417283164</v>
+        <v>32108.748323616</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08865882683615159</v>
+        <v>0.08902787854697874</v>
       </c>
       <c r="T9">
-        <v>0.9898112433291361</v>
+        <v>0.9983343775283773</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>88.10916558301004</v>
+        <v>77.09551988513378</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08504436826322044</v>
+        <v>0.08488964756881991</v>
       </c>
       <c r="C10">
-        <v>84752.31286817061</v>
+        <v>83879.49516624695</v>
       </c>
       <c r="D10">
-        <v>84227.28886817061</v>
+        <v>84289.09316624695</v>
       </c>
       <c r="E10">
-        <v>-22119.024</v>
+        <v>-21184.402</v>
       </c>
       <c r="F10">
-        <v>7476.976</v>
+        <v>8411.598</v>
       </c>
       <c r="G10">
         <v>8002</v>
@@ -2113,28 +2113,28 @@
         <v>28995</v>
       </c>
       <c r="M10">
-        <v>376.0918928</v>
+        <v>423.1033794</v>
       </c>
       <c r="N10">
-        <v>28618.9081072</v>
+        <v>28571.8966206</v>
       </c>
       <c r="O10">
-        <v>6296.159783584</v>
+        <v>6285.817256532</v>
       </c>
       <c r="P10">
-        <v>22322.748323616</v>
+        <v>22286.079364068</v>
       </c>
       <c r="Q10">
-        <v>32108.748323616</v>
+        <v>32072.079364068</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08902787854697874</v>
+        <v>0.08940504128441748</v>
       </c>
       <c r="T10">
-        <v>0.9983343775283773</v>
+        <v>1.007044833358371</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>77.09551988513378</v>
+        <v>68.5293510090078</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08488964756881991</v>
+        <v>0.08473492687441937</v>
       </c>
       <c r="C11">
-        <v>83879.49516624695</v>
+        <v>83006.76823243995</v>
       </c>
       <c r="D11">
-        <v>84289.09316624695</v>
+        <v>84350.98823243995</v>
       </c>
       <c r="E11">
-        <v>-21184.402</v>
+        <v>-20249.78</v>
       </c>
       <c r="F11">
-        <v>8411.598</v>
+        <v>9346.219999999999</v>
       </c>
       <c r="G11">
         <v>8002</v>
@@ -2195,28 +2195,28 @@
         <v>28995</v>
       </c>
       <c r="M11">
-        <v>423.1033794</v>
+        <v>470.1148659999999</v>
       </c>
       <c r="N11">
-        <v>28571.8966206</v>
+        <v>28524.885134</v>
       </c>
       <c r="O11">
-        <v>6285.817256532</v>
+        <v>6275.47472948</v>
       </c>
       <c r="P11">
-        <v>22286.079364068</v>
+        <v>22249.41040452</v>
       </c>
       <c r="Q11">
-        <v>32072.079364068</v>
+        <v>32035.41040452</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08940504128441748</v>
+        <v>0.08979058541602153</v>
       </c>
       <c r="T11">
-        <v>1.007044833358371</v>
+        <v>1.015948854873476</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>68.5293510090078</v>
+        <v>61.67641590810702</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08473492687441937</v>
+        <v>0.08458020618001884</v>
       </c>
       <c r="C12">
-        <v>83006.76823243995</v>
+        <v>82134.13226685474</v>
       </c>
       <c r="D12">
-        <v>84350.98823243995</v>
+        <v>84412.97426685474</v>
       </c>
       <c r="E12">
-        <v>-20249.78</v>
+        <v>-19315.158</v>
       </c>
       <c r="F12">
-        <v>9346.219999999999</v>
+        <v>10280.842</v>
       </c>
       <c r="G12">
         <v>8002</v>
@@ -2277,28 +2277,28 @@
         <v>28995</v>
       </c>
       <c r="M12">
-        <v>470.1148659999999</v>
+        <v>517.1263526</v>
       </c>
       <c r="N12">
-        <v>28524.885134</v>
+        <v>28477.8736474</v>
       </c>
       <c r="O12">
-        <v>6275.47472948</v>
+        <v>6265.132202428</v>
       </c>
       <c r="P12">
-        <v>22249.41040452</v>
+        <v>22212.741444972</v>
       </c>
       <c r="Q12">
-        <v>32035.41040452</v>
+        <v>31998.741444972</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08979058541602153</v>
+        <v>0.09018479346069533</v>
       </c>
       <c r="T12">
-        <v>1.015948854873476</v>
+        <v>1.025052966759707</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>61.67641590810702</v>
+        <v>56.06946900737002</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08458020618001884</v>
+        <v>0.08442548548561832</v>
       </c>
       <c r="C13">
-        <v>82134.13226685474</v>
+        <v>81261.5874701851</v>
       </c>
       <c r="D13">
-        <v>84412.97426685474</v>
+        <v>84475.05147018509</v>
       </c>
       <c r="E13">
-        <v>-19315.158</v>
+        <v>-18380.536</v>
       </c>
       <c r="F13">
-        <v>10280.842</v>
+        <v>11215.464</v>
       </c>
       <c r="G13">
         <v>8002</v>
@@ -2359,28 +2359,28 @@
         <v>28995</v>
       </c>
       <c r="M13">
-        <v>517.1263526</v>
+        <v>564.1378391999999</v>
       </c>
       <c r="N13">
-        <v>28477.8736474</v>
+        <v>28430.8621608</v>
       </c>
       <c r="O13">
-        <v>6265.132202428</v>
+        <v>6254.789675376</v>
       </c>
       <c r="P13">
-        <v>22212.741444972</v>
+        <v>22176.072485424</v>
       </c>
       <c r="Q13">
-        <v>31998.741444972</v>
+        <v>31962.072485424</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09018479346069533</v>
+        <v>0.09058796077911171</v>
       </c>
       <c r="T13">
-        <v>1.025052966759707</v>
+        <v>1.034363990279716</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>56.06946900737002</v>
+        <v>51.39701325675586</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08442548548561832</v>
+        <v>0.08427076479121776</v>
       </c>
       <c r="C14">
-        <v>81261.5874701851</v>
+        <v>80389.13404371562</v>
       </c>
       <c r="D14">
-        <v>84475.05147018509</v>
+        <v>84537.22004371561</v>
       </c>
       <c r="E14">
-        <v>-18380.536</v>
+        <v>-17445.914</v>
       </c>
       <c r="F14">
-        <v>11215.464</v>
+        <v>12150.086</v>
       </c>
       <c r="G14">
         <v>8002</v>
@@ -2441,28 +2441,28 @@
         <v>28995</v>
       </c>
       <c r="M14">
-        <v>564.1378391999999</v>
+        <v>611.1493257999999</v>
       </c>
       <c r="N14">
-        <v>28430.8621608</v>
+        <v>28383.8506742</v>
       </c>
       <c r="O14">
-        <v>6254.789675376</v>
+        <v>6244.447148323999</v>
       </c>
       <c r="P14">
-        <v>22176.072485424</v>
+        <v>22139.403525876</v>
       </c>
       <c r="Q14">
-        <v>31962.072485424</v>
+        <v>31925.403525876</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09058796077911171</v>
+        <v>0.09100039631174456</v>
       </c>
       <c r="T14">
-        <v>1.034363990279716</v>
+        <v>1.043889060317426</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>51.39701325675586</v>
+        <v>47.44339685239002</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08427076479121776</v>
+        <v>0.08411604409681722</v>
       </c>
       <c r="C15">
-        <v>80389.13404371562</v>
+        <v>79516.77218932379</v>
       </c>
       <c r="D15">
-        <v>84537.22004371561</v>
+        <v>84599.48018932379</v>
       </c>
       <c r="E15">
-        <v>-17445.914</v>
+        <v>-16511.292</v>
       </c>
       <c r="F15">
-        <v>12150.086</v>
+        <v>13084.708</v>
       </c>
       <c r="G15">
         <v>8002</v>
@@ -2523,28 +2523,28 @@
         <v>28995</v>
       </c>
       <c r="M15">
-        <v>611.1493257999999</v>
+        <v>658.1608123999999</v>
       </c>
       <c r="N15">
-        <v>28383.8506742</v>
+        <v>28336.8391876</v>
       </c>
       <c r="O15">
-        <v>6244.447148323999</v>
+        <v>6234.104621271999</v>
       </c>
       <c r="P15">
-        <v>22139.403525876</v>
+        <v>22102.734566328</v>
       </c>
       <c r="Q15">
-        <v>31925.403525876</v>
+        <v>31888.734566328</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09100039631174456</v>
+        <v>0.09142242336839213</v>
       </c>
       <c r="T15">
-        <v>1.043889060317426</v>
+        <v>1.053635643611827</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>47.44339685239002</v>
+        <v>44.05458279150502</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08411604409681722</v>
+        <v>0.0839613234024167</v>
       </c>
       <c r="C16">
-        <v>79516.77218932379</v>
+        <v>78644.50210948233</v>
       </c>
       <c r="D16">
-        <v>84599.48018932379</v>
+        <v>84661.83210948233</v>
       </c>
       <c r="E16">
-        <v>-16511.292</v>
+        <v>-15576.67</v>
       </c>
       <c r="F16">
-        <v>13084.708</v>
+        <v>14019.33</v>
       </c>
       <c r="G16">
         <v>8002</v>
@@ -2605,28 +2605,28 @@
         <v>28995</v>
       </c>
       <c r="M16">
-        <v>658.1608123999999</v>
+        <v>705.1722990000001</v>
       </c>
       <c r="N16">
-        <v>28336.8391876</v>
+        <v>28289.827701</v>
       </c>
       <c r="O16">
-        <v>6234.104621271999</v>
+        <v>6223.76209422</v>
       </c>
       <c r="P16">
-        <v>22102.734566328</v>
+        <v>22066.06560678</v>
       </c>
       <c r="Q16">
-        <v>31888.734566328</v>
+        <v>31852.06560678</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09142242336839213</v>
+        <v>0.09185438047343142</v>
       </c>
       <c r="T16">
-        <v>1.053635643611827</v>
+        <v>1.063611558277862</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>44.05458279150502</v>
+        <v>41.11761060540467</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0839613234024167</v>
+        <v>0.08380660270801615</v>
       </c>
       <c r="C17">
-        <v>78644.50210948233</v>
+        <v>77772.32400726131</v>
       </c>
       <c r="D17">
-        <v>84661.83210948233</v>
+        <v>84724.27600726132</v>
       </c>
       <c r="E17">
-        <v>-15576.67</v>
+        <v>-14642.048</v>
       </c>
       <c r="F17">
-        <v>14019.33</v>
+        <v>14953.952</v>
       </c>
       <c r="G17">
         <v>8002</v>
@@ -2687,28 +2687,28 @@
         <v>28995</v>
       </c>
       <c r="M17">
-        <v>705.172299</v>
+        <v>752.1837856</v>
       </c>
       <c r="N17">
-        <v>28289.827701</v>
+        <v>28242.8162144</v>
       </c>
       <c r="O17">
-        <v>6223.76209422</v>
+        <v>6213.419567168</v>
       </c>
       <c r="P17">
-        <v>22066.06560678</v>
+        <v>22029.396647232</v>
       </c>
       <c r="Q17">
-        <v>31852.06560678</v>
+        <v>31815.396647232</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09185438047343142</v>
+        <v>0.0922966222714478</v>
       </c>
       <c r="T17">
-        <v>1.063611558277862</v>
+        <v>1.073824994721658</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>41.11761060540468</v>
+        <v>38.54775994256689</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08380660270801615</v>
+        <v>0.08365188201361563</v>
       </c>
       <c r="C18">
-        <v>77772.32400726131</v>
+        <v>76900.2380863303</v>
       </c>
       <c r="D18">
-        <v>84724.27600726132</v>
+        <v>84786.81208633029</v>
       </c>
       <c r="E18">
-        <v>-14642.048</v>
+        <v>-13707.426</v>
       </c>
       <c r="F18">
-        <v>14953.952</v>
+        <v>15888.574</v>
       </c>
       <c r="G18">
         <v>8002</v>
@@ -2769,28 +2769,28 @@
         <v>28995</v>
       </c>
       <c r="M18">
-        <v>752.1837856</v>
+        <v>799.1952722</v>
       </c>
       <c r="N18">
-        <v>28242.8162144</v>
+        <v>28195.8047278</v>
       </c>
       <c r="O18">
-        <v>6213.419567168</v>
+        <v>6203.077040116001</v>
       </c>
       <c r="P18">
-        <v>22029.396647232</v>
+        <v>21992.727687684</v>
       </c>
       <c r="Q18">
-        <v>31815.396647232</v>
+        <v>31778.727687684</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0922966222714478</v>
+        <v>0.0927495204983321</v>
       </c>
       <c r="T18">
-        <v>1.073824994721658</v>
+        <v>1.084284538067716</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>38.54775994256689</v>
+        <v>36.28024465182766</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08365188201361563</v>
+        <v>0.08349716131921511</v>
       </c>
       <c r="C19">
-        <v>76900.2380863303</v>
+        <v>76028.24455096065</v>
       </c>
       <c r="D19">
-        <v>84786.81208633029</v>
+        <v>84849.44055096064</v>
       </c>
       <c r="E19">
-        <v>-13707.426</v>
+        <v>-12772.804</v>
       </c>
       <c r="F19">
-        <v>15888.574</v>
+        <v>16823.196</v>
       </c>
       <c r="G19">
         <v>8002</v>
@@ -2851,28 +2851,28 @@
         <v>28995</v>
       </c>
       <c r="M19">
-        <v>799.1952722</v>
+        <v>846.2067588</v>
       </c>
       <c r="N19">
-        <v>28195.8047278</v>
+        <v>28148.7932412</v>
       </c>
       <c r="O19">
-        <v>6203.077040116001</v>
+        <v>6192.734513064001</v>
       </c>
       <c r="P19">
-        <v>21992.727687684</v>
+        <v>21956.058728136</v>
       </c>
       <c r="Q19">
-        <v>31778.727687684</v>
+        <v>31742.058728136</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.0927495204983321</v>
+        <v>0.09321346502343306</v>
       </c>
       <c r="T19">
-        <v>1.084284538067716</v>
+        <v>1.094999192227091</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>36.28024465182766</v>
+        <v>34.2646755045039</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0834971613192151</v>
+        <v>0.08334244062481456</v>
       </c>
       <c r="C20">
-        <v>76028.24455096065</v>
+        <v>75156.34360602775</v>
       </c>
       <c r="D20">
-        <v>84849.44055096064</v>
+        <v>84912.16160602774</v>
       </c>
       <c r="E20">
-        <v>-12772.804</v>
+        <v>-11838.182</v>
       </c>
       <c r="F20">
-        <v>16823.196</v>
+        <v>17757.818</v>
       </c>
       <c r="G20">
         <v>8002</v>
@@ -2933,28 +2933,28 @@
         <v>28995</v>
       </c>
       <c r="M20">
-        <v>846.2067588</v>
+        <v>893.2182453999999</v>
       </c>
       <c r="N20">
-        <v>28148.7932412</v>
+        <v>28101.7817546</v>
       </c>
       <c r="O20">
-        <v>6192.734513064001</v>
+        <v>6182.391986012</v>
       </c>
       <c r="P20">
-        <v>21956.058728136</v>
+        <v>21919.389768588</v>
       </c>
       <c r="Q20">
-        <v>31742.058728136</v>
+        <v>31705.389768588</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09321346502343303</v>
+        <v>0.09368886496890687</v>
       </c>
       <c r="T20">
-        <v>1.094999192227091</v>
+        <v>1.105978405748427</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>34.2646755045039</v>
+        <v>32.46127153058265</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08334244062481456</v>
+        <v>0.08318771993041403</v>
       </c>
       <c r="C21">
-        <v>75156.34360602775</v>
+        <v>74284.53545701316</v>
       </c>
       <c r="D21">
-        <v>84912.16160602774</v>
+        <v>84974.97545701316</v>
       </c>
       <c r="E21">
-        <v>-11838.182</v>
+        <v>-10903.56</v>
       </c>
       <c r="F21">
-        <v>17757.818</v>
+        <v>18692.44</v>
       </c>
       <c r="G21">
         <v>8002</v>
@@ -3015,28 +3015,28 @@
         <v>28995</v>
       </c>
       <c r="M21">
-        <v>893.2182453999999</v>
+        <v>940.2297319999999</v>
       </c>
       <c r="N21">
-        <v>28101.7817546</v>
+        <v>28054.770268</v>
       </c>
       <c r="O21">
-        <v>6182.391986012</v>
+        <v>6172.04945896</v>
       </c>
       <c r="P21">
-        <v>21919.389768588</v>
+        <v>21882.72080904</v>
       </c>
       <c r="Q21">
-        <v>31705.389768588</v>
+        <v>31668.72080904</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09368886496890687</v>
+        <v>0.09417614991301754</v>
       </c>
       <c r="T21">
-        <v>1.105978405748427</v>
+        <v>1.117232099607795</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>32.46127153058265</v>
+        <v>30.83820795405351</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08318771993041403</v>
+        <v>0.08303299923601351</v>
       </c>
       <c r="C22">
-        <v>74284.53545701316</v>
+        <v>73412.82031000697</v>
       </c>
       <c r="D22">
-        <v>84974.97545701316</v>
+        <v>85037.88231000697</v>
       </c>
       <c r="E22">
-        <v>-10903.56</v>
+        <v>-9968.937999999998</v>
       </c>
       <c r="F22">
-        <v>18692.44</v>
+        <v>19627.062</v>
       </c>
       <c r="G22">
         <v>8002</v>
@@ -3097,28 +3097,28 @@
         <v>28995</v>
       </c>
       <c r="M22">
-        <v>940.2297319999999</v>
+        <v>987.2412186</v>
       </c>
       <c r="N22">
-        <v>28054.770268</v>
+        <v>28007.7587814</v>
       </c>
       <c r="O22">
-        <v>6172.04945896</v>
+        <v>6161.706931908</v>
       </c>
       <c r="P22">
-        <v>21882.72080904</v>
+        <v>21846.051849492</v>
       </c>
       <c r="Q22">
-        <v>31668.72080904</v>
+        <v>31632.051849492</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09417614991301754</v>
+        <v>0.09467577118482721</v>
       </c>
       <c r="T22">
-        <v>1.117232099607795</v>
+        <v>1.128770697109174</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>30.83820795405351</v>
+        <v>29.36972186100334</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08303299923601348</v>
+        <v>0.08287827854161296</v>
       </c>
       <c r="C23">
-        <v>73412.82031000697</v>
+        <v>72541.19837170994</v>
       </c>
       <c r="D23">
-        <v>85037.88231000697</v>
+        <v>85100.88237170994</v>
       </c>
       <c r="E23">
-        <v>-9968.938000000002</v>
+        <v>-9034.315999999999</v>
       </c>
       <c r="F23">
-        <v>19627.062</v>
+        <v>20561.684</v>
       </c>
       <c r="G23">
         <v>8002</v>
@@ -3179,28 +3179,28 @@
         <v>28995</v>
       </c>
       <c r="M23">
-        <v>987.2412185999998</v>
+        <v>1034.2527052</v>
       </c>
       <c r="N23">
-        <v>28007.7587814</v>
+        <v>27960.7472948</v>
       </c>
       <c r="O23">
-        <v>6161.706931908</v>
+        <v>6151.364404856</v>
       </c>
       <c r="P23">
-        <v>21846.051849492</v>
+        <v>21809.382889944</v>
       </c>
       <c r="Q23">
-        <v>31632.051849492</v>
+        <v>31595.382889944</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0946757711848272</v>
+        <v>0.09518820325847815</v>
       </c>
       <c r="T23">
-        <v>1.128770697109173</v>
+        <v>1.140605156084946</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>29.36972186100335</v>
+        <v>28.03473450368501</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08287827854161296</v>
+        <v>0.08272355784721243</v>
       </c>
       <c r="C24">
-        <v>72541.19837170994</v>
+        <v>71669.66984943586</v>
       </c>
       <c r="D24">
-        <v>85100.88237170994</v>
+        <v>85163.97584943585</v>
       </c>
       <c r="E24">
-        <v>-9034.315999999999</v>
+        <v>-8099.694</v>
       </c>
       <c r="F24">
-        <v>20561.684</v>
+        <v>21496.306</v>
       </c>
       <c r="G24">
         <v>8002</v>
@@ -3261,28 +3261,28 @@
         <v>28995</v>
       </c>
       <c r="M24">
-        <v>1034.2527052</v>
+        <v>1081.2641918</v>
       </c>
       <c r="N24">
-        <v>27960.7472948</v>
+        <v>27913.7358082</v>
       </c>
       <c r="O24">
-        <v>6151.364404856</v>
+        <v>6141.021877804</v>
       </c>
       <c r="P24">
-        <v>21809.382889944</v>
+        <v>21772.713930396</v>
       </c>
       <c r="Q24">
-        <v>31595.382889944</v>
+        <v>31558.713930396</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09518820325847815</v>
+        <v>0.09571394525612004</v>
       </c>
       <c r="T24">
-        <v>1.140605156084946</v>
+        <v>1.152747003605544</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>28.03473450368501</v>
+        <v>26.81583300352479</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08272355784721243</v>
+        <v>0.08256883715281188</v>
       </c>
       <c r="C25">
-        <v>71669.66984943586</v>
+        <v>70798.23495111374</v>
       </c>
       <c r="D25">
-        <v>85163.97584943585</v>
+        <v>85227.16295111374</v>
       </c>
       <c r="E25">
-        <v>-8099.694</v>
+        <v>-7165.072</v>
       </c>
       <c r="F25">
-        <v>21496.306</v>
+        <v>22430.928</v>
       </c>
       <c r="G25">
         <v>8002</v>
@@ -3343,28 +3343,28 @@
         <v>28995</v>
       </c>
       <c r="M25">
-        <v>1081.2641918</v>
+        <v>1128.2756784</v>
       </c>
       <c r="N25">
-        <v>27913.7358082</v>
+        <v>27866.7243216</v>
       </c>
       <c r="O25">
-        <v>6141.021877804</v>
+        <v>6130.679350752</v>
       </c>
       <c r="P25">
-        <v>21772.713930396</v>
+        <v>21736.044970848</v>
       </c>
       <c r="Q25">
-        <v>31558.713930396</v>
+        <v>31522.044970848</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09571394525612004</v>
+        <v>0.09625352256948932</v>
       </c>
       <c r="T25">
-        <v>1.152747003605544</v>
+        <v>1.165208373429315</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>26.81583300352479</v>
+        <v>25.69850662837793</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08256883715281188</v>
+        <v>0.08241411645841136</v>
       </c>
       <c r="C26">
-        <v>70798.23495111374</v>
+        <v>69926.89388529018</v>
       </c>
       <c r="D26">
-        <v>85227.16295111374</v>
+        <v>85290.44388529018</v>
       </c>
       <c r="E26">
-        <v>-7165.072</v>
+        <v>-6230.450000000001</v>
       </c>
       <c r="F26">
-        <v>22430.928</v>
+        <v>23365.55</v>
       </c>
       <c r="G26">
         <v>8002</v>
@@ -3425,28 +3425,28 @@
         <v>28995</v>
       </c>
       <c r="M26">
-        <v>1128.2756784</v>
+        <v>1175.287165</v>
       </c>
       <c r="N26">
-        <v>27866.7243216</v>
+        <v>27819.712835</v>
       </c>
       <c r="O26">
-        <v>6130.679350752</v>
+        <v>6120.3368237</v>
       </c>
       <c r="P26">
-        <v>21736.044970848</v>
+        <v>21699.3760113</v>
       </c>
       <c r="Q26">
-        <v>31522.044970848</v>
+        <v>31485.3760113</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09625352256948932</v>
+        <v>0.09680748861121515</v>
       </c>
       <c r="T26">
-        <v>1.165208373429315</v>
+        <v>1.178002046448387</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>25.69850662837793</v>
+        <v>24.67056636324281</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08241411645841136</v>
+        <v>0.08225939576401083</v>
       </c>
       <c r="C27">
-        <v>69926.89388529018</v>
+        <v>69055.64686113159</v>
       </c>
       <c r="D27">
-        <v>85290.44388529018</v>
+        <v>85353.81886113159</v>
       </c>
       <c r="E27">
-        <v>-6230.450000000001</v>
+        <v>-5295.828000000001</v>
       </c>
       <c r="F27">
-        <v>23365.55</v>
+        <v>24300.172</v>
       </c>
       <c r="G27">
         <v>8002</v>
@@ -3507,28 +3507,28 @@
         <v>28995</v>
       </c>
       <c r="M27">
-        <v>1175.287165</v>
+        <v>1222.2986516</v>
       </c>
       <c r="N27">
-        <v>27819.712835</v>
+        <v>27772.7013484</v>
       </c>
       <c r="O27">
-        <v>6120.3368237</v>
+        <v>6109.994296648</v>
       </c>
       <c r="P27">
-        <v>21699.3760113</v>
+        <v>21662.707051752</v>
       </c>
       <c r="Q27">
-        <v>31485.3760113</v>
+        <v>31448.707051752</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09680748861121515</v>
+        <v>0.09737642670812274</v>
       </c>
       <c r="T27">
-        <v>1.178002046448387</v>
+        <v>1.19114149441392</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>24.67056636324281</v>
+        <v>23.72169842619501</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08225939576401083</v>
+        <v>0.08210467506961028</v>
       </c>
       <c r="C28">
-        <v>69055.64686113159</v>
+        <v>68184.49408842652</v>
       </c>
       <c r="D28">
-        <v>85353.81886113159</v>
+        <v>85417.28808842653</v>
       </c>
       <c r="E28">
-        <v>-5295.828000000001</v>
+        <v>-4361.205999999998</v>
       </c>
       <c r="F28">
-        <v>24300.172</v>
+        <v>25234.794</v>
       </c>
       <c r="G28">
         <v>8002</v>
@@ -3589,28 +3589,28 @@
         <v>28995</v>
       </c>
       <c r="M28">
-        <v>1222.2986516</v>
+        <v>1269.3101382</v>
       </c>
       <c r="N28">
-        <v>27772.7013484</v>
+        <v>27725.6898618</v>
       </c>
       <c r="O28">
-        <v>6109.994296648</v>
+        <v>6099.651769596</v>
       </c>
       <c r="P28">
-        <v>21662.707051752</v>
+        <v>21626.038092204</v>
       </c>
       <c r="Q28">
-        <v>31448.707051752</v>
+        <v>31412.038092204</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09737642670812274</v>
+        <v>0.09796095215015108</v>
       </c>
       <c r="T28">
-        <v>1.19114149441392</v>
+        <v>1.204640927255221</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>23.72169842619501</v>
+        <v>22.8431170030026</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08210467506961028</v>
+        <v>0.08194995437520974</v>
       </c>
       <c r="C29">
-        <v>68184.49408842652</v>
+        <v>67313.43577758805</v>
       </c>
       <c r="D29">
-        <v>85417.28808842653</v>
+        <v>85480.85177758805</v>
       </c>
       <c r="E29">
-        <v>-4361.205999999998</v>
+        <v>-3426.583999999999</v>
       </c>
       <c r="F29">
-        <v>25234.794</v>
+        <v>26169.416</v>
       </c>
       <c r="G29">
         <v>8002</v>
@@ -3671,28 +3671,28 @@
         <v>28995</v>
       </c>
       <c r="M29">
-        <v>1269.3101382</v>
+        <v>1316.3216248</v>
       </c>
       <c r="N29">
-        <v>27725.6898618</v>
+        <v>27678.6783752</v>
       </c>
       <c r="O29">
-        <v>6099.651769596</v>
+        <v>6089.309242544</v>
       </c>
       <c r="P29">
-        <v>21626.038092204</v>
+        <v>21589.369132656</v>
       </c>
       <c r="Q29">
-        <v>31412.038092204</v>
+        <v>31375.369132656</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09796095215015108</v>
+        <v>0.09856171441001355</v>
       </c>
       <c r="T29">
-        <v>1.204640927255221</v>
+        <v>1.218515344342114</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>22.8431170030026</v>
+        <v>22.02729139575251</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08194995437520974</v>
+        <v>0.08179523368080922</v>
       </c>
       <c r="C30">
-        <v>67313.43577758805</v>
+        <v>66442.47213965593</v>
       </c>
       <c r="D30">
-        <v>85480.85177758805</v>
+        <v>85544.51013965593</v>
       </c>
       <c r="E30">
-        <v>-3426.583999999999</v>
+        <v>-2491.961999999996</v>
       </c>
       <c r="F30">
-        <v>26169.416</v>
+        <v>27104.038</v>
       </c>
       <c r="G30">
         <v>8002</v>
@@ -3753,28 +3753,28 @@
         <v>28995</v>
       </c>
       <c r="M30">
-        <v>1316.3216248</v>
+        <v>1363.3331114</v>
       </c>
       <c r="N30">
-        <v>27678.6783752</v>
+        <v>27631.6668886</v>
       </c>
       <c r="O30">
-        <v>6089.309242544</v>
+        <v>6078.966715492</v>
       </c>
       <c r="P30">
-        <v>21589.369132656</v>
+        <v>21552.700173108</v>
       </c>
       <c r="Q30">
-        <v>31375.369132656</v>
+        <v>31338.700173108</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09856171441001355</v>
+        <v>0.09917939955043552</v>
       </c>
       <c r="T30">
-        <v>1.218515344342114</v>
+        <v>1.232780590079342</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>22.02729139575251</v>
+        <v>21.26772962348518</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08179523368080922</v>
+        <v>0.08164051298640866</v>
       </c>
       <c r="C31">
-        <v>66442.47213965593</v>
+        <v>65571.60338629918</v>
       </c>
       <c r="D31">
-        <v>85544.51013965593</v>
+        <v>85608.26338629918</v>
       </c>
       <c r="E31">
-        <v>-2491.962000000003</v>
+        <v>-1557.34</v>
       </c>
       <c r="F31">
-        <v>27104.038</v>
+        <v>28038.66</v>
       </c>
       <c r="G31">
         <v>8002</v>
@@ -3835,28 +3835,28 @@
         <v>28995</v>
       </c>
       <c r="M31">
-        <v>1363.3331114</v>
+        <v>1410.344598</v>
       </c>
       <c r="N31">
-        <v>27631.6668886</v>
+        <v>27584.655402</v>
       </c>
       <c r="O31">
-        <v>6078.966715492</v>
+        <v>6068.62418844</v>
       </c>
       <c r="P31">
-        <v>21552.700173108</v>
+        <v>21516.03121356</v>
       </c>
       <c r="Q31">
-        <v>31338.700173108</v>
+        <v>31302.03121356</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09917939955043552</v>
+        <v>0.09981473283772668</v>
       </c>
       <c r="T31">
-        <v>1.232780590079342</v>
+        <v>1.247453414266205</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>21.26772962348518</v>
+        <v>20.55880530270234</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08164051298640866</v>
+        <v>0.08148579229200814</v>
       </c>
       <c r="C32">
-        <v>65571.60338629918</v>
+        <v>64700.82972981812</v>
       </c>
       <c r="D32">
-        <v>85608.26338629918</v>
+        <v>85672.11172981812</v>
       </c>
       <c r="E32">
-        <v>-1557.34</v>
+        <v>-622.7180000000008</v>
       </c>
       <c r="F32">
-        <v>28038.66</v>
+        <v>28973.282</v>
       </c>
       <c r="G32">
         <v>8002</v>
@@ -3917,28 +3917,28 @@
         <v>28995</v>
       </c>
       <c r="M32">
-        <v>1410.344598</v>
+        <v>1457.3560846</v>
       </c>
       <c r="N32">
-        <v>27584.655402</v>
+        <v>27537.6439154</v>
       </c>
       <c r="O32">
-        <v>6068.62418844</v>
+        <v>6058.281661388</v>
       </c>
       <c r="P32">
-        <v>21516.03121356</v>
+        <v>21479.362254012</v>
       </c>
       <c r="Q32">
-        <v>31302.03121356</v>
+        <v>31265.362254012</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09981473283772668</v>
+        <v>0.1004684815826205</v>
       </c>
       <c r="T32">
-        <v>1.247453414266205</v>
+        <v>1.262551537704862</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>20.55880530270234</v>
+        <v>19.89561803487323</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08148579229200814</v>
+        <v>0.08133107159760762</v>
       </c>
       <c r="C33">
-        <v>64700.82972981812</v>
+        <v>63830.15138314702</v>
       </c>
       <c r="D33">
-        <v>85672.11172981812</v>
+        <v>85736.05538314702</v>
       </c>
       <c r="E33">
-        <v>-622.7180000000008</v>
+        <v>311.9039999999986</v>
       </c>
       <c r="F33">
-        <v>28973.282</v>
+        <v>29907.904</v>
       </c>
       <c r="G33">
         <v>8002</v>
@@ -3999,28 +3999,28 @@
         <v>28995</v>
       </c>
       <c r="M33">
-        <v>1457.3560846</v>
+        <v>1504.3675712</v>
       </c>
       <c r="N33">
-        <v>27537.6439154</v>
+        <v>27490.6324288</v>
       </c>
       <c r="O33">
-        <v>6058.281661388</v>
+        <v>6047.939134336</v>
       </c>
       <c r="P33">
-        <v>21479.362254012</v>
+        <v>21442.693294464</v>
       </c>
       <c r="Q33">
-        <v>31265.362254012</v>
+        <v>31228.693294464</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1004684815826205</v>
+        <v>0.1011414582317759</v>
       </c>
       <c r="T33">
-        <v>1.262551537704862</v>
+        <v>1.278093723597596</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>19.89561803487323</v>
+        <v>19.27387997128345</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08133107159760762</v>
+        <v>0.08117635090320707</v>
       </c>
       <c r="C34">
-        <v>63830.15138314702</v>
+        <v>62959.5685598563</v>
       </c>
       <c r="D34">
-        <v>85736.05538314702</v>
+        <v>85800.0945598563</v>
       </c>
       <c r="E34">
-        <v>311.9039999999986</v>
+        <v>1246.526000000002</v>
       </c>
       <c r="F34">
-        <v>29907.904</v>
+        <v>30842.526</v>
       </c>
       <c r="G34">
         <v>8002</v>
@@ -4081,28 +4081,28 @@
         <v>28995</v>
       </c>
       <c r="M34">
-        <v>1504.3675712</v>
+        <v>1551.3790578</v>
       </c>
       <c r="N34">
-        <v>27490.6324288</v>
+        <v>27443.6209422</v>
       </c>
       <c r="O34">
-        <v>6047.939134336</v>
+        <v>6037.596607284</v>
       </c>
       <c r="P34">
-        <v>21442.693294464</v>
+        <v>21406.024334916</v>
       </c>
       <c r="Q34">
-        <v>31228.693294464</v>
+        <v>31192.024334916</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1011414582317759</v>
+        <v>0.10183452373613</v>
       </c>
       <c r="T34">
-        <v>1.278093723597596</v>
+        <v>1.294099855337875</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>19.27387997128345</v>
+        <v>18.68982300245667</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08117635090320707</v>
+        <v>0.08102163020880654</v>
       </c>
       <c r="C35">
-        <v>62959.5685598563</v>
+        <v>62089.08147415493</v>
       </c>
       <c r="D35">
-        <v>85800.0945598563</v>
+        <v>85864.22947415493</v>
       </c>
       <c r="E35">
-        <v>1246.526000000002</v>
+        <v>2181.148000000001</v>
       </c>
       <c r="F35">
-        <v>30842.526</v>
+        <v>31777.148</v>
       </c>
       <c r="G35">
         <v>8002</v>
@@ -4163,28 +4163,28 @@
         <v>28995</v>
       </c>
       <c r="M35">
-        <v>1551.3790578</v>
+        <v>1598.3905444</v>
       </c>
       <c r="N35">
-        <v>27443.6209422</v>
+        <v>27396.6094556</v>
       </c>
       <c r="O35">
-        <v>6037.596607284</v>
+        <v>6027.254080232</v>
       </c>
       <c r="P35">
-        <v>21406.024334916</v>
+        <v>21369.355375368</v>
       </c>
       <c r="Q35">
-        <v>31192.024334916</v>
+        <v>31155.355375368</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.10183452373613</v>
+        <v>0.1025485912254645</v>
       </c>
       <c r="T35">
-        <v>1.294099855337875</v>
+        <v>1.310591021373313</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>18.68982300245667</v>
+        <v>18.14012232591383</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08102163020880654</v>
+        <v>0.080866909514406</v>
       </c>
       <c r="C36">
-        <v>62089.08147415493</v>
+        <v>61218.69034089286</v>
       </c>
       <c r="D36">
-        <v>85864.22947415493</v>
+        <v>85928.46034089287</v>
       </c>
       <c r="E36">
-        <v>2181.148000000001</v>
+        <v>3115.77</v>
       </c>
       <c r="F36">
-        <v>31777.148</v>
+        <v>32711.77</v>
       </c>
       <c r="G36">
         <v>8002</v>
@@ -4245,28 +4245,28 @@
         <v>28995</v>
       </c>
       <c r="M36">
-        <v>1598.3905444</v>
+        <v>1645.402031</v>
       </c>
       <c r="N36">
-        <v>27396.6094556</v>
+        <v>27349.597969</v>
       </c>
       <c r="O36">
-        <v>6027.254080232</v>
+        <v>6016.91155318</v>
       </c>
       <c r="P36">
-        <v>21369.355375368</v>
+        <v>21332.68641582</v>
       </c>
       <c r="Q36">
-        <v>31155.355375368</v>
+        <v>31118.68641582</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1025485912254645</v>
+        <v>0.1032846300221631</v>
       </c>
       <c r="T36">
-        <v>1.310591021373313</v>
+        <v>1.32758960790215</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>18.14012232591383</v>
+        <v>17.62183311660201</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.080866909514406</v>
+        <v>0.08071218882000546</v>
       </c>
       <c r="C37">
-        <v>61218.69034089286</v>
+        <v>60348.39537556341</v>
       </c>
       <c r="D37">
-        <v>85928.46034089287</v>
+        <v>85992.78737556341</v>
       </c>
       <c r="E37">
-        <v>3115.77</v>
+        <v>4050.392</v>
       </c>
       <c r="F37">
-        <v>32711.77</v>
+        <v>33646.392</v>
       </c>
       <c r="G37">
         <v>8002</v>
@@ -4327,28 +4327,28 @@
         <v>28995</v>
       </c>
       <c r="M37">
-        <v>1645.402031</v>
+        <v>1692.4135176</v>
       </c>
       <c r="N37">
-        <v>27349.597969</v>
+        <v>27302.5864824</v>
       </c>
       <c r="O37">
-        <v>6016.91155318</v>
+        <v>6006.569026128001</v>
       </c>
       <c r="P37">
-        <v>21332.68641582</v>
+        <v>21296.017456272</v>
       </c>
       <c r="Q37">
-        <v>31118.68641582</v>
+        <v>31082.017456272</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1032846300221631</v>
+        <v>0.1040436700312586</v>
       </c>
       <c r="T37">
-        <v>1.32758960790215</v>
+        <v>1.345119400260013</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>17.62183311660201</v>
+        <v>17.13233775225195</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08071218882000547</v>
+        <v>0.08055746812560495</v>
       </c>
       <c r="C38">
-        <v>60348.39537556341</v>
+        <v>59478.19679430562</v>
       </c>
       <c r="D38">
-        <v>85992.78737556341</v>
+        <v>86057.21079430562</v>
       </c>
       <c r="E38">
-        <v>4050.392</v>
+        <v>4985.013999999996</v>
       </c>
       <c r="F38">
-        <v>33646.392</v>
+        <v>34581.014</v>
       </c>
       <c r="G38">
         <v>8002</v>
@@ -4409,28 +4409,28 @@
         <v>28995</v>
       </c>
       <c r="M38">
-        <v>1692.4135176</v>
+        <v>1739.4250042</v>
       </c>
       <c r="N38">
-        <v>27302.5864824</v>
+        <v>27255.5749958</v>
       </c>
       <c r="O38">
-        <v>6006.569026128001</v>
+        <v>5996.226499076</v>
       </c>
       <c r="P38">
-        <v>21296.017456272</v>
+        <v>21259.348496724</v>
       </c>
       <c r="Q38">
-        <v>31082.017456272</v>
+        <v>31045.348496724</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1040436700312586</v>
+        <v>0.1048268065485793</v>
       </c>
       <c r="T38">
-        <v>1.345119400260013</v>
+        <v>1.36320569396257</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>17.13233775225195</v>
+        <v>16.66930159678569</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08055746812560495</v>
+        <v>0.0804027474312044</v>
       </c>
       <c r="C39">
-        <v>59478.19679430562</v>
+        <v>58608.09481390679</v>
       </c>
       <c r="D39">
-        <v>86057.21079430562</v>
+        <v>86121.73081390679</v>
       </c>
       <c r="E39">
-        <v>4985.013999999996</v>
+        <v>5919.635999999999</v>
       </c>
       <c r="F39">
-        <v>34581.014</v>
+        <v>35515.636</v>
       </c>
       <c r="G39">
         <v>8002</v>
@@ -4491,28 +4491,28 @@
         <v>28995</v>
       </c>
       <c r="M39">
-        <v>1739.4250042</v>
+        <v>1786.4364908</v>
       </c>
       <c r="N39">
-        <v>27255.5749958</v>
+        <v>27208.5635092</v>
       </c>
       <c r="O39">
-        <v>5996.226499076</v>
+        <v>5985.883972024</v>
       </c>
       <c r="P39">
-        <v>21259.348496724</v>
+        <v>21222.679537176</v>
       </c>
       <c r="Q39">
-        <v>31045.348496724</v>
+        <v>31008.679537176</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1048268065485793</v>
+        <v>0.1056352055342007</v>
       </c>
       <c r="T39">
-        <v>1.36320569396257</v>
+        <v>1.381875416494242</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>16.66930159678569</v>
+        <v>16.23063576529132</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0804027474312044</v>
+        <v>0.08024802673680387</v>
       </c>
       <c r="C40">
-        <v>58608.09481390679</v>
+        <v>57738.08965180475</v>
       </c>
       <c r="D40">
-        <v>86121.73081390679</v>
+        <v>86186.34765180475</v>
       </c>
       <c r="E40">
-        <v>5919.635999999999</v>
+        <v>6854.258000000002</v>
       </c>
       <c r="F40">
-        <v>35515.636</v>
+        <v>36450.258</v>
       </c>
       <c r="G40">
         <v>8002</v>
@@ -4573,28 +4573,28 @@
         <v>28995</v>
       </c>
       <c r="M40">
-        <v>1786.4364908</v>
+        <v>1833.4479774</v>
       </c>
       <c r="N40">
-        <v>27208.5635092</v>
+        <v>27161.5520226</v>
       </c>
       <c r="O40">
-        <v>5985.883972024</v>
+        <v>5975.541444972</v>
       </c>
       <c r="P40">
-        <v>21222.679537176</v>
+        <v>21186.010577628</v>
       </c>
       <c r="Q40">
-        <v>31008.679537176</v>
+        <v>30972.010577628</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1056352055342007</v>
+        <v>0.1064701094045965</v>
       </c>
       <c r="T40">
-        <v>1.381875416494242</v>
+        <v>1.401157261076132</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>16.23063576529132</v>
+        <v>15.81446561746334</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08024802673680387</v>
+        <v>0.08009330604240333</v>
       </c>
       <c r="C41">
-        <v>57738.08965180475</v>
+        <v>56868.18152609045</v>
       </c>
       <c r="D41">
-        <v>86186.34765180475</v>
+        <v>86251.06152609045</v>
       </c>
       <c r="E41">
-        <v>6854.258000000002</v>
+        <v>7788.879999999997</v>
       </c>
       <c r="F41">
-        <v>36450.258</v>
+        <v>37384.88</v>
       </c>
       <c r="G41">
         <v>8002</v>
@@ -4655,28 +4655,28 @@
         <v>28995</v>
       </c>
       <c r="M41">
-        <v>1833.4479774</v>
+        <v>1880.459464</v>
       </c>
       <c r="N41">
-        <v>27161.5520226</v>
+        <v>27114.540536</v>
       </c>
       <c r="O41">
-        <v>5975.541444972</v>
+        <v>5965.19891792</v>
       </c>
       <c r="P41">
-        <v>21186.010577628</v>
+        <v>21149.34161808</v>
       </c>
       <c r="Q41">
-        <v>30972.010577628</v>
+        <v>30935.34161808</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1064701094045965</v>
+        <v>0.1073328434040056</v>
       </c>
       <c r="T41">
-        <v>1.401157261076132</v>
+        <v>1.421081833810752</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>15.81446561746334</v>
+        <v>15.41910397702676</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08009330604240333</v>
+        <v>0.0799385853480028</v>
       </c>
       <c r="C42">
-        <v>56868.18152609045</v>
+        <v>55998.37065551035</v>
       </c>
       <c r="D42">
-        <v>86251.06152609045</v>
+        <v>86315.87265551035</v>
       </c>
       <c r="E42">
-        <v>7788.879999999997</v>
+        <v>8723.502</v>
       </c>
       <c r="F42">
-        <v>37384.88</v>
+        <v>38319.502</v>
       </c>
       <c r="G42">
         <v>8002</v>
@@ -4737,28 +4737,28 @@
         <v>28995</v>
       </c>
       <c r="M42">
-        <v>1880.459464</v>
+        <v>1927.4709506</v>
       </c>
       <c r="N42">
-        <v>27114.540536</v>
+        <v>27067.5290494</v>
       </c>
       <c r="O42">
-        <v>5965.19891792</v>
+        <v>5954.856390868</v>
       </c>
       <c r="P42">
-        <v>21149.34161808</v>
+        <v>21112.672658532</v>
       </c>
       <c r="Q42">
-        <v>30935.34161808</v>
+        <v>30898.672658532</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1073328434040056</v>
+        <v>0.1082248226237336</v>
       </c>
       <c r="T42">
-        <v>1.421081833810752</v>
+        <v>1.441681815790613</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>15.41910397702676</v>
+        <v>15.04302827027001</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0799385853480028</v>
+        <v>0.07978386465360225</v>
       </c>
       <c r="C43">
-        <v>55998.37065551035</v>
+        <v>55128.65725946888</v>
       </c>
       <c r="D43">
-        <v>86315.87265551035</v>
+        <v>86380.78125946889</v>
       </c>
       <c r="E43">
-        <v>8723.502</v>
+        <v>9658.124000000003</v>
       </c>
       <c r="F43">
-        <v>38319.502</v>
+        <v>39254.124</v>
       </c>
       <c r="G43">
         <v>8002</v>
@@ -4819,28 +4819,28 @@
         <v>28995</v>
       </c>
       <c r="M43">
-        <v>1927.4709506</v>
+        <v>1974.4824372</v>
       </c>
       <c r="N43">
-        <v>27067.5290494</v>
+        <v>27020.5175628</v>
       </c>
       <c r="O43">
-        <v>5954.856390868</v>
+        <v>5944.513863816</v>
       </c>
       <c r="P43">
-        <v>21112.672658532</v>
+        <v>21076.003698984</v>
       </c>
       <c r="Q43">
-        <v>30898.672658532</v>
+        <v>30862.003698984</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1082248226237336</v>
+        <v>0.1091475597475901</v>
       </c>
       <c r="T43">
-        <v>1.441681815790613</v>
+        <v>1.462992141976677</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>15.04302827027001</v>
+        <v>14.68486093050167</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07978386465360227</v>
+        <v>0.07962914395920175</v>
       </c>
       <c r="C44">
-        <v>55128.65725946888</v>
+        <v>54259.04155803091</v>
       </c>
       <c r="D44">
-        <v>86380.78125946887</v>
+        <v>86445.7875580309</v>
       </c>
       <c r="E44">
-        <v>9658.123999999996</v>
+        <v>10592.746</v>
       </c>
       <c r="F44">
-        <v>39254.124</v>
+        <v>40188.746</v>
       </c>
       <c r="G44">
         <v>8002</v>
@@ -4901,28 +4901,28 @@
         <v>28995</v>
       </c>
       <c r="M44">
-        <v>1974.4824372</v>
+        <v>2021.4939238</v>
       </c>
       <c r="N44">
-        <v>27020.5175628</v>
+        <v>26973.5060762</v>
       </c>
       <c r="O44">
-        <v>5944.513863816</v>
+        <v>5934.171336764</v>
       </c>
       <c r="P44">
-        <v>21076.003698984</v>
+        <v>21039.334739436</v>
       </c>
       <c r="Q44">
-        <v>30862.003698984</v>
+        <v>30825.334739436</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1091475597475901</v>
+        <v>0.1101026736126346</v>
       </c>
       <c r="T44">
-        <v>1.462992141976677</v>
+        <v>1.485050198906111</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>14.68486093050167</v>
+        <v>14.34335253676907</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07962914395920175</v>
+        <v>0.07947442326480121</v>
       </c>
       <c r="C45">
-        <v>54259.04155803091</v>
+        <v>53389.52377192429</v>
       </c>
       <c r="D45">
-        <v>86445.7875580309</v>
+        <v>86510.89177192429</v>
       </c>
       <c r="E45">
-        <v>10592.746</v>
+        <v>11527.368</v>
       </c>
       <c r="F45">
-        <v>40188.746</v>
+        <v>41123.368</v>
       </c>
       <c r="G45">
         <v>8002</v>
@@ -4983,28 +4983,28 @@
         <v>28995</v>
       </c>
       <c r="M45">
-        <v>2021.4939238</v>
+        <v>2068.5054104</v>
       </c>
       <c r="N45">
-        <v>26973.5060762</v>
+        <v>26926.4945896</v>
       </c>
       <c r="O45">
-        <v>5934.171336764</v>
+        <v>5923.828809711999</v>
       </c>
       <c r="P45">
-        <v>21039.334739436</v>
+        <v>21002.665779888</v>
       </c>
       <c r="Q45">
-        <v>30825.334739436</v>
+        <v>30788.665779888</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1101026736126346</v>
+        <v>0.111091898687145</v>
       </c>
       <c r="T45">
-        <v>1.485050198906111</v>
+        <v>1.507896043583026</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>14.34335253676907</v>
+        <v>14.0173672518425</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07947442326480121</v>
+        <v>0.07931970257040066</v>
       </c>
       <c r="C46">
-        <v>53389.52377192429</v>
+        <v>52520.10412254229</v>
       </c>
       <c r="D46">
-        <v>86510.89177192429</v>
+        <v>86576.09412254229</v>
       </c>
       <c r="E46">
-        <v>11527.368</v>
+        <v>12461.99</v>
       </c>
       <c r="F46">
-        <v>41123.368</v>
+        <v>42057.99</v>
       </c>
       <c r="G46">
         <v>8002</v>
@@ -5065,28 +5065,28 @@
         <v>28995</v>
       </c>
       <c r="M46">
-        <v>2068.5054104</v>
+        <v>2115.516897</v>
       </c>
       <c r="N46">
-        <v>26926.4945896</v>
+        <v>26879.483103</v>
       </c>
       <c r="O46">
-        <v>5923.828809711999</v>
+        <v>5913.48628266</v>
       </c>
       <c r="P46">
-        <v>21002.665779888</v>
+        <v>20965.99682034</v>
       </c>
       <c r="Q46">
-        <v>30788.665779888</v>
+        <v>30751.99682034</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.111091898687145</v>
+        <v>0.1121170955825466</v>
       </c>
       <c r="T46">
-        <v>1.507896043583026</v>
+        <v>1.531572646248191</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>14.0173672518425</v>
+        <v>13.70587020180156</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07931970257040066</v>
+        <v>0.07916498187600013</v>
       </c>
       <c r="C47">
-        <v>52520.10412254229</v>
+        <v>51650.78283194612</v>
       </c>
       <c r="D47">
-        <v>86576.09412254229</v>
+        <v>86641.39483194612</v>
       </c>
       <c r="E47">
-        <v>12461.99</v>
+        <v>13396.612</v>
       </c>
       <c r="F47">
-        <v>42057.99</v>
+        <v>42992.612</v>
       </c>
       <c r="G47">
         <v>8002</v>
@@ -5147,28 +5147,28 @@
         <v>28995</v>
       </c>
       <c r="M47">
-        <v>2115.516897</v>
+        <v>2162.5283836</v>
       </c>
       <c r="N47">
-        <v>26879.483103</v>
+        <v>26832.4716164</v>
       </c>
       <c r="O47">
-        <v>5913.48628266</v>
+        <v>5903.143755608</v>
       </c>
       <c r="P47">
-        <v>20965.99682034</v>
+        <v>20929.327860792</v>
       </c>
       <c r="Q47">
-        <v>30751.99682034</v>
+        <v>30715.327860792</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1121170955825466</v>
+        <v>0.1131802627333336</v>
       </c>
       <c r="T47">
-        <v>1.531572646248191</v>
+        <v>1.556126160123177</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>13.70587020180156</v>
+        <v>13.4079165017624</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07916498187600013</v>
+        <v>0.07901026118159961</v>
       </c>
       <c r="C48">
-        <v>51650.78283194612</v>
+        <v>50781.56012286747</v>
       </c>
       <c r="D48">
-        <v>86641.39483194612</v>
+        <v>86706.79412286748</v>
       </c>
       <c r="E48">
-        <v>13396.612</v>
+        <v>14331.234</v>
       </c>
       <c r="F48">
-        <v>42992.612</v>
+        <v>43927.234</v>
       </c>
       <c r="G48">
         <v>8002</v>
@@ -5229,28 +5229,28 @@
         <v>28995</v>
       </c>
       <c r="M48">
-        <v>2162.5283836</v>
+        <v>2209.5398702</v>
       </c>
       <c r="N48">
-        <v>26832.4716164</v>
+        <v>26785.4601298</v>
       </c>
       <c r="O48">
-        <v>5903.143755608</v>
+        <v>5892.801228556</v>
       </c>
       <c r="P48">
-        <v>20929.327860792</v>
+        <v>20892.658901244</v>
       </c>
       <c r="Q48">
-        <v>30715.327860792</v>
+        <v>30678.658901244</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1131802627333336</v>
+        <v>0.1142835493992445</v>
       </c>
       <c r="T48">
-        <v>1.556126160123177</v>
+        <v>1.58160622169156</v>
       </c>
       <c r="U48">
         <v>0.0503</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>13.4079165017624</v>
+        <v>13.12264168257596</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07901026118159961</v>
+        <v>0.07885554048719906</v>
       </c>
       <c r="C49">
-        <v>50781.56012286747</v>
+        <v>49912.43621871108</v>
       </c>
       <c r="D49">
-        <v>86706.79412286748</v>
+        <v>86772.29221871108</v>
       </c>
       <c r="E49">
-        <v>14331.234</v>
+        <v>15265.856</v>
       </c>
       <c r="F49">
-        <v>43927.234</v>
+        <v>44861.856</v>
       </c>
       <c r="G49">
         <v>8002</v>
@@ -5311,28 +5311,28 @@
         <v>28995</v>
       </c>
       <c r="M49">
-        <v>2209.5398702</v>
+        <v>2256.5513568</v>
       </c>
       <c r="N49">
-        <v>26785.4601298</v>
+        <v>26738.4486432</v>
       </c>
       <c r="O49">
-        <v>5892.801228556</v>
+        <v>5882.458701504001</v>
       </c>
       <c r="P49">
-        <v>20892.658901244</v>
+        <v>20855.989941696</v>
       </c>
       <c r="Q49">
-        <v>30678.658901244</v>
+        <v>30641.989941696</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1142835493992445</v>
+        <v>0.1154292701676905</v>
       </c>
       <c r="T49">
-        <v>1.58160622169156</v>
+        <v>1.608066285627956</v>
       </c>
       <c r="U49">
         <v>0.0503</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>13.12264168257596</v>
+        <v>12.84925331418897</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07885554048719906</v>
+        <v>0.07870081979279853</v>
       </c>
       <c r="C50">
-        <v>49912.43621871108</v>
+        <v>49043.41134355713</v>
       </c>
       <c r="D50">
-        <v>86772.29221871108</v>
+        <v>86837.88934355712</v>
       </c>
       <c r="E50">
-        <v>15265.856</v>
+        <v>16200.478</v>
       </c>
       <c r="F50">
-        <v>44861.856</v>
+        <v>45796.478</v>
       </c>
       <c r="G50">
         <v>8002</v>
@@ -5393,28 +5393,28 @@
         <v>28995</v>
       </c>
       <c r="M50">
-        <v>2256.5513568</v>
+        <v>2303.5628434</v>
       </c>
       <c r="N50">
-        <v>26738.4486432</v>
+        <v>26691.4371566</v>
       </c>
       <c r="O50">
-        <v>5882.458701504001</v>
+        <v>5872.116174452</v>
       </c>
       <c r="P50">
-        <v>20855.989941696</v>
+        <v>20819.320982148</v>
       </c>
       <c r="Q50">
-        <v>30641.989941696</v>
+        <v>30605.320982148</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1154292701676905</v>
+        <v>0.1166199211623501</v>
       </c>
       <c r="T50">
-        <v>1.608066285627956</v>
+        <v>1.635563999130486</v>
       </c>
       <c r="U50">
         <v>0.0503</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>12.84925331418897</v>
+        <v>12.58702365471572</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07870081979279853</v>
+        <v>0.07854609909839799</v>
       </c>
       <c r="C51">
-        <v>49043.41134355713</v>
+        <v>48174.48572216402</v>
       </c>
       <c r="D51">
-        <v>86837.88934355712</v>
+        <v>86903.58572216402</v>
       </c>
       <c r="E51">
-        <v>16200.478</v>
+        <v>17135.1</v>
       </c>
       <c r="F51">
-        <v>45796.478</v>
+        <v>46731.1</v>
       </c>
       <c r="G51">
         <v>8002</v>
@@ -5475,28 +5475,28 @@
         <v>28995</v>
       </c>
       <c r="M51">
-        <v>2303.5628434</v>
+        <v>2350.57433</v>
       </c>
       <c r="N51">
-        <v>26691.4371566</v>
+        <v>26644.42567</v>
       </c>
       <c r="O51">
-        <v>5872.116174452</v>
+        <v>5861.7736474</v>
       </c>
       <c r="P51">
-        <v>20819.320982148</v>
+        <v>20782.6520226</v>
       </c>
       <c r="Q51">
-        <v>30605.320982148</v>
+        <v>30568.6520226</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1166199211623501</v>
+        <v>0.117858198196796</v>
       </c>
       <c r="T51">
-        <v>1.635563999130486</v>
+        <v>1.664161621173118</v>
       </c>
       <c r="U51">
         <v>0.0503</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>12.58702365471572</v>
+        <v>12.3352831816214</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07854609909839799</v>
+        <v>0.07839137840399746</v>
       </c>
       <c r="C52">
-        <v>48174.48572216402</v>
+        <v>47305.65957997072</v>
       </c>
       <c r="D52">
-        <v>86903.58572216402</v>
+        <v>86969.38157997072</v>
       </c>
       <c r="E52">
-        <v>17135.1</v>
+        <v>18069.722</v>
       </c>
       <c r="F52">
-        <v>46731.1</v>
+        <v>47665.722</v>
       </c>
       <c r="G52">
         <v>8002</v>
@@ -5557,28 +5557,28 @@
         <v>28995</v>
       </c>
       <c r="M52">
-        <v>2350.57433</v>
+        <v>2397.5858166</v>
       </c>
       <c r="N52">
-        <v>26644.42567</v>
+        <v>26597.4141834</v>
       </c>
       <c r="O52">
-        <v>5861.7736474</v>
+        <v>5851.431120348</v>
       </c>
       <c r="P52">
-        <v>20782.6520226</v>
+        <v>20745.983063052</v>
       </c>
       <c r="Q52">
-        <v>30568.6520226</v>
+        <v>30531.983063052</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.117858198196796</v>
+        <v>0.1191470171510152</v>
       </c>
       <c r="T52">
-        <v>1.664161621173118</v>
+        <v>1.69392649309504</v>
       </c>
       <c r="U52">
         <v>0.0503</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>12.3352831816214</v>
+        <v>12.09341488394255</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07839137840399746</v>
+        <v>0.07823665770959692</v>
       </c>
       <c r="C53">
-        <v>47305.65957997072</v>
+        <v>46436.93314309954</v>
       </c>
       <c r="D53">
-        <v>86969.38157997072</v>
+        <v>87035.27714309953</v>
       </c>
       <c r="E53">
-        <v>18069.722</v>
+        <v>19004.344</v>
       </c>
       <c r="F53">
-        <v>47665.722</v>
+        <v>48600.344</v>
       </c>
       <c r="G53">
         <v>8002</v>
@@ -5639,28 +5639,28 @@
         <v>28995</v>
       </c>
       <c r="M53">
-        <v>2397.5858166</v>
+        <v>2444.5973032</v>
       </c>
       <c r="N53">
-        <v>26597.4141834</v>
+        <v>26550.4026968</v>
       </c>
       <c r="O53">
-        <v>5851.431120348</v>
+        <v>5841.088593296</v>
       </c>
       <c r="P53">
-        <v>20745.983063052</v>
+        <v>20709.314103504</v>
       </c>
       <c r="Q53">
-        <v>30531.983063052</v>
+        <v>30495.314103504</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1191470171510152</v>
+        <v>0.1204895368949936</v>
       </c>
       <c r="T53">
-        <v>1.69392649309504</v>
+        <v>1.724931568013709</v>
       </c>
       <c r="U53">
         <v>0.0503</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>12.09341488394255</v>
+        <v>11.86084921309751</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07823665770959692</v>
+        <v>0.07808193701519639</v>
       </c>
       <c r="C54">
-        <v>46436.93314309954</v>
+        <v>45568.30663835855</v>
       </c>
       <c r="D54">
-        <v>87035.27714309953</v>
+        <v>87101.27263835855</v>
       </c>
       <c r="E54">
-        <v>19004.344</v>
+        <v>19938.966</v>
       </c>
       <c r="F54">
-        <v>48600.344</v>
+        <v>49534.966</v>
       </c>
       <c r="G54">
         <v>8002</v>
@@ -5721,28 +5721,28 @@
         <v>28995</v>
       </c>
       <c r="M54">
-        <v>2444.5973032</v>
+        <v>2491.6087898</v>
       </c>
       <c r="N54">
-        <v>26550.4026968</v>
+        <v>26503.3912102</v>
       </c>
       <c r="O54">
-        <v>5841.088593296</v>
+        <v>5830.746066244</v>
       </c>
       <c r="P54">
-        <v>20709.314103504</v>
+        <v>20672.645143956</v>
       </c>
       <c r="Q54">
-        <v>30495.314103504</v>
+        <v>30458.645143956</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1204895368949936</v>
+        <v>0.1218891851387157</v>
       </c>
       <c r="T54">
-        <v>1.724931568013709</v>
+        <v>1.757256007822534</v>
       </c>
       <c r="U54">
         <v>0.0503</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>11.86084921309751</v>
+        <v>11.63705960530321</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07808193701519639</v>
+        <v>0.07792721632079586</v>
       </c>
       <c r="C55">
-        <v>45568.30663835855</v>
+        <v>44699.78029324432</v>
       </c>
       <c r="D55">
-        <v>87101.27263835855</v>
+        <v>87167.36829324432</v>
       </c>
       <c r="E55">
-        <v>19938.966</v>
+        <v>20873.588</v>
       </c>
       <c r="F55">
-        <v>49534.966</v>
+        <v>50469.588</v>
       </c>
       <c r="G55">
         <v>8002</v>
@@ -5803,28 +5803,28 @@
         <v>28995</v>
       </c>
       <c r="M55">
-        <v>2491.6087898</v>
+        <v>2538.6202764</v>
       </c>
       <c r="N55">
-        <v>26503.3912102</v>
+        <v>26456.3797236</v>
       </c>
       <c r="O55">
-        <v>5830.746066244</v>
+        <v>5820.403539192</v>
       </c>
       <c r="P55">
-        <v>20672.645143956</v>
+        <v>20635.976184408</v>
       </c>
       <c r="Q55">
-        <v>30458.645143956</v>
+        <v>30421.976184408</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1218891851387157</v>
+        <v>0.1233496876539041</v>
       </c>
       <c r="T55">
-        <v>1.757256007822534</v>
+        <v>1.79098585805783</v>
       </c>
       <c r="U55">
         <v>0.0503</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>11.63705960530321</v>
+        <v>11.4215585015013</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07792721632079586</v>
+        <v>0.07777249562639532</v>
       </c>
       <c r="C56">
-        <v>44699.78029324432</v>
+        <v>43831.35433594447</v>
       </c>
       <c r="D56">
-        <v>87167.36829324432</v>
+        <v>87233.56433594447</v>
       </c>
       <c r="E56">
-        <v>20873.588</v>
+        <v>21808.21</v>
       </c>
       <c r="F56">
-        <v>50469.588</v>
+        <v>51404.21</v>
       </c>
       <c r="G56">
         <v>8002</v>
@@ -5885,28 +5885,28 @@
         <v>28995</v>
       </c>
       <c r="M56">
-        <v>2538.6202764</v>
+        <v>2585.631763</v>
       </c>
       <c r="N56">
-        <v>26456.3797236</v>
+        <v>26409.368237</v>
       </c>
       <c r="O56">
-        <v>5820.403539192</v>
+        <v>5810.06101214</v>
       </c>
       <c r="P56">
-        <v>20635.976184408</v>
+        <v>20599.30722486</v>
       </c>
       <c r="Q56">
-        <v>30421.976184408</v>
+        <v>30385.30722486</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1233496876539041</v>
+        <v>0.1248751013919896</v>
       </c>
       <c r="T56">
-        <v>1.79098585805783</v>
+        <v>1.826214812748028</v>
       </c>
       <c r="U56">
         <v>0.0503</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>11.4215585015013</v>
+        <v>11.213893801474</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07777249562639532</v>
+        <v>0.07761777493199477</v>
       </c>
       <c r="C57">
-        <v>43831.35433594447</v>
+        <v>42963.02899534023</v>
       </c>
       <c r="D57">
-        <v>87233.56433594447</v>
+        <v>87299.86099534023</v>
       </c>
       <c r="E57">
-        <v>21808.21</v>
+        <v>22742.832</v>
       </c>
       <c r="F57">
-        <v>51404.21</v>
+        <v>52338.832</v>
       </c>
       <c r="G57">
         <v>8002</v>
@@ -5967,28 +5967,28 @@
         <v>28995</v>
       </c>
       <c r="M57">
-        <v>2585.631763</v>
+        <v>2632.6432496</v>
       </c>
       <c r="N57">
-        <v>26409.368237</v>
+        <v>26362.3567504</v>
       </c>
       <c r="O57">
-        <v>5810.06101214</v>
+        <v>5799.718485088</v>
       </c>
       <c r="P57">
-        <v>20599.30722486</v>
+        <v>20562.638265312</v>
       </c>
       <c r="Q57">
-        <v>30385.30722486</v>
+        <v>30348.638265312</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1248751013919896</v>
+        <v>0.12646985211817</v>
       </c>
       <c r="T57">
-        <v>1.826214812748028</v>
+        <v>1.863045083560508</v>
       </c>
       <c r="U57">
         <v>0.0503</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>11.213893801474</v>
+        <v>11.01364569787625</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07761777493199477</v>
+        <v>0.07746305423759425</v>
       </c>
       <c r="C58">
-        <v>42963.02899534023</v>
+        <v>42094.80450100924</v>
       </c>
       <c r="D58">
-        <v>87299.86099534023</v>
+        <v>87366.25850100924</v>
       </c>
       <c r="E58">
-        <v>22742.832</v>
+        <v>23677.45400000001</v>
       </c>
       <c r="F58">
-        <v>52338.832</v>
+        <v>53273.45400000001</v>
       </c>
       <c r="G58">
         <v>8002</v>
@@ -6049,28 +6049,28 @@
         <v>28995</v>
       </c>
       <c r="M58">
-        <v>2632.6432496</v>
+        <v>2679.6547362</v>
       </c>
       <c r="N58">
-        <v>26362.3567504</v>
+        <v>26315.3452638</v>
       </c>
       <c r="O58">
-        <v>5799.718485088</v>
+        <v>5789.375958036</v>
       </c>
       <c r="P58">
-        <v>20562.638265312</v>
+        <v>20525.969305764</v>
       </c>
       <c r="Q58">
-        <v>30348.638265312</v>
+        <v>30311.969305764</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.12646985211817</v>
+        <v>0.1281387772967308</v>
       </c>
       <c r="T58">
-        <v>1.863045083560508</v>
+        <v>1.901588390224731</v>
       </c>
       <c r="U58">
         <v>0.0503</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>11.01364569787625</v>
+        <v>10.82042384352755</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07746305423759425</v>
+        <v>0.07730833354319372</v>
       </c>
       <c r="C59">
-        <v>42094.80450100924</v>
+        <v>41226.68108322808</v>
       </c>
       <c r="D59">
-        <v>87366.25850100924</v>
+        <v>87432.75708322809</v>
       </c>
       <c r="E59">
-        <v>23677.45400000001</v>
+        <v>24612.07600000001</v>
       </c>
       <c r="F59">
-        <v>53273.45400000001</v>
+        <v>54208.07600000001</v>
       </c>
       <c r="G59">
         <v>8002</v>
@@ -6131,28 +6131,28 @@
         <v>28995</v>
       </c>
       <c r="M59">
-        <v>2679.6547362</v>
+        <v>2726.6662228</v>
       </c>
       <c r="N59">
-        <v>26315.3452638</v>
+        <v>26268.3337772</v>
       </c>
       <c r="O59">
-        <v>5789.375958036</v>
+        <v>5779.033430984</v>
       </c>
       <c r="P59">
-        <v>20525.969305764</v>
+        <v>20489.300346216</v>
       </c>
       <c r="Q59">
-        <v>30311.969305764</v>
+        <v>30275.300346216</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1281387772967308</v>
+        <v>0.1298871751028422</v>
       </c>
       <c r="T59">
-        <v>1.901588390224731</v>
+        <v>1.941967092444393</v>
       </c>
       <c r="U59">
         <v>0.0503</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>10.82042384352755</v>
+        <v>10.63386481174259</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07730833354319372</v>
+        <v>0.07715361284879318</v>
       </c>
       <c r="C60">
-        <v>41226.6810832281</v>
+        <v>40358.65897297495</v>
       </c>
       <c r="D60">
-        <v>87432.75708322809</v>
+        <v>87499.35697297494</v>
       </c>
       <c r="E60">
-        <v>24612.07599999999</v>
+        <v>25546.698</v>
       </c>
       <c r="F60">
-        <v>54208.07599999999</v>
+        <v>55142.698</v>
       </c>
       <c r="G60">
         <v>8002</v>
@@ -6213,28 +6213,28 @@
         <v>28995</v>
       </c>
       <c r="M60">
-        <v>2726.6662228</v>
+        <v>2773.6777094</v>
       </c>
       <c r="N60">
-        <v>26268.3337772</v>
+        <v>26221.3222906</v>
       </c>
       <c r="O60">
-        <v>5779.033430984</v>
+        <v>5768.690903932</v>
       </c>
       <c r="P60">
-        <v>20489.300346216</v>
+        <v>20452.631386668</v>
       </c>
       <c r="Q60">
-        <v>30275.300346216</v>
+        <v>30238.631386668</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1298871751028422</v>
+        <v>0.1317208606068126</v>
       </c>
       <c r="T60">
-        <v>1.941967092444392</v>
+        <v>1.984315487455257</v>
       </c>
       <c r="U60">
         <v>0.0503</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>10.63386481174259</v>
+        <v>10.45362981493339</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07715361284879318</v>
+        <v>0.07699889215439266</v>
       </c>
       <c r="C61">
-        <v>40358.65897297495</v>
+        <v>39490.73840193233</v>
       </c>
       <c r="D61">
-        <v>87499.35697297494</v>
+        <v>87566.05840193233</v>
       </c>
       <c r="E61">
-        <v>25546.698</v>
+        <v>26481.32</v>
       </c>
       <c r="F61">
-        <v>55142.698</v>
+        <v>56077.32</v>
       </c>
       <c r="G61">
         <v>8002</v>
@@ -6295,28 +6295,28 @@
         <v>28995</v>
       </c>
       <c r="M61">
-        <v>2773.6777094</v>
+        <v>2820.689196</v>
       </c>
       <c r="N61">
-        <v>26221.3222906</v>
+        <v>26174.310804</v>
       </c>
       <c r="O61">
-        <v>5768.690903932</v>
+        <v>5758.348376880001</v>
       </c>
       <c r="P61">
-        <v>20452.631386668</v>
+        <v>20415.96242712</v>
       </c>
       <c r="Q61">
-        <v>30238.631386668</v>
+        <v>30201.96242712</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1317208606068126</v>
+        <v>0.1336462303859816</v>
       </c>
       <c r="T61">
-        <v>1.984315487455257</v>
+        <v>2.028781302216666</v>
       </c>
       <c r="U61">
         <v>0.0503</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>10.45362981493339</v>
+        <v>10.27940265135117</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07699889215439266</v>
+        <v>0.07684417145999212</v>
       </c>
       <c r="C62">
-        <v>39490.73840193233</v>
+        <v>38622.91960248977</v>
       </c>
       <c r="D62">
-        <v>87566.05840193233</v>
+        <v>87632.86160248976</v>
       </c>
       <c r="E62">
-        <v>26481.32</v>
+        <v>27415.942</v>
       </c>
       <c r="F62">
-        <v>56077.32</v>
+        <v>57011.942</v>
       </c>
       <c r="G62">
         <v>8002</v>
@@ -6377,28 +6377,28 @@
         <v>28995</v>
       </c>
       <c r="M62">
-        <v>2820.689196</v>
+        <v>2867.7006826</v>
       </c>
       <c r="N62">
-        <v>26174.310804</v>
+        <v>26127.2993174</v>
       </c>
       <c r="O62">
-        <v>5758.348376880001</v>
+        <v>5748.005849828</v>
       </c>
       <c r="P62">
-        <v>20415.96242712</v>
+        <v>20379.293467572</v>
       </c>
       <c r="Q62">
-        <v>30201.96242712</v>
+        <v>30165.293467572</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1336462303859816</v>
+        <v>0.1356703370769028</v>
       </c>
       <c r="T62">
-        <v>2.028781302216666</v>
+        <v>2.075527415170967</v>
       </c>
       <c r="U62">
         <v>0.0503</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>10.27940265135117</v>
+        <v>10.11088785378804</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07684417145999212</v>
+        <v>0.07668945076559158</v>
       </c>
       <c r="C63">
-        <v>38622.91960248977</v>
+        <v>37755.20280774641</v>
       </c>
       <c r="D63">
-        <v>87632.86160248976</v>
+        <v>87699.7668077464</v>
       </c>
       <c r="E63">
-        <v>27415.942</v>
+        <v>28350.564</v>
       </c>
       <c r="F63">
-        <v>57011.942</v>
+        <v>57946.564</v>
       </c>
       <c r="G63">
         <v>8002</v>
@@ -6459,28 +6459,28 @@
         <v>28995</v>
       </c>
       <c r="M63">
-        <v>2867.7006826</v>
+        <v>2914.7121692</v>
       </c>
       <c r="N63">
-        <v>26127.2993174</v>
+        <v>26080.2878308</v>
       </c>
       <c r="O63">
-        <v>5748.005849828</v>
+        <v>5737.663322776</v>
       </c>
       <c r="P63">
-        <v>20379.293467572</v>
+        <v>20342.624508024</v>
       </c>
       <c r="Q63">
-        <v>30165.293467572</v>
+        <v>30128.624508024</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1356703370769028</v>
+        <v>0.1378009756989252</v>
       </c>
       <c r="T63">
-        <v>2.075527415170967</v>
+        <v>2.124733849859705</v>
       </c>
       <c r="U63">
         <v>0.0503</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>10.11088785378804</v>
+        <v>9.947809017436617</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07668945076559158</v>
+        <v>0.07653473007119105</v>
       </c>
       <c r="C64">
-        <v>37755.20280774641</v>
+        <v>36887.58825151388</v>
       </c>
       <c r="D64">
-        <v>87699.7668077464</v>
+        <v>87766.77425151388</v>
       </c>
       <c r="E64">
-        <v>28350.564</v>
+        <v>29285.186</v>
       </c>
       <c r="F64">
-        <v>57946.564</v>
+        <v>58881.186</v>
       </c>
       <c r="G64">
         <v>8002</v>
@@ -6541,28 +6541,28 @@
         <v>28995</v>
       </c>
       <c r="M64">
-        <v>2914.7121692</v>
+        <v>2961.7236558</v>
       </c>
       <c r="N64">
-        <v>26080.2878308</v>
+        <v>26033.2763442</v>
       </c>
       <c r="O64">
-        <v>5737.663322776</v>
+        <v>5727.320795724</v>
       </c>
       <c r="P64">
-        <v>20342.624508024</v>
+        <v>20305.955548476</v>
       </c>
       <c r="Q64">
-        <v>30128.624508024</v>
+        <v>30091.955548476</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1378009756989252</v>
+        <v>0.140046783976192</v>
       </c>
       <c r="T64">
-        <v>2.124733849859705</v>
+        <v>2.176600091828915</v>
       </c>
       <c r="U64">
         <v>0.0503</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>9.947809017436617</v>
+        <v>9.789907287001114</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07653473007119105</v>
+        <v>0.07638000937679051</v>
       </c>
       <c r="C65">
-        <v>36887.58825151388</v>
+        <v>36020.0761683189</v>
       </c>
       <c r="D65">
-        <v>87766.77425151388</v>
+        <v>87833.88416831889</v>
       </c>
       <c r="E65">
-        <v>29285.186</v>
+        <v>30219.808</v>
       </c>
       <c r="F65">
-        <v>58881.186</v>
+        <v>59815.808</v>
       </c>
       <c r="G65">
         <v>8002</v>
@@ -6623,28 +6623,28 @@
         <v>28995</v>
       </c>
       <c r="M65">
-        <v>2961.7236558</v>
+        <v>3008.7351424</v>
       </c>
       <c r="N65">
-        <v>26033.2763442</v>
+        <v>25986.2648576</v>
       </c>
       <c r="O65">
-        <v>5727.320795724</v>
+        <v>5716.978268672</v>
       </c>
       <c r="P65">
-        <v>20305.955548476</v>
+        <v>20269.286588928</v>
       </c>
       <c r="Q65">
-        <v>30091.955548476</v>
+        <v>30055.286588928</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.140046783976192</v>
+        <v>0.1424173593799737</v>
       </c>
       <c r="T65">
-        <v>2.176600091828915</v>
+        <v>2.231347791685304</v>
       </c>
       <c r="U65">
         <v>0.0503</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>9.789907287001114</v>
+        <v>9.636939985641723</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07638000937679051</v>
+        <v>0.07622528868238998</v>
       </c>
       <c r="C66">
-        <v>36020.0761683189</v>
+        <v>35152.66679340605</v>
       </c>
       <c r="D66">
-        <v>87833.88416831889</v>
+        <v>87901.09679340605</v>
       </c>
       <c r="E66">
-        <v>30219.808</v>
+        <v>31154.43</v>
       </c>
       <c r="F66">
-        <v>59815.808</v>
+        <v>60750.43</v>
       </c>
       <c r="G66">
         <v>8002</v>
@@ -6705,28 +6705,28 @@
         <v>28995</v>
       </c>
       <c r="M66">
-        <v>3008.7351424</v>
+        <v>3055.746629</v>
       </c>
       <c r="N66">
-        <v>25986.2648576</v>
+        <v>25939.253371</v>
       </c>
       <c r="O66">
-        <v>5716.978268672</v>
+        <v>5706.63574162</v>
       </c>
       <c r="P66">
-        <v>20269.286588928</v>
+        <v>20232.61762938</v>
       </c>
       <c r="Q66">
-        <v>30055.286588928</v>
+        <v>30018.61762938</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1424173593799737</v>
+        <v>0.1449233962354</v>
       </c>
       <c r="T66">
-        <v>2.231347791685304</v>
+        <v>2.289223931533486</v>
       </c>
       <c r="U66">
         <v>0.0503</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>9.636939985641723</v>
+        <v>9.488679370478003</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07622528868238998</v>
+        <v>0.07607056798798945</v>
       </c>
       <c r="C67">
-        <v>35152.66679340605</v>
+        <v>34285.3603627405</v>
       </c>
       <c r="D67">
-        <v>87901.09679340605</v>
+        <v>87968.41236274051</v>
       </c>
       <c r="E67">
-        <v>31154.43</v>
+        <v>32089.052</v>
       </c>
       <c r="F67">
-        <v>60750.43</v>
+        <v>61685.052</v>
       </c>
       <c r="G67">
         <v>8002</v>
@@ -6787,28 +6787,28 @@
         <v>28995</v>
       </c>
       <c r="M67">
-        <v>3055.746629</v>
+        <v>3102.7581156</v>
       </c>
       <c r="N67">
-        <v>25939.253371</v>
+        <v>25892.2418844</v>
       </c>
       <c r="O67">
-        <v>5706.63574162</v>
+        <v>5696.293214568</v>
       </c>
       <c r="P67">
-        <v>20232.61762938</v>
+        <v>20195.948669832</v>
       </c>
       <c r="Q67">
-        <v>30018.61762938</v>
+        <v>29981.948669832</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1449233962354</v>
+        <v>0.1475768470234984</v>
       </c>
       <c r="T67">
-        <v>2.289223931533486</v>
+        <v>2.350504550196268</v>
       </c>
       <c r="U67">
         <v>0.0503</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>9.488679370478003</v>
+        <v>9.344911501228335</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07607056798798945</v>
+        <v>0.0759158472935889</v>
       </c>
       <c r="C68">
-        <v>34285.3603627405</v>
+        <v>33418.15711301089</v>
       </c>
       <c r="D68">
-        <v>87968.41236274051</v>
+        <v>88035.83111301089</v>
       </c>
       <c r="E68">
-        <v>32089.052</v>
+        <v>33023.674</v>
       </c>
       <c r="F68">
-        <v>61685.052</v>
+        <v>62619.674</v>
       </c>
       <c r="G68">
         <v>8002</v>
@@ -6869,28 +6869,28 @@
         <v>28995</v>
       </c>
       <c r="M68">
-        <v>3102.7581156</v>
+        <v>3149.7696022</v>
       </c>
       <c r="N68">
-        <v>25892.2418844</v>
+        <v>25845.2303978</v>
       </c>
       <c r="O68">
-        <v>5696.293214568</v>
+        <v>5685.950687516</v>
       </c>
       <c r="P68">
-        <v>20195.948669832</v>
+        <v>20159.279710284</v>
       </c>
       <c r="Q68">
-        <v>29981.948669832</v>
+        <v>29945.279710284</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1475768470234984</v>
+        <v>0.1503911130108755</v>
       </c>
       <c r="T68">
-        <v>2.350504550196268</v>
+        <v>2.415499145747702</v>
       </c>
       <c r="U68">
         <v>0.0503</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>9.344911501228335</v>
+        <v>9.205435210165227</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.0759158472935889</v>
+        <v>0.07576112659918838</v>
       </c>
       <c r="C69">
-        <v>33418.15711301089</v>
+        <v>32551.05728163185</v>
       </c>
       <c r="D69">
-        <v>88035.83111301089</v>
+        <v>88103.35328163185</v>
       </c>
       <c r="E69">
-        <v>33023.674</v>
+        <v>33958.296</v>
       </c>
       <c r="F69">
-        <v>62619.674</v>
+        <v>63554.296</v>
       </c>
       <c r="G69">
         <v>8002</v>
@@ -6951,28 +6951,28 @@
         <v>28995</v>
       </c>
       <c r="M69">
-        <v>3149.7696022</v>
+        <v>3196.7810888</v>
       </c>
       <c r="N69">
-        <v>25845.2303978</v>
+        <v>25798.2189112</v>
       </c>
       <c r="O69">
-        <v>5685.950687516</v>
+        <v>5675.608160464</v>
       </c>
       <c r="P69">
-        <v>20159.279710284</v>
+        <v>20122.610750736</v>
       </c>
       <c r="Q69">
-        <v>29945.279710284</v>
+        <v>29908.610750736</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1503911130108755</v>
+        <v>0.1533812706224637</v>
       </c>
       <c r="T69">
-        <v>2.415499145747702</v>
+        <v>2.484555903521102</v>
       </c>
       <c r="U69">
         <v>0.0503</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>9.205435210165227</v>
+        <v>9.070061162956915</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07576112659918838</v>
+        <v>0.07560640590478784</v>
       </c>
       <c r="C70">
-        <v>32551.05728163185</v>
+        <v>31684.06110674706</v>
       </c>
       <c r="D70">
-        <v>88103.35328163185</v>
+        <v>88170.97910674707</v>
       </c>
       <c r="E70">
-        <v>33958.296</v>
+        <v>34892.91800000001</v>
       </c>
       <c r="F70">
-        <v>63554.296</v>
+        <v>64488.91800000001</v>
       </c>
       <c r="G70">
         <v>8002</v>
@@ -7033,28 +7033,28 @@
         <v>28995</v>
       </c>
       <c r="M70">
-        <v>3196.7810888</v>
+        <v>3243.7925754</v>
       </c>
       <c r="N70">
-        <v>25798.2189112</v>
+        <v>25751.2074246</v>
       </c>
       <c r="O70">
-        <v>5675.608160464</v>
+        <v>5665.265633412</v>
       </c>
       <c r="P70">
-        <v>20122.610750736</v>
+        <v>20085.941791188</v>
       </c>
       <c r="Q70">
-        <v>29908.610750736</v>
+        <v>29871.941791188</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1533812706224637</v>
+        <v>0.1565643416283479</v>
       </c>
       <c r="T70">
-        <v>2.484555903521102</v>
+        <v>2.558067935989559</v>
       </c>
       <c r="U70">
         <v>0.0503</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>9.070061162956915</v>
+        <v>8.93861100117493</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07560640590478784</v>
+        <v>0.0754516852103873</v>
       </c>
       <c r="C71">
-        <v>31684.06110674706</v>
+        <v>30817.16882723194</v>
       </c>
       <c r="D71">
-        <v>88170.97910674707</v>
+        <v>88238.70882723194</v>
       </c>
       <c r="E71">
-        <v>34892.91800000001</v>
+        <v>35827.54</v>
       </c>
       <c r="F71">
-        <v>64488.91800000001</v>
+        <v>65423.54</v>
       </c>
       <c r="G71">
         <v>8002</v>
@@ -7115,28 +7115,28 @@
         <v>28995</v>
       </c>
       <c r="M71">
-        <v>3243.7925754</v>
+        <v>3290.804062</v>
       </c>
       <c r="N71">
-        <v>25751.2074246</v>
+        <v>25704.195938</v>
       </c>
       <c r="O71">
-        <v>5665.265633412</v>
+        <v>5654.92310636</v>
       </c>
       <c r="P71">
-        <v>20085.941791188</v>
+        <v>20049.27283164</v>
       </c>
       <c r="Q71">
-        <v>29871.941791188</v>
+        <v>29835.27283164</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1565643416283479</v>
+        <v>0.1599596173679577</v>
       </c>
       <c r="T71">
-        <v>2.558067935989559</v>
+        <v>2.63648077062258</v>
       </c>
       <c r="U71">
         <v>0.0503</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>8.93861100117493</v>
+        <v>8.810916558301003</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.0754516852103873</v>
+        <v>0.07612766451598679</v>
       </c>
       <c r="C72">
-        <v>30817.16882723194</v>
+        <v>29587.39691979748</v>
       </c>
       <c r="D72">
-        <v>88238.70882723194</v>
+        <v>87943.55891979749</v>
       </c>
       <c r="E72">
-        <v>35827.54</v>
+        <v>36762.16200000001</v>
       </c>
       <c r="F72">
-        <v>65423.54</v>
+        <v>66358.16200000001</v>
       </c>
       <c r="G72">
         <v>8002</v>
@@ -7197,45 +7197,45 @@
         <v>28995</v>
       </c>
       <c r="M72">
-        <v>3290.804062</v>
+        <v>3437.352791600001</v>
       </c>
       <c r="N72">
-        <v>25704.195938</v>
+        <v>25557.6472084</v>
       </c>
       <c r="O72">
-        <v>5654.92310636</v>
+        <v>5622.682385847999</v>
       </c>
       <c r="P72">
-        <v>20049.27283164</v>
+        <v>19934.964822552</v>
       </c>
       <c r="Q72">
-        <v>29835.27283164</v>
+        <v>29720.964822552</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1599596173679577</v>
+        <v>0.1635890500551269</v>
       </c>
       <c r="T72">
-        <v>2.63648077062258</v>
+        <v>2.720301386954431</v>
       </c>
       <c r="U72">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V72">
         <v>0.22</v>
       </c>
       <c r="W72">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y72">
-        <v>8.810916558301003</v>
+        <v>8.435270325133999</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07612766451598678</v>
+        <v>0.07598464382158623</v>
       </c>
       <c r="C73">
-        <v>29587.39691979749</v>
+        <v>28715.05662349581</v>
       </c>
       <c r="D73">
-        <v>87943.55891979749</v>
+        <v>88005.84062349581</v>
       </c>
       <c r="E73">
-        <v>36762.162</v>
+        <v>37696.784</v>
       </c>
       <c r="F73">
-        <v>66358.162</v>
+        <v>67292.784</v>
       </c>
       <c r="G73">
         <v>8002</v>
@@ -7279,28 +7279,28 @@
         <v>28995</v>
       </c>
       <c r="M73">
-        <v>3437.3527916</v>
+        <v>3485.7662112</v>
       </c>
       <c r="N73">
-        <v>25557.6472084</v>
+        <v>25509.2337888</v>
       </c>
       <c r="O73">
-        <v>5622.682385848</v>
+        <v>5612.031433536</v>
       </c>
       <c r="P73">
-        <v>19934.964822552</v>
+        <v>19897.202355264</v>
       </c>
       <c r="Q73">
-        <v>29720.964822552</v>
+        <v>29683.202355264</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1635890500551268</v>
+        <v>0.1674777279342366</v>
       </c>
       <c r="T73">
-        <v>2.720301386954429</v>
+        <v>2.810109190167126</v>
       </c>
       <c r="U73">
         <v>0.0518</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>8.435270325134002</v>
+        <v>8.318113792840474</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07598464382158623</v>
+        <v>0.0758416231271857</v>
       </c>
       <c r="C74">
-        <v>28715.05662349581</v>
+        <v>27842.80460562473</v>
       </c>
       <c r="D74">
-        <v>88005.84062349581</v>
+        <v>88068.21060562473</v>
       </c>
       <c r="E74">
-        <v>37696.784</v>
+        <v>38631.406</v>
       </c>
       <c r="F74">
-        <v>67292.784</v>
+        <v>68227.406</v>
       </c>
       <c r="G74">
         <v>8002</v>
@@ -7361,28 +7361,28 @@
         <v>28995</v>
       </c>
       <c r="M74">
-        <v>3485.7662112</v>
+        <v>3534.1796308</v>
       </c>
       <c r="N74">
-        <v>25509.2337888</v>
+        <v>25460.8203692</v>
       </c>
       <c r="O74">
-        <v>5612.031433536</v>
+        <v>5601.380481224</v>
       </c>
       <c r="P74">
-        <v>19897.202355264</v>
+        <v>19859.439887976</v>
       </c>
       <c r="Q74">
-        <v>29683.202355264</v>
+        <v>29645.439887976</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1674777279342366</v>
+        <v>0.1716544560266137</v>
       </c>
       <c r="T74">
-        <v>2.810109190167126</v>
+        <v>2.90656942324743</v>
       </c>
       <c r="U74">
         <v>0.0518</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>8.318113792840474</v>
+        <v>8.204167028554988</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.0758416231271857</v>
+        <v>0.07569860243278517</v>
       </c>
       <c r="C75">
-        <v>27842.80460562473</v>
+        <v>26970.64105400686</v>
       </c>
       <c r="D75">
-        <v>88068.21060562473</v>
+        <v>88130.66905400685</v>
       </c>
       <c r="E75">
-        <v>38631.406</v>
+        <v>39566.02799999999</v>
       </c>
       <c r="F75">
-        <v>68227.406</v>
+        <v>69162.02799999999</v>
       </c>
       <c r="G75">
         <v>8002</v>
@@ -7443,28 +7443,28 @@
         <v>28995</v>
       </c>
       <c r="M75">
-        <v>3534.1796308</v>
+        <v>3582.593050399999</v>
       </c>
       <c r="N75">
-        <v>25460.8203692</v>
+        <v>25412.4069496</v>
       </c>
       <c r="O75">
-        <v>5601.380481224</v>
+        <v>5590.729528912</v>
       </c>
       <c r="P75">
-        <v>19859.439887976</v>
+        <v>19821.677420688</v>
       </c>
       <c r="Q75">
-        <v>29645.439887976</v>
+        <v>29607.677420688</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1716544560266137</v>
+        <v>0.1761524708953276</v>
       </c>
       <c r="T75">
-        <v>2.90656942324743</v>
+        <v>3.010449674256988</v>
       </c>
       <c r="U75">
         <v>0.0518</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>8.204167028554988</v>
+        <v>8.09329990654749</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07569860243278517</v>
+        <v>0.07555558173838464</v>
       </c>
       <c r="C76">
-        <v>26970.64105400686</v>
+        <v>26098.56615699799</v>
       </c>
       <c r="D76">
-        <v>88130.66905400685</v>
+        <v>88193.21615699798</v>
       </c>
       <c r="E76">
-        <v>39566.02799999999</v>
+        <v>40500.64999999999</v>
       </c>
       <c r="F76">
-        <v>69162.02799999999</v>
+        <v>70096.64999999999</v>
       </c>
       <c r="G76">
         <v>8002</v>
@@ -7525,28 +7525,28 @@
         <v>28995</v>
       </c>
       <c r="M76">
-        <v>3582.593050399999</v>
+        <v>3631.00647</v>
       </c>
       <c r="N76">
-        <v>25412.4069496</v>
+        <v>25363.99353</v>
       </c>
       <c r="O76">
-        <v>5590.729528912</v>
+        <v>5580.0785766</v>
       </c>
       <c r="P76">
-        <v>19821.677420688</v>
+        <v>19783.9149534</v>
       </c>
       <c r="Q76">
-        <v>29607.677420688</v>
+        <v>29569.9149534</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1761524708953276</v>
+        <v>0.1810103269535386</v>
       </c>
       <c r="T76">
-        <v>3.010449674256988</v>
+        <v>3.12264034534731</v>
       </c>
       <c r="U76">
         <v>0.0518</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>8.09329990654749</v>
+        <v>7.985389241126855</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07555558173838464</v>
+        <v>0.07541256104398411</v>
       </c>
       <c r="C77">
-        <v>26098.56615699799</v>
+        <v>25226.58010348903</v>
       </c>
       <c r="D77">
-        <v>88193.21615699798</v>
+        <v>88255.85210348903</v>
       </c>
       <c r="E77">
-        <v>40500.64999999999</v>
+        <v>41435.272</v>
       </c>
       <c r="F77">
-        <v>70096.64999999999</v>
+        <v>71031.272</v>
       </c>
       <c r="G77">
         <v>8002</v>
@@ -7607,28 +7607,28 @@
         <v>28995</v>
       </c>
       <c r="M77">
-        <v>3631.00647</v>
+        <v>3679.4198896</v>
       </c>
       <c r="N77">
-        <v>25363.99353</v>
+        <v>25315.5801104</v>
       </c>
       <c r="O77">
-        <v>5580.0785766</v>
+        <v>5569.427624288</v>
       </c>
       <c r="P77">
-        <v>19783.9149534</v>
+        <v>19746.152486112</v>
       </c>
       <c r="Q77">
-        <v>29569.9149534</v>
+        <v>29532.152486112</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1810103269535386</v>
+        <v>0.1862730043499338</v>
       </c>
       <c r="T77">
-        <v>3.12264034534731</v>
+        <v>3.244180239028494</v>
       </c>
       <c r="U77">
         <v>0.0518</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>7.985389241126855</v>
+        <v>7.880318330059396</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07541256104398411</v>
+        <v>0.07526954034958357</v>
       </c>
       <c r="C78">
-        <v>25226.58010348903</v>
+        <v>24354.68308290788</v>
       </c>
       <c r="D78">
-        <v>88255.85210348903</v>
+        <v>88318.57708290788</v>
       </c>
       <c r="E78">
-        <v>41435.272</v>
+        <v>42369.894</v>
       </c>
       <c r="F78">
-        <v>71031.272</v>
+        <v>71965.894</v>
       </c>
       <c r="G78">
         <v>8002</v>
@@ -7689,28 +7689,28 @@
         <v>28995</v>
       </c>
       <c r="M78">
-        <v>3679.4198896</v>
+        <v>3727.8333092</v>
       </c>
       <c r="N78">
-        <v>25315.5801104</v>
+        <v>25267.1666908</v>
       </c>
       <c r="O78">
-        <v>5569.427624288</v>
+        <v>5558.776671976</v>
       </c>
       <c r="P78">
-        <v>19746.152486112</v>
+        <v>19708.390018824</v>
       </c>
       <c r="Q78">
-        <v>29532.152486112</v>
+        <v>29494.390018824</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1862730043499338</v>
+        <v>0.1919933058677546</v>
       </c>
       <c r="T78">
-        <v>3.244180239028494</v>
+        <v>3.376288819116736</v>
       </c>
       <c r="U78">
         <v>0.0518</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>7.880318330059396</v>
+        <v>7.777976533565119</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07526954034958357</v>
+        <v>0.07512651965518302</v>
       </c>
       <c r="C79">
-        <v>24354.68308290788</v>
+        <v>23482.87528522134</v>
       </c>
       <c r="D79">
-        <v>88318.57708290788</v>
+        <v>88381.39128522134</v>
       </c>
       <c r="E79">
-        <v>42369.894</v>
+        <v>43304.516</v>
       </c>
       <c r="F79">
-        <v>71965.894</v>
+        <v>72900.516</v>
       </c>
       <c r="G79">
         <v>8002</v>
@@ -7771,28 +7771,28 @@
         <v>28995</v>
       </c>
       <c r="M79">
-        <v>3727.8333092</v>
+        <v>3776.2467288</v>
       </c>
       <c r="N79">
-        <v>25267.1666908</v>
+        <v>25218.7532712</v>
       </c>
       <c r="O79">
-        <v>5558.776671976</v>
+        <v>5548.125719664</v>
       </c>
       <c r="P79">
-        <v>19708.390018824</v>
+        <v>19670.627551536</v>
       </c>
       <c r="Q79">
-        <v>29494.390018824</v>
+        <v>29456.627551536</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1919933058677546</v>
+        <v>0.1982336347962865</v>
       </c>
       <c r="T79">
-        <v>3.376288819116736</v>
+        <v>3.520407270122091</v>
       </c>
       <c r="U79">
         <v>0.0518</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>7.777976533565119</v>
+        <v>7.678258885698898</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07512651965518302</v>
+        <v>0.07498349896078249</v>
       </c>
       <c r="C80">
-        <v>23482.87528522134</v>
+        <v>22611.15690093703</v>
       </c>
       <c r="D80">
-        <v>88381.39128522134</v>
+        <v>88444.29490093703</v>
       </c>
       <c r="E80">
-        <v>43304.516</v>
+        <v>44239.13800000001</v>
       </c>
       <c r="F80">
-        <v>72900.516</v>
+        <v>73835.13800000001</v>
       </c>
       <c r="G80">
         <v>8002</v>
@@ -7853,28 +7853,28 @@
         <v>28995</v>
       </c>
       <c r="M80">
-        <v>3776.2467288</v>
+        <v>3824.6601484</v>
       </c>
       <c r="N80">
-        <v>25218.7532712</v>
+        <v>25170.3398516</v>
       </c>
       <c r="O80">
-        <v>5548.125719664</v>
+        <v>5537.474767352001</v>
       </c>
       <c r="P80">
-        <v>19670.627551536</v>
+        <v>19632.865084248</v>
       </c>
       <c r="Q80">
-        <v>29456.627551536</v>
+        <v>29418.865084248</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1982336347962865</v>
+        <v>0.205068280765631</v>
       </c>
       <c r="T80">
-        <v>3.520407270122091</v>
+        <v>3.678251287889861</v>
       </c>
       <c r="U80">
         <v>0.0518</v>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>7.678258885698898</v>
+        <v>7.581065735247014</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07498349896078249</v>
+        <v>0.07484047826638196</v>
       </c>
       <c r="C81">
-        <v>22611.15690093703</v>
+        <v>21739.52812110529</v>
       </c>
       <c r="D81">
-        <v>88444.29490093703</v>
+        <v>88507.28812110529</v>
       </c>
       <c r="E81">
-        <v>44239.13800000001</v>
+        <v>45173.75999999999</v>
       </c>
       <c r="F81">
-        <v>73835.13800000001</v>
+        <v>74769.75999999999</v>
       </c>
       <c r="G81">
         <v>8002</v>
@@ -7935,28 +7935,28 @@
         <v>28995</v>
       </c>
       <c r="M81">
-        <v>3824.6601484</v>
+        <v>3873.073568</v>
       </c>
       <c r="N81">
-        <v>25170.3398516</v>
+        <v>25121.926432</v>
       </c>
       <c r="O81">
-        <v>5537.474767352001</v>
+        <v>5526.82381504</v>
       </c>
       <c r="P81">
-        <v>19632.865084248</v>
+        <v>19595.10261696</v>
       </c>
       <c r="Q81">
-        <v>29418.865084248</v>
+        <v>29381.10261696</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.205068280765631</v>
+        <v>0.2125863913319098</v>
       </c>
       <c r="T81">
-        <v>3.678251287889861</v>
+        <v>3.851879707434408</v>
       </c>
       <c r="U81">
         <v>0.0518</v>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>7.581065735247014</v>
+        <v>7.486302413556427</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.07484047826638196</v>
+        <v>0.07469745757198143</v>
       </c>
       <c r="C82">
-        <v>21739.52812110529</v>
+        <v>20867.98913732117</v>
       </c>
       <c r="D82">
-        <v>88507.28812110529</v>
+        <v>88570.37113732117</v>
       </c>
       <c r="E82">
-        <v>45173.75999999999</v>
+        <v>46108.382</v>
       </c>
       <c r="F82">
-        <v>74769.75999999999</v>
+        <v>75704.382</v>
       </c>
       <c r="G82">
         <v>8002</v>
@@ -8017,28 +8017,28 @@
         <v>28995</v>
       </c>
       <c r="M82">
-        <v>3873.073568</v>
+        <v>3921.4869876</v>
       </c>
       <c r="N82">
-        <v>25121.926432</v>
+        <v>25073.5130124</v>
       </c>
       <c r="O82">
-        <v>5526.82381504</v>
+        <v>5516.172862728</v>
       </c>
       <c r="P82">
-        <v>19595.10261696</v>
+        <v>19557.340149672</v>
       </c>
       <c r="Q82">
-        <v>29381.10261696</v>
+        <v>29343.340149672</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2125863913319098</v>
+        <v>0.2208958819577971</v>
       </c>
       <c r="T82">
-        <v>3.851879707434408</v>
+        <v>4.043784802720486</v>
       </c>
       <c r="U82">
         <v>0.0518</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>7.486302413556427</v>
+        <v>7.39387892696931</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07469745757198143</v>
+        <v>0.0745544368775809</v>
       </c>
       <c r="C83">
-        <v>20867.98913732117</v>
+        <v>19996.54014172632</v>
       </c>
       <c r="D83">
-        <v>88570.37113732117</v>
+        <v>88633.54414172632</v>
       </c>
       <c r="E83">
-        <v>46108.382</v>
+        <v>47043.004</v>
       </c>
       <c r="F83">
-        <v>75704.382</v>
+        <v>76639.004</v>
       </c>
       <c r="G83">
         <v>8002</v>
@@ -8099,28 +8099,28 @@
         <v>28995</v>
       </c>
       <c r="M83">
-        <v>3921.4869876</v>
+        <v>3969.9004072</v>
       </c>
       <c r="N83">
-        <v>25073.5130124</v>
+        <v>25025.0995928</v>
       </c>
       <c r="O83">
-        <v>5516.172862728</v>
+        <v>5505.521910416001</v>
       </c>
       <c r="P83">
-        <v>19557.340149672</v>
+        <v>19519.577682384</v>
       </c>
       <c r="Q83">
-        <v>29343.340149672</v>
+        <v>29305.577682384</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2208958819577971</v>
+        <v>0.2301286493198939</v>
       </c>
       <c r="T83">
-        <v>4.043784802720486</v>
+        <v>4.257012686371684</v>
       </c>
       <c r="U83">
         <v>0.0518</v>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>7.39387892696931</v>
+        <v>7.303709671762368</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.0745544368775809</v>
+        <v>0.07441141618318037</v>
       </c>
       <c r="C84">
-        <v>19996.54014172632</v>
+        <v>19125.18132701099</v>
       </c>
       <c r="D84">
-        <v>88633.54414172632</v>
+        <v>88696.80732701099</v>
       </c>
       <c r="E84">
-        <v>47043.004</v>
+        <v>47977.626</v>
       </c>
       <c r="F84">
-        <v>76639.004</v>
+        <v>77573.626</v>
       </c>
       <c r="G84">
         <v>8002</v>
@@ -8181,28 +8181,28 @@
         <v>28995</v>
       </c>
       <c r="M84">
-        <v>3969.9004072</v>
+        <v>4018.3138268</v>
       </c>
       <c r="N84">
-        <v>25025.0995928</v>
+        <v>24976.6861732</v>
       </c>
       <c r="O84">
-        <v>5505.521910416001</v>
+        <v>5494.870958104</v>
       </c>
       <c r="P84">
-        <v>19519.577682384</v>
+        <v>19481.815215096</v>
       </c>
       <c r="Q84">
-        <v>29305.577682384</v>
+        <v>29267.815215096</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2301286493198939</v>
+        <v>0.2404476246069434</v>
       </c>
       <c r="T84">
-        <v>4.257012686371684</v>
+        <v>4.495326203393612</v>
       </c>
       <c r="U84">
         <v>0.0518</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>7.303709671762368</v>
+        <v>7.215713169692941</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.07441141618318037</v>
+        <v>0.07426839548877984</v>
       </c>
       <c r="C85">
-        <v>19125.18132701099</v>
+        <v>18253.91288641594</v>
       </c>
       <c r="D85">
-        <v>88696.80732701099</v>
+        <v>88760.16088641595</v>
       </c>
       <c r="E85">
-        <v>47977.626</v>
+        <v>48912.24800000001</v>
       </c>
       <c r="F85">
-        <v>77573.626</v>
+        <v>78508.24800000001</v>
       </c>
       <c r="G85">
         <v>8002</v>
@@ -8263,28 +8263,28 @@
         <v>28995</v>
       </c>
       <c r="M85">
-        <v>4018.3138268</v>
+        <v>4066.7272464</v>
       </c>
       <c r="N85">
-        <v>24976.6861732</v>
+        <v>24928.2727536</v>
       </c>
       <c r="O85">
-        <v>5494.870958104</v>
+        <v>5484.220005792</v>
       </c>
       <c r="P85">
-        <v>19481.815215096</v>
+        <v>19444.052747808</v>
       </c>
       <c r="Q85">
-        <v>29267.815215096</v>
+        <v>29230.052747808</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2404476246069434</v>
+        <v>0.2520564718048741</v>
       </c>
       <c r="T85">
-        <v>4.495326203393612</v>
+        <v>4.763428910043281</v>
       </c>
       <c r="U85">
         <v>0.0518</v>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>7.215713169692941</v>
+        <v>7.129811822434691</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.07426839548877984</v>
+        <v>0.07412537479437931</v>
       </c>
       <c r="C86">
-        <v>18253.91288641596</v>
+        <v>17382.73501373448</v>
       </c>
       <c r="D86">
-        <v>88760.16088641595</v>
+        <v>88823.60501373447</v>
       </c>
       <c r="E86">
-        <v>48912.24799999999</v>
+        <v>49846.87</v>
       </c>
       <c r="F86">
-        <v>78508.24799999999</v>
+        <v>79442.87</v>
       </c>
       <c r="G86">
         <v>8002</v>
@@ -8345,28 +8345,28 @@
         <v>28995</v>
       </c>
       <c r="M86">
-        <v>4066.727246399999</v>
+        <v>4115.140665999999</v>
       </c>
       <c r="N86">
-        <v>24928.2727536</v>
+        <v>24879.859334</v>
       </c>
       <c r="O86">
-        <v>5484.220005792001</v>
+        <v>5473.569053480001</v>
       </c>
       <c r="P86">
-        <v>19444.052747808</v>
+        <v>19406.29028052</v>
       </c>
       <c r="Q86">
-        <v>29230.052747808</v>
+        <v>29192.29028052</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2520564718048739</v>
+        <v>0.2652131652958619</v>
       </c>
       <c r="T86">
-        <v>4.763428910043277</v>
+        <v>5.067278644246234</v>
       </c>
       <c r="U86">
         <v>0.0518</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>7.129811822434693</v>
+        <v>7.045931683347226</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.07412537479437931</v>
+        <v>0.07398235409997876</v>
       </c>
       <c r="C87">
-        <v>17382.73501373448</v>
+        <v>16511.64790331427</v>
       </c>
       <c r="D87">
-        <v>88823.60501373447</v>
+        <v>88887.13990331427</v>
       </c>
       <c r="E87">
-        <v>49846.87</v>
+        <v>50781.492</v>
       </c>
       <c r="F87">
-        <v>79442.87</v>
+        <v>80377.492</v>
       </c>
       <c r="G87">
         <v>8002</v>
@@ -8427,28 +8427,28 @@
         <v>28995</v>
       </c>
       <c r="M87">
-        <v>4115.140665999999</v>
+        <v>4163.5540856</v>
       </c>
       <c r="N87">
-        <v>24879.859334</v>
+        <v>24831.4459144</v>
       </c>
       <c r="O87">
-        <v>5473.569053480001</v>
+        <v>5462.918101168</v>
       </c>
       <c r="P87">
-        <v>19406.29028052</v>
+        <v>19368.527813232</v>
       </c>
       <c r="Q87">
-        <v>29192.29028052</v>
+        <v>29154.527813232</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2652131652958619</v>
+        <v>0.2802493864284197</v>
       </c>
       <c r="T87">
-        <v>5.067278644246234</v>
+        <v>5.414535483335327</v>
       </c>
       <c r="U87">
         <v>0.0518</v>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>7.045931683347226</v>
+        <v>6.964002245168769</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.07398235409997876</v>
+        <v>0.07383933340557822</v>
       </c>
       <c r="C88">
-        <v>16511.64790331427</v>
+        <v>15640.65175005957</v>
       </c>
       <c r="D88">
-        <v>88887.13990331427</v>
+        <v>88950.76575005957</v>
       </c>
       <c r="E88">
-        <v>50781.492</v>
+        <v>51716.114</v>
       </c>
       <c r="F88">
-        <v>80377.492</v>
+        <v>81312.114</v>
       </c>
       <c r="G88">
         <v>8002</v>
@@ -8509,28 +8509,28 @@
         <v>28995</v>
       </c>
       <c r="M88">
-        <v>4163.5540856</v>
+        <v>4211.9675052</v>
       </c>
       <c r="N88">
-        <v>24831.4459144</v>
+        <v>24783.0324948</v>
       </c>
       <c r="O88">
-        <v>5462.918101168</v>
+        <v>5452.267148856</v>
       </c>
       <c r="P88">
-        <v>19368.527813232</v>
+        <v>19330.765345944</v>
       </c>
       <c r="Q88">
-        <v>29154.527813232</v>
+        <v>29116.765345944</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2802493864284197</v>
+        <v>0.2975988723506017</v>
       </c>
       <c r="T88">
-        <v>5.414535483335327</v>
+        <v>5.815216451515052</v>
       </c>
       <c r="U88">
         <v>0.0518</v>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>6.964002245168769</v>
+        <v>6.883956242350736</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.07383933340557822</v>
+        <v>0.07369631271117769</v>
       </c>
       <c r="C89">
-        <v>15640.65175005957</v>
+        <v>14769.74674943302</v>
       </c>
       <c r="D89">
-        <v>88950.76575005957</v>
+        <v>89014.48274943302</v>
       </c>
       <c r="E89">
-        <v>51716.114</v>
+        <v>52650.736</v>
       </c>
       <c r="F89">
-        <v>81312.114</v>
+        <v>82246.736</v>
       </c>
       <c r="G89">
         <v>8002</v>
@@ -8591,28 +8591,28 @@
         <v>28995</v>
       </c>
       <c r="M89">
-        <v>4211.9675052</v>
+        <v>4260.3809248</v>
       </c>
       <c r="N89">
-        <v>24783.0324948</v>
+        <v>24734.6190752</v>
       </c>
       <c r="O89">
-        <v>5452.267148856</v>
+        <v>5441.616196544</v>
       </c>
       <c r="P89">
-        <v>19330.765345944</v>
+        <v>19293.002878656</v>
       </c>
       <c r="Q89">
-        <v>29116.765345944</v>
+        <v>29079.002878656</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2975988723506017</v>
+        <v>0.3178399392598141</v>
       </c>
       <c r="T89">
-        <v>5.815216451515052</v>
+        <v>6.282677581058063</v>
       </c>
       <c r="U89">
         <v>0.0518</v>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>6.883956242350736</v>
+        <v>6.805729466869479</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.07369631271117769</v>
+        <v>0.07355329201677716</v>
       </c>
       <c r="C90">
-        <v>14769.74674943302</v>
+        <v>13898.93309745775</v>
       </c>
       <c r="D90">
-        <v>89014.48274943302</v>
+        <v>89078.29109745774</v>
       </c>
       <c r="E90">
-        <v>52650.736</v>
+        <v>53585.35799999999</v>
       </c>
       <c r="F90">
-        <v>82246.736</v>
+        <v>83181.35799999999</v>
       </c>
       <c r="G90">
         <v>8002</v>
@@ -8673,28 +8673,28 @@
         <v>28995</v>
       </c>
       <c r="M90">
-        <v>4260.3809248</v>
+        <v>4308.794344399999</v>
       </c>
       <c r="N90">
-        <v>24734.6190752</v>
+        <v>24686.2056556</v>
       </c>
       <c r="O90">
-        <v>5441.616196544</v>
+        <v>5430.965244232</v>
       </c>
       <c r="P90">
-        <v>19293.002878656</v>
+        <v>19255.240411368</v>
       </c>
       <c r="Q90">
-        <v>29079.002878656</v>
+        <v>29041.240411368</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3178399392598141</v>
+        <v>0.3417612001525196</v>
       </c>
       <c r="T90">
-        <v>6.282677581058063</v>
+        <v>6.835131643245257</v>
       </c>
       <c r="U90">
         <v>0.0518</v>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>6.805729466869479</v>
+        <v>6.729260596455216</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.07355329201677716</v>
+        <v>0.07460367132237662</v>
       </c>
       <c r="C91">
-        <v>13898.93309745775</v>
+        <v>12497.80685555839</v>
       </c>
       <c r="D91">
-        <v>89078.29109745774</v>
+        <v>88611.78685555838</v>
       </c>
       <c r="E91">
-        <v>53585.35799999999</v>
+        <v>54519.98</v>
       </c>
       <c r="F91">
-        <v>83181.35799999999</v>
+        <v>84115.98</v>
       </c>
       <c r="G91">
         <v>8002</v>
@@ -8755,45 +8755,45 @@
         <v>28995</v>
       </c>
       <c r="M91">
-        <v>4308.794344399999</v>
+        <v>4500.20493</v>
       </c>
       <c r="N91">
-        <v>24686.2056556</v>
+        <v>24494.79507</v>
       </c>
       <c r="O91">
-        <v>5430.965244232</v>
+        <v>5388.8549154</v>
       </c>
       <c r="P91">
-        <v>19255.240411368</v>
+        <v>19105.9401546</v>
       </c>
       <c r="Q91">
-        <v>29041.240411368</v>
+        <v>28891.9401546</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3417612001525196</v>
+        <v>0.3704667132237662</v>
       </c>
       <c r="T91">
-        <v>6.835131643245257</v>
+        <v>7.49807651786989</v>
       </c>
       <c r="U91">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V91">
         <v>0.22</v>
       </c>
       <c r="W91">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y91">
-        <v>6.729260596455216</v>
+        <v>6.4430399172955</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.07460367132237662</v>
+        <v>0.07447391062797609</v>
       </c>
       <c r="C92">
-        <v>12497.80685555839</v>
+        <v>11620.55068573273</v>
       </c>
       <c r="D92">
-        <v>88611.78685555838</v>
+        <v>88669.15268573273</v>
       </c>
       <c r="E92">
-        <v>54519.98</v>
+        <v>55454.602</v>
       </c>
       <c r="F92">
-        <v>84115.98</v>
+        <v>85050.602</v>
       </c>
       <c r="G92">
         <v>8002</v>
@@ -8837,28 +8837,28 @@
         <v>28995</v>
       </c>
       <c r="M92">
-        <v>4500.20493</v>
+        <v>4550.207206999999</v>
       </c>
       <c r="N92">
-        <v>24494.79507</v>
+        <v>24444.792793</v>
       </c>
       <c r="O92">
-        <v>5388.8549154</v>
+        <v>5377.85441446</v>
       </c>
       <c r="P92">
-        <v>19105.9401546</v>
+        <v>19066.93837854</v>
       </c>
       <c r="Q92">
-        <v>28891.9401546</v>
+        <v>28852.93837854</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3704667132237662</v>
+        <v>0.4055512291997344</v>
       </c>
       <c r="T92">
-        <v>7.49807651786989</v>
+        <v>8.308342475744444</v>
       </c>
       <c r="U92">
         <v>0.0535</v>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>6.4430399172955</v>
+        <v>6.372237280841704</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.07447391062797609</v>
+        <v>0.07434414993357555</v>
       </c>
       <c r="C93">
-        <v>11620.55068573273</v>
+        <v>10743.36883943455</v>
       </c>
       <c r="D93">
-        <v>88669.15268573273</v>
+        <v>88726.59283943455</v>
       </c>
       <c r="E93">
-        <v>55454.602</v>
+        <v>56389.224</v>
       </c>
       <c r="F93">
-        <v>85050.602</v>
+        <v>85985.224</v>
       </c>
       <c r="G93">
         <v>8002</v>
@@ -8919,28 +8919,28 @@
         <v>28995</v>
       </c>
       <c r="M93">
-        <v>4550.207206999999</v>
+        <v>4600.209484</v>
       </c>
       <c r="N93">
-        <v>24444.792793</v>
+        <v>24394.790516</v>
       </c>
       <c r="O93">
-        <v>5377.85441446</v>
+        <v>5366.85391352</v>
       </c>
       <c r="P93">
-        <v>19066.93837854</v>
+        <v>19027.93660248</v>
       </c>
       <c r="Q93">
-        <v>28852.93837854</v>
+        <v>28813.93660248</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4055512291997344</v>
+        <v>0.4494068741696946</v>
       </c>
       <c r="T93">
-        <v>8.308342475744444</v>
+        <v>9.321174923087636</v>
       </c>
       <c r="U93">
         <v>0.0535</v>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>6.372237280841704</v>
+        <v>6.302973832136902</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.07434414993357555</v>
+        <v>0.07421438923917503</v>
       </c>
       <c r="C94">
-        <v>10743.36883943455</v>
+        <v>9866.261461198505</v>
       </c>
       <c r="D94">
-        <v>88726.59283943455</v>
+        <v>88784.10746119851</v>
       </c>
       <c r="E94">
-        <v>56389.224</v>
+        <v>57323.84600000001</v>
       </c>
       <c r="F94">
-        <v>85985.224</v>
+        <v>86919.84600000001</v>
       </c>
       <c r="G94">
         <v>8002</v>
@@ -9001,28 +9001,28 @@
         <v>28995</v>
       </c>
       <c r="M94">
-        <v>4600.209484</v>
+        <v>4650.211761</v>
       </c>
       <c r="N94">
-        <v>24394.790516</v>
+        <v>24344.788239</v>
       </c>
       <c r="O94">
-        <v>5366.85391352</v>
+        <v>5355.853412580001</v>
       </c>
       <c r="P94">
-        <v>19027.93660248</v>
+        <v>18988.93482642</v>
       </c>
       <c r="Q94">
-        <v>28813.93660248</v>
+        <v>28774.93482642</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4494068741696946</v>
+        <v>0.5057927034167863</v>
       </c>
       <c r="T94">
-        <v>9.321174923087636</v>
+        <v>10.62338806967174</v>
       </c>
       <c r="U94">
         <v>0.0535</v>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>6.302973832136902</v>
+        <v>6.235199919963387</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.07421438923917503</v>
+        <v>0.07408462854477449</v>
       </c>
       <c r="C95">
-        <v>9866.261461198505</v>
+        <v>8989.22869593426</v>
       </c>
       <c r="D95">
-        <v>88784.10746119851</v>
+        <v>88841.69669593427</v>
       </c>
       <c r="E95">
-        <v>57323.84600000001</v>
+        <v>58258.46800000001</v>
       </c>
       <c r="F95">
-        <v>86919.84600000001</v>
+        <v>87854.46800000001</v>
       </c>
       <c r="G95">
         <v>8002</v>
@@ -9083,28 +9083,28 @@
         <v>28995</v>
       </c>
       <c r="M95">
-        <v>4650.211761</v>
+        <v>4700.214038</v>
       </c>
       <c r="N95">
-        <v>24344.788239</v>
+        <v>24294.785962</v>
       </c>
       <c r="O95">
-        <v>5355.853412580001</v>
+        <v>5344.85291164</v>
       </c>
       <c r="P95">
-        <v>18988.93482642</v>
+        <v>18949.93305036</v>
       </c>
       <c r="Q95">
-        <v>28774.93482642</v>
+        <v>28735.93305036</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5057927034167863</v>
+        <v>0.5809738090795752</v>
       </c>
       <c r="T95">
-        <v>10.62338806967174</v>
+        <v>12.35967226511721</v>
       </c>
       <c r="U95">
         <v>0.0535</v>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>6.235199919963387</v>
+        <v>6.168868005921223</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.07408462854477449</v>
+        <v>0.07395486785037395</v>
       </c>
       <c r="C96">
-        <v>8989.22869593426</v>
+        <v>8112.270688927732</v>
       </c>
       <c r="D96">
-        <v>88841.69669593427</v>
+        <v>88899.36068892773</v>
       </c>
       <c r="E96">
-        <v>58258.46800000001</v>
+        <v>59193.09</v>
       </c>
       <c r="F96">
-        <v>87854.46800000001</v>
+        <v>88789.09</v>
       </c>
       <c r="G96">
         <v>8002</v>
@@ -9165,28 +9165,28 @@
         <v>28995</v>
       </c>
       <c r="M96">
-        <v>4700.214038</v>
+        <v>4750.216315</v>
       </c>
       <c r="N96">
-        <v>24294.785962</v>
+        <v>24244.783685</v>
       </c>
       <c r="O96">
-        <v>5344.85291164</v>
+        <v>5333.8524107</v>
       </c>
       <c r="P96">
-        <v>18949.93305036</v>
+        <v>18910.9312743</v>
       </c>
       <c r="Q96">
-        <v>28735.93305036</v>
+        <v>28696.9312743</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5809738090795752</v>
+        <v>0.6862273570074798</v>
       </c>
       <c r="T96">
-        <v>12.35967226511721</v>
+        <v>14.79047013874088</v>
       </c>
       <c r="U96">
         <v>0.0535</v>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>6.168868005921223</v>
+        <v>6.103932553227316</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.07395486785037395</v>
+        <v>0.07382510715597342</v>
       </c>
       <c r="C97">
-        <v>8112.270688927732</v>
+        <v>7235.387585842254</v>
       </c>
       <c r="D97">
-        <v>88899.36068892773</v>
+        <v>88957.09958584225</v>
       </c>
       <c r="E97">
-        <v>59193.09</v>
+        <v>60127.712</v>
       </c>
       <c r="F97">
-        <v>88789.09</v>
+        <v>89723.712</v>
       </c>
       <c r="G97">
         <v>8002</v>
@@ -9247,28 +9247,28 @@
         <v>28995</v>
       </c>
       <c r="M97">
-        <v>4750.216315</v>
+        <v>4800.218592</v>
       </c>
       <c r="N97">
-        <v>24244.783685</v>
+        <v>24194.781408</v>
       </c>
       <c r="O97">
-        <v>5333.8524107</v>
+        <v>5322.85190976</v>
       </c>
       <c r="P97">
-        <v>18910.9312743</v>
+        <v>18871.92949824</v>
       </c>
       <c r="Q97">
-        <v>28696.9312743</v>
+        <v>28657.92949824</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6862273570074798</v>
+        <v>0.8441076788993368</v>
       </c>
       <c r="T97">
-        <v>14.79047013874088</v>
+        <v>18.43666694917637</v>
       </c>
       <c r="U97">
         <v>0.0535</v>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>6.103932553227316</v>
+        <v>6.040349922464531</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.07382510715597342</v>
+        <v>0.07369534646157289</v>
       </c>
       <c r="C98">
-        <v>7235.387585842254</v>
+        <v>6358.579532719828</v>
       </c>
       <c r="D98">
-        <v>88957.09958584225</v>
+        <v>89014.91353271982</v>
       </c>
       <c r="E98">
-        <v>60127.712</v>
+        <v>61062.33399999999</v>
       </c>
       <c r="F98">
-        <v>89723.712</v>
+        <v>90658.33399999999</v>
       </c>
       <c r="G98">
         <v>8002</v>
@@ -9329,28 +9329,28 @@
         <v>28995</v>
       </c>
       <c r="M98">
-        <v>4800.218592</v>
+        <v>4850.220868999999</v>
       </c>
       <c r="N98">
-        <v>24194.781408</v>
+        <v>24144.779131</v>
       </c>
       <c r="O98">
-        <v>5322.85190976</v>
+        <v>5311.851408820001</v>
       </c>
       <c r="P98">
-        <v>18871.92949824</v>
+        <v>18832.92772218</v>
       </c>
       <c r="Q98">
-        <v>28657.92949824</v>
+        <v>28618.92772218</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8441076788993346</v>
+        <v>1.107241548719095</v>
       </c>
       <c r="T98">
-        <v>18.43666694917632</v>
+        <v>24.51366163323545</v>
       </c>
       <c r="U98">
         <v>0.0535</v>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>6.040349922464531</v>
+        <v>5.978078273779332</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.07369534646157289</v>
+        <v>0.07356558576717236</v>
       </c>
       <c r="C99">
-        <v>6358.579532719828</v>
+        <v>5481.846675982364</v>
       </c>
       <c r="D99">
-        <v>89014.91353271982</v>
+        <v>89072.80267598236</v>
       </c>
       <c r="E99">
-        <v>61062.33399999999</v>
+        <v>61996.95599999999</v>
       </c>
       <c r="F99">
-        <v>90658.33399999999</v>
+        <v>91592.95599999999</v>
       </c>
       <c r="G99">
         <v>8002</v>
@@ -9411,28 +9411,28 @@
         <v>28995</v>
       </c>
       <c r="M99">
-        <v>4850.220868999999</v>
+        <v>4900.223145999999</v>
       </c>
       <c r="N99">
-        <v>24144.779131</v>
+        <v>24094.776854</v>
       </c>
       <c r="O99">
-        <v>5311.851408820001</v>
+        <v>5300.85090788</v>
       </c>
       <c r="P99">
-        <v>18832.92772218</v>
+        <v>18793.92594612</v>
       </c>
       <c r="Q99">
-        <v>28618.92772218</v>
+        <v>28579.92594612</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.107241548719095</v>
+        <v>1.633509288358616</v>
       </c>
       <c r="T99">
-        <v>24.51366163323545</v>
+        <v>36.66765100135372</v>
       </c>
       <c r="U99">
         <v>0.0535</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>5.978078273779332</v>
+        <v>5.917077475067297</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.07356558576717236</v>
+        <v>0.07343582507277181</v>
       </c>
       <c r="C100">
-        <v>5481.846675982364</v>
+        <v>4605.189162432958</v>
       </c>
       <c r="D100">
-        <v>89072.80267598236</v>
+        <v>89130.76716243295</v>
       </c>
       <c r="E100">
-        <v>61996.95599999999</v>
+        <v>62931.57799999999</v>
       </c>
       <c r="F100">
-        <v>91592.95599999999</v>
+        <v>92527.57799999999</v>
       </c>
       <c r="G100">
         <v>8002</v>
@@ -9493,28 +9493,28 @@
         <v>28995</v>
       </c>
       <c r="M100">
-        <v>4900.223145999999</v>
+        <v>4950.225423</v>
       </c>
       <c r="N100">
-        <v>24094.776854</v>
+        <v>24044.774577</v>
       </c>
       <c r="O100">
-        <v>5300.85090788</v>
+        <v>5289.85040694</v>
       </c>
       <c r="P100">
-        <v>18793.92594612</v>
+        <v>18754.92417006</v>
       </c>
       <c r="Q100">
-        <v>28579.92594612</v>
+        <v>28540.92417006</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.633509288358616</v>
+        <v>3.212312507277178</v>
       </c>
       <c r="T100">
-        <v>36.66765100135372</v>
+        <v>73.12961910570851</v>
       </c>
       <c r="U100">
         <v>0.0535</v>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>5.917077475067297</v>
+        <v>5.857309015723182</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.07343582507277181</v>
-      </c>
-      <c r="C101">
-        <v>4605.189162432958</v>
-      </c>
-      <c r="D101">
-        <v>89130.76716243295</v>
-      </c>
-      <c r="E101">
-        <v>62931.57799999999</v>
-      </c>
-      <c r="F101">
-        <v>92527.57799999999</v>
-      </c>
-      <c r="G101">
-        <v>8002</v>
-      </c>
-      <c r="H101">
-        <v>63866.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>38781</v>
-      </c>
-      <c r="K101">
-        <v>9786</v>
-      </c>
-      <c r="L101">
-        <v>28995</v>
-      </c>
-      <c r="M101">
-        <v>4950.225423</v>
-      </c>
-      <c r="N101">
-        <v>24044.774577</v>
-      </c>
-      <c r="O101">
-        <v>5289.85040694</v>
-      </c>
-      <c r="P101">
-        <v>18754.92417006</v>
-      </c>
-      <c r="Q101">
-        <v>28540.92417006</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.212312507277178</v>
-      </c>
-      <c r="T101">
-        <v>73.12961910570851</v>
-      </c>
-      <c r="U101">
-        <v>0.0535</v>
-      </c>
-      <c r="V101">
-        <v>0.22</v>
-      </c>
-      <c r="W101">
-        <v>0.04173</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A1/A+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>5.857309015723182</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
